--- a/client/public/election-data/BC_Election_2026_Riding_Analysis_Preliminary.xlsx
+++ b/client/public/election-data/BC_Election_2026_Riding_Analysis_Preliminary.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive dashboard" sheetId="1" r:id="Ra48c60cae2f34427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding comparison" sheetId="2" r:id="Rf32f2dcce955455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional patterns" sheetId="3" r:id="R897dcdf5f8564d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDP seat changes" sheetId="4" r:id="Rd5da3a45081f4a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closest races" sheetId="5" r:id="Rb07ba222512c41dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and sources" sheetId="6" r:id="R95d2fbb916684e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive dashboard" sheetId="1" r:id="Rb1759a6322464445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding comparison" sheetId="2" r:id="R2a5aa45eff8d42f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional patterns" sheetId="3" r:id="R1d35ce84f15b4559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDP seat changes" sheetId="4" r:id="R8b1d1223dbcf470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closest races" sheetId="5" r:id="Rbf403fbcf4434545"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and sources" sheetId="6" r:id="R41228100a60f4278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since last snapshot" sheetId="7" r:id="R39b2c0de49e540a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,12 +19,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0.00%"/>
     <x:numFmt numFmtId="201" formatCode="+0.00;[Red]-0.00;0.00"/>
     <x:numFmt numFmtId="202" formatCode="#,##0;[Red](#,##0);-"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);–"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -60,8 +62,31 @@
       <x:color rgb="FF213748"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="17"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF136D77"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF516573"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,6 +103,26 @@
         <x:fgColor rgb="FFEFF5F8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17313E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF0F7F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF3F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F9F5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -86,7 +131,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="41">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -150,11 +195,31 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="1">
+  <x:dxfs count="2">
     <x:dxf>
       <x:font>
         <x:color rgb="FF974D13"/>
@@ -162,6 +227,17 @@
       <x:fill>
         <x:patternFill>
           <x:bgColor rgb="FFFFF0D7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFB91C1C"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -403,7 +479,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>PRELIMINARY SNAPSHOT • Initial count completed; results updated 26 Oct 2026 at 10:34 PST • final count scheduled 6-10 Nov</x:v>
+        <x:v>PRELIMINARY INITIAL COUNT • Elections BC data: 26 Oct 2026, 10:34 (site timestamp) • rechecked 27 Oct: NO NEW DATA • final count planned 6-10 Nov</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -911,7 +987,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>2026 count: 26 Oct 2026, 10:34 PST  |  vote share = party votes / valid votes  |  turnout by riding for 2026 NOT available here</x:v>
+        <x:v>Latest official snapshot: 26 Oct 2026, 10:34 (site timestamp) • verified 27 Oct: same data • NDP/Con/Green shares use valid votes</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -17751,7 +17827,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>Public edition | Results snapshot: 26 October 2026 | Preliminary, not certified</x:v>
+        <x:v>Public edition | Initial-count data: 26 Oct 2026 | Latest source check: 27 Oct 2026 | Still preliminary</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -17939,10 +18015,26 @@
     </x:row>
     <x:row r="27" ht="33" customHeight="1">
       <x:c r="A27" t="str">
-        <x:v>Preparation timestamp</x:v>
+        <x:v>Verification update</x:v>
       </x:c>
       <x:c r="B27" s="40" t="str">
-        <x:v>26 October 2026, preparatory initial-count version</x:v>
+        <x:v>27 October 2026: official live results page still shows initial-count snapshot dated 26 Oct, 10:34. No new riding-level data or seat-lead changes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>Comparison baseline</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>26 October 2026 original initial-count report, same underlying Elections BC result as latest available.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>Source status</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>No new official count published as of 27 October check; avoid interpreting unchanged figures as a new vote count.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -17952,4 +18044,7779 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="15" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="15" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="15" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="19" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="32" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="32" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="44" t="str">
+        <x:v>2026 election | Riding-level update comparison</x:v>
+      </x:c>
+      <x:c r="B1" s="44"/>
+      <x:c r="C1" s="44"/>
+      <x:c r="D1" s="44"/>
+      <x:c r="E1" s="44"/>
+      <x:c r="F1" s="44"/>
+      <x:c r="G1" s="44"/>
+      <x:c r="H1" s="44"/>
+      <x:c r="I1" s="44"/>
+      <x:c r="J1" s="44"/>
+      <x:c r="K1" s="44"/>
+      <x:c r="L1" s="44"/>
+      <x:c r="M1" s="44"/>
+      <x:c r="N1" s="44"/>
+      <x:c r="O1" s="44"/>
+      <x:c r="P1" s="44"/>
+      <x:c r="Q1" s="44"/>
+      <x:c r="R1" s="44"/>
+      <x:c r="S1" s="44"/>
+      <x:c r="T1" s="44"/>
+      <x:c r="U1" s="44"/>
+      <x:c r="V1" s="44"/>
+    </x:row>
+    <x:row r="2" ht="27" customHeight="1">
+      <x:c r="A2" s="46" t="str">
+        <x:v>CHECKED 27 OCT 2026  |  LATEST ELECTIONS BC DATA 26 OCT, 10:34  |  NO NEW COUNT PUBLISHED</x:v>
+      </x:c>
+      <x:c r="B2" s="46"/>
+      <x:c r="C2" s="46"/>
+      <x:c r="D2" s="46"/>
+      <x:c r="E2" s="46"/>
+      <x:c r="F2" s="46"/>
+      <x:c r="G2" s="46"/>
+      <x:c r="H2" s="46"/>
+      <x:c r="I2" s="46"/>
+      <x:c r="J2" s="46"/>
+      <x:c r="K2" s="46"/>
+      <x:c r="L2" s="46"/>
+      <x:c r="M2" s="46"/>
+      <x:c r="N2" s="46"/>
+      <x:c r="O2" s="46"/>
+      <x:c r="P2" s="46"/>
+      <x:c r="Q2" s="46"/>
+      <x:c r="R2" s="46"/>
+      <x:c r="S2" s="46"/>
+      <x:c r="T2" s="46"/>
+      <x:c r="U2" s="46"/>
+      <x:c r="V2" s="46"/>
+    </x:row>
+    <x:row r="3" ht="23" customHeight="1">
+      <x:c r="A3" s="47" t="str">
+        <x:v>Blue columns are the saved Oct 26 snapshot; current columns link to Riding comparison; differences are calculated automatically when future official counts are entered.</x:v>
+      </x:c>
+      <x:c r="B3" s="47"/>
+      <x:c r="C3" s="47"/>
+      <x:c r="D3" s="47"/>
+      <x:c r="E3" s="47"/>
+      <x:c r="F3" s="47"/>
+      <x:c r="G3" s="47"/>
+      <x:c r="H3" s="47"/>
+      <x:c r="I3" s="47"/>
+      <x:c r="J3" s="47"/>
+      <x:c r="K3" s="47"/>
+      <x:c r="L3" s="47"/>
+      <x:c r="M3" s="47"/>
+      <x:c r="N3" s="47"/>
+      <x:c r="O3" s="47"/>
+      <x:c r="P3" s="47"/>
+      <x:c r="Q3" s="47"/>
+      <x:c r="R3" s="47"/>
+      <x:c r="S3" s="47"/>
+      <x:c r="T3" s="47"/>
+      <x:c r="U3" s="47"/>
+      <x:c r="V3" s="47"/>
+    </x:row>
+    <x:row r="5" ht="39" customHeight="1">
+      <x:c r="A5" s="50" t="str">
+        <x:v>Riding</x:v>
+      </x:c>
+      <x:c r="B5" s="50" t="str">
+        <x:v>26 Oct NDP</x:v>
+      </x:c>
+      <x:c r="C5" s="50" t="str">
+        <x:v>26 Oct Con</x:v>
+      </x:c>
+      <x:c r="D5" s="50" t="str">
+        <x:v>26 Oct Green</x:v>
+      </x:c>
+      <x:c r="E5" s="50" t="str">
+        <x:v>26 Oct Other</x:v>
+      </x:c>
+      <x:c r="F5" s="50" t="str">
+        <x:v>26 Oct valid</x:v>
+      </x:c>
+      <x:c r="G5" s="50" t="str">
+        <x:v>26 Oct ballots</x:v>
+      </x:c>
+      <x:c r="H5" s="50" t="str">
+        <x:v>Latest NDP</x:v>
+      </x:c>
+      <x:c r="I5" s="50" t="str">
+        <x:v>Latest Con</x:v>
+      </x:c>
+      <x:c r="J5" s="50" t="str">
+        <x:v>Latest Green</x:v>
+      </x:c>
+      <x:c r="K5" s="50" t="str">
+        <x:v>Latest Other</x:v>
+      </x:c>
+      <x:c r="L5" s="50" t="str">
+        <x:v>Latest valid</x:v>
+      </x:c>
+      <x:c r="M5" s="50" t="str">
+        <x:v>Latest ballots</x:v>
+      </x:c>
+      <x:c r="N5" s="50" t="str">
+        <x:v>Δ NDP</x:v>
+      </x:c>
+      <x:c r="O5" s="50" t="str">
+        <x:v>Δ Con</x:v>
+      </x:c>
+      <x:c r="P5" s="50" t="str">
+        <x:v>Δ Green</x:v>
+      </x:c>
+      <x:c r="Q5" s="50" t="str">
+        <x:v>Δ Other</x:v>
+      </x:c>
+      <x:c r="R5" s="50" t="str">
+        <x:v>Δ valid</x:v>
+      </x:c>
+      <x:c r="S5" s="50" t="str">
+        <x:v>Δ ballots</x:v>
+      </x:c>
+      <x:c r="T5" s="50" t="str">
+        <x:v>Riding changed?</x:v>
+      </x:c>
+      <x:c r="U5" s="50" t="str">
+        <x:v>Initial source</x:v>
+      </x:c>
+      <x:c r="V5" s="50" t="str">
+        <x:v>Latest source</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="19" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>Abbotsford-Mission</x:v>
+      </x:c>
+      <x:c r="B6" s="51" t="n">
+        <x:v>7486</x:v>
+      </x:c>
+      <x:c r="C6" s="51" t="n">
+        <x:v>11848</x:v>
+      </x:c>
+      <x:c r="D6" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="51" t="n">
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="F6" s="51" t="n">
+        <x:v>20902</x:v>
+      </x:c>
+      <x:c r="G6" s="51" t="n">
+        <x:v>20948</x:v>
+      </x:c>
+      <x:c r="H6" s="52" t="n">
+        <x:f>'Riding comparison'!K6</x:f>
+        <x:v>7486</x:v>
+      </x:c>
+      <x:c r="I6" s="52" t="n">
+        <x:f>'Riding comparison'!L6</x:f>
+        <x:v>11848</x:v>
+      </x:c>
+      <x:c r="J6" s="52" t="n">
+        <x:f>'Riding comparison'!M6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="52" t="n">
+        <x:f>'Riding comparison'!N6</x:f>
+        <x:v>1568</x:v>
+      </x:c>
+      <x:c r="L6" s="52" t="n">
+        <x:f>'Riding comparison'!O6</x:f>
+        <x:v>20902</x:v>
+      </x:c>
+      <x:c r="M6" s="52" t="n">
+        <x:f>'Riding comparison'!P6</x:f>
+        <x:v>20948</x:v>
+      </x:c>
+      <x:c r="N6" s="53" t="n">
+        <x:f>H6-B6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="53" t="n">
+        <x:f>I6-C6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="53" t="n">
+        <x:f>J6-D6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q6" s="53" t="n">
+        <x:f>K6-E6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R6" s="53" t="n">
+        <x:f>L6-F6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" s="53" t="n">
+        <x:f>M6-G6</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T6" t="str">
+        <x:f>IF(COUNTIF(N6:S6,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U6" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V6" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="19" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>Abbotsford South</x:v>
+      </x:c>
+      <x:c r="B7" s="51" t="n">
+        <x:v>5201</x:v>
+      </x:c>
+      <x:c r="C7" s="51" t="n">
+        <x:v>11023</x:v>
+      </x:c>
+      <x:c r="D7" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="51" t="n">
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="F7" s="51" t="n">
+        <x:v>17369</x:v>
+      </x:c>
+      <x:c r="G7" s="51" t="n">
+        <x:v>17423</x:v>
+      </x:c>
+      <x:c r="H7" s="52" t="n">
+        <x:f>'Riding comparison'!K7</x:f>
+        <x:v>5201</x:v>
+      </x:c>
+      <x:c r="I7" s="52" t="n">
+        <x:f>'Riding comparison'!L7</x:f>
+        <x:v>11023</x:v>
+      </x:c>
+      <x:c r="J7" s="52" t="n">
+        <x:f>'Riding comparison'!M7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="52" t="n">
+        <x:f>'Riding comparison'!N7</x:f>
+        <x:v>1145</x:v>
+      </x:c>
+      <x:c r="L7" s="52" t="n">
+        <x:f>'Riding comparison'!O7</x:f>
+        <x:v>17369</x:v>
+      </x:c>
+      <x:c r="M7" s="52" t="n">
+        <x:f>'Riding comparison'!P7</x:f>
+        <x:v>17423</x:v>
+      </x:c>
+      <x:c r="N7" s="53" t="n">
+        <x:f>H7-B7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="53" t="n">
+        <x:f>I7-C7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="53" t="n">
+        <x:f>J7-D7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q7" s="53" t="n">
+        <x:f>K7-E7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R7" s="53" t="n">
+        <x:f>L7-F7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="53" t="n">
+        <x:f>M7-G7</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T7" t="str">
+        <x:f>IF(COUNTIF(N7:S7,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U7" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V7" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="19" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>Abbotsford West</x:v>
+      </x:c>
+      <x:c r="B8" s="51" t="n">
+        <x:v>4517</x:v>
+      </x:c>
+      <x:c r="C8" s="51" t="n">
+        <x:v>9696</x:v>
+      </x:c>
+      <x:c r="D8" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="51" t="n">
+        <x:v>1442</x:v>
+      </x:c>
+      <x:c r="F8" s="51" t="n">
+        <x:v>15655</x:v>
+      </x:c>
+      <x:c r="G8" s="51" t="n">
+        <x:v>15705</x:v>
+      </x:c>
+      <x:c r="H8" s="52" t="n">
+        <x:f>'Riding comparison'!K8</x:f>
+        <x:v>4517</x:v>
+      </x:c>
+      <x:c r="I8" s="52" t="n">
+        <x:f>'Riding comparison'!L8</x:f>
+        <x:v>9696</x:v>
+      </x:c>
+      <x:c r="J8" s="52" t="n">
+        <x:f>'Riding comparison'!M8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="52" t="n">
+        <x:f>'Riding comparison'!N8</x:f>
+        <x:v>1442</x:v>
+      </x:c>
+      <x:c r="L8" s="52" t="n">
+        <x:f>'Riding comparison'!O8</x:f>
+        <x:v>15655</x:v>
+      </x:c>
+      <x:c r="M8" s="52" t="n">
+        <x:f>'Riding comparison'!P8</x:f>
+        <x:v>15705</x:v>
+      </x:c>
+      <x:c r="N8" s="53" t="n">
+        <x:f>H8-B8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" s="53" t="n">
+        <x:f>I8-C8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="53" t="n">
+        <x:f>J8-D8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q8" s="53" t="n">
+        <x:f>K8-E8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R8" s="53" t="n">
+        <x:f>L8-F8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" s="53" t="n">
+        <x:f>M8-G8</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T8" t="str">
+        <x:f>IF(COUNTIF(N8:S8,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U8" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V8" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="19" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>Boundary-Similkameen</x:v>
+      </x:c>
+      <x:c r="B9" s="51" t="n">
+        <x:v>8870</x:v>
+      </x:c>
+      <x:c r="C9" s="51" t="n">
+        <x:v>11465</x:v>
+      </x:c>
+      <x:c r="D9" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="51" t="n">
+        <x:v>1495</x:v>
+      </x:c>
+      <x:c r="F9" s="51" t="n">
+        <x:v>21830</x:v>
+      </x:c>
+      <x:c r="G9" s="51" t="n">
+        <x:v>21888</x:v>
+      </x:c>
+      <x:c r="H9" s="52" t="n">
+        <x:f>'Riding comparison'!K9</x:f>
+        <x:v>8870</x:v>
+      </x:c>
+      <x:c r="I9" s="52" t="n">
+        <x:f>'Riding comparison'!L9</x:f>
+        <x:v>11465</x:v>
+      </x:c>
+      <x:c r="J9" s="52" t="n">
+        <x:f>'Riding comparison'!M9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9" s="52" t="n">
+        <x:f>'Riding comparison'!N9</x:f>
+        <x:v>1495</x:v>
+      </x:c>
+      <x:c r="L9" s="52" t="n">
+        <x:f>'Riding comparison'!O9</x:f>
+        <x:v>21830</x:v>
+      </x:c>
+      <x:c r="M9" s="52" t="n">
+        <x:f>'Riding comparison'!P9</x:f>
+        <x:v>21888</x:v>
+      </x:c>
+      <x:c r="N9" s="53" t="n">
+        <x:f>H9-B9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" s="53" t="n">
+        <x:f>I9-C9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="53" t="n">
+        <x:f>J9-D9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q9" s="53" t="n">
+        <x:f>K9-E9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R9" s="53" t="n">
+        <x:f>L9-F9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" s="53" t="n">
+        <x:f>M9-G9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T9" t="str">
+        <x:f>IF(COUNTIF(N9:S9,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U9" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V9" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="19" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>Bulkley Valley-Stikine</x:v>
+      </x:c>
+      <x:c r="B10" s="51" t="n">
+        <x:v>3872</x:v>
+      </x:c>
+      <x:c r="C10" s="51" t="n">
+        <x:v>4333</x:v>
+      </x:c>
+      <x:c r="D10" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="51" t="n">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="F10" s="51" t="n">
+        <x:v>8489</x:v>
+      </x:c>
+      <x:c r="G10" s="51" t="n">
+        <x:v>8539</x:v>
+      </x:c>
+      <x:c r="H10" s="52" t="n">
+        <x:f>'Riding comparison'!K10</x:f>
+        <x:v>3872</x:v>
+      </x:c>
+      <x:c r="I10" s="52" t="n">
+        <x:f>'Riding comparison'!L10</x:f>
+        <x:v>4333</x:v>
+      </x:c>
+      <x:c r="J10" s="52" t="n">
+        <x:f>'Riding comparison'!M10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="52" t="n">
+        <x:f>'Riding comparison'!N10</x:f>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="L10" s="52" t="n">
+        <x:f>'Riding comparison'!O10</x:f>
+        <x:v>8489</x:v>
+      </x:c>
+      <x:c r="M10" s="52" t="n">
+        <x:f>'Riding comparison'!P10</x:f>
+        <x:v>8539</x:v>
+      </x:c>
+      <x:c r="N10" s="53" t="n">
+        <x:f>H10-B10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="53" t="n">
+        <x:f>I10-C10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" s="53" t="n">
+        <x:f>J10-D10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q10" s="53" t="n">
+        <x:f>K10-E10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R10" s="53" t="n">
+        <x:f>L10-F10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" s="53" t="n">
+        <x:f>M10-G10</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T10" t="str">
+        <x:f>IF(COUNTIF(N10:S10,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U10" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V10" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="19" customHeight="1">
+      <x:c r="A11" t="str">
+        <x:v>Burnaby Centre</x:v>
+      </x:c>
+      <x:c r="B11" s="51" t="n">
+        <x:v>5955</x:v>
+      </x:c>
+      <x:c r="C11" s="51" t="n">
+        <x:v>6735</x:v>
+      </x:c>
+      <x:c r="D11" s="51" t="n">
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="E11" s="51" t="n">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="F11" s="51" t="n">
+        <x:v>14229</x:v>
+      </x:c>
+      <x:c r="G11" s="51" t="n">
+        <x:v>14275</x:v>
+      </x:c>
+      <x:c r="H11" s="52" t="n">
+        <x:f>'Riding comparison'!K11</x:f>
+        <x:v>5955</x:v>
+      </x:c>
+      <x:c r="I11" s="52" t="n">
+        <x:f>'Riding comparison'!L11</x:f>
+        <x:v>6735</x:v>
+      </x:c>
+      <x:c r="J11" s="52" t="n">
+        <x:f>'Riding comparison'!M11</x:f>
+        <x:v>1169</x:v>
+      </x:c>
+      <x:c r="K11" s="52" t="n">
+        <x:f>'Riding comparison'!N11</x:f>
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="L11" s="52" t="n">
+        <x:f>'Riding comparison'!O11</x:f>
+        <x:v>14229</x:v>
+      </x:c>
+      <x:c r="M11" s="52" t="n">
+        <x:f>'Riding comparison'!P11</x:f>
+        <x:v>14275</x:v>
+      </x:c>
+      <x:c r="N11" s="53" t="n">
+        <x:f>H11-B11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="53" t="n">
+        <x:f>I11-C11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" s="53" t="n">
+        <x:f>J11-D11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q11" s="53" t="n">
+        <x:f>K11-E11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R11" s="53" t="n">
+        <x:f>L11-F11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" s="53" t="n">
+        <x:f>M11-G11</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T11" t="str">
+        <x:f>IF(COUNTIF(N11:S11,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U11" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V11" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="19" customHeight="1">
+      <x:c r="A12" t="str">
+        <x:v>Burnaby East</x:v>
+      </x:c>
+      <x:c r="B12" s="51" t="n">
+        <x:v>7759</x:v>
+      </x:c>
+      <x:c r="C12" s="51" t="n">
+        <x:v>7518</x:v>
+      </x:c>
+      <x:c r="D12" s="51" t="n">
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="E12" s="51" t="n">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="F12" s="51" t="n">
+        <x:v>17472</x:v>
+      </x:c>
+      <x:c r="G12" s="51" t="n">
+        <x:v>17509</x:v>
+      </x:c>
+      <x:c r="H12" s="52" t="n">
+        <x:f>'Riding comparison'!K12</x:f>
+        <x:v>7759</x:v>
+      </x:c>
+      <x:c r="I12" s="52" t="n">
+        <x:f>'Riding comparison'!L12</x:f>
+        <x:v>7518</x:v>
+      </x:c>
+      <x:c r="J12" s="52" t="n">
+        <x:f>'Riding comparison'!M12</x:f>
+        <x:v>1672</x:v>
+      </x:c>
+      <x:c r="K12" s="52" t="n">
+        <x:f>'Riding comparison'!N12</x:f>
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="L12" s="52" t="n">
+        <x:f>'Riding comparison'!O12</x:f>
+        <x:v>17472</x:v>
+      </x:c>
+      <x:c r="M12" s="52" t="n">
+        <x:f>'Riding comparison'!P12</x:f>
+        <x:v>17509</x:v>
+      </x:c>
+      <x:c r="N12" s="53" t="n">
+        <x:f>H12-B12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="53" t="n">
+        <x:f>I12-C12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="53" t="n">
+        <x:f>J12-D12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q12" s="53" t="n">
+        <x:f>K12-E12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R12" s="53" t="n">
+        <x:f>L12-F12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" s="53" t="n">
+        <x:f>M12-G12</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T12" t="str">
+        <x:f>IF(COUNTIF(N12:S12,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U12" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V12" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="19" customHeight="1">
+      <x:c r="A13" t="str">
+        <x:v>Burnaby-New Westminster</x:v>
+      </x:c>
+      <x:c r="B13" s="51" t="n">
+        <x:v>7748</x:v>
+      </x:c>
+      <x:c r="C13" s="51" t="n">
+        <x:v>6163</x:v>
+      </x:c>
+      <x:c r="D13" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="51" t="n">
+        <x:v>13911</x:v>
+      </x:c>
+      <x:c r="G13" s="51" t="n">
+        <x:v>14393</x:v>
+      </x:c>
+      <x:c r="H13" s="52" t="n">
+        <x:f>'Riding comparison'!K13</x:f>
+        <x:v>7748</x:v>
+      </x:c>
+      <x:c r="I13" s="52" t="n">
+        <x:f>'Riding comparison'!L13</x:f>
+        <x:v>6163</x:v>
+      </x:c>
+      <x:c r="J13" s="52" t="n">
+        <x:f>'Riding comparison'!M13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="52" t="n">
+        <x:f>'Riding comparison'!N13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="52" t="n">
+        <x:f>'Riding comparison'!O13</x:f>
+        <x:v>13911</x:v>
+      </x:c>
+      <x:c r="M13" s="52" t="n">
+        <x:f>'Riding comparison'!P13</x:f>
+        <x:v>14393</x:v>
+      </x:c>
+      <x:c r="N13" s="53" t="n">
+        <x:f>H13-B13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="53" t="n">
+        <x:f>I13-C13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="53" t="n">
+        <x:f>J13-D13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q13" s="53" t="n">
+        <x:f>K13-E13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R13" s="53" t="n">
+        <x:f>L13-F13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" s="53" t="n">
+        <x:f>M13-G13</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T13" t="str">
+        <x:f>IF(COUNTIF(N13:S13,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U13" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V13" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="19" customHeight="1">
+      <x:c r="A14" t="str">
+        <x:v>Burnaby North</x:v>
+      </x:c>
+      <x:c r="B14" s="51" t="n">
+        <x:v>7478</x:v>
+      </x:c>
+      <x:c r="C14" s="51" t="n">
+        <x:v>8260</x:v>
+      </x:c>
+      <x:c r="D14" s="51" t="n">
+        <x:v>1618</x:v>
+      </x:c>
+      <x:c r="E14" s="51" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="F14" s="51" t="n">
+        <x:v>17769</x:v>
+      </x:c>
+      <x:c r="G14" s="51" t="n">
+        <x:v>17819</x:v>
+      </x:c>
+      <x:c r="H14" s="52" t="n">
+        <x:f>'Riding comparison'!K14</x:f>
+        <x:v>7478</x:v>
+      </x:c>
+      <x:c r="I14" s="52" t="n">
+        <x:f>'Riding comparison'!L14</x:f>
+        <x:v>8260</x:v>
+      </x:c>
+      <x:c r="J14" s="52" t="n">
+        <x:f>'Riding comparison'!M14</x:f>
+        <x:v>1618</x:v>
+      </x:c>
+      <x:c r="K14" s="52" t="n">
+        <x:f>'Riding comparison'!N14</x:f>
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="L14" s="52" t="n">
+        <x:f>'Riding comparison'!O14</x:f>
+        <x:v>17769</x:v>
+      </x:c>
+      <x:c r="M14" s="52" t="n">
+        <x:f>'Riding comparison'!P14</x:f>
+        <x:v>17819</x:v>
+      </x:c>
+      <x:c r="N14" s="53" t="n">
+        <x:f>H14-B14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="53" t="n">
+        <x:f>I14-C14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="53" t="n">
+        <x:f>J14-D14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q14" s="53" t="n">
+        <x:f>K14-E14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R14" s="53" t="n">
+        <x:f>L14-F14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" s="53" t="n">
+        <x:f>M14-G14</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T14" t="str">
+        <x:f>IF(COUNTIF(N14:S14,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U14" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V14" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="19" customHeight="1">
+      <x:c r="A15" t="str">
+        <x:v>Burnaby South-Metrotown</x:v>
+      </x:c>
+      <x:c r="B15" s="51" t="n">
+        <x:v>5811</x:v>
+      </x:c>
+      <x:c r="C15" s="51" t="n">
+        <x:v>5745</x:v>
+      </x:c>
+      <x:c r="D15" s="51" t="n">
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c r="E15" s="51" t="n">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="F15" s="51" t="n">
+        <x:v>13086</x:v>
+      </x:c>
+      <x:c r="G15" s="51" t="n">
+        <x:v>13144</x:v>
+      </x:c>
+      <x:c r="H15" s="52" t="n">
+        <x:f>'Riding comparison'!K15</x:f>
+        <x:v>5811</x:v>
+      </x:c>
+      <x:c r="I15" s="52" t="n">
+        <x:f>'Riding comparison'!L15</x:f>
+        <x:v>5745</x:v>
+      </x:c>
+      <x:c r="J15" s="52" t="n">
+        <x:f>'Riding comparison'!M15</x:f>
+        <x:v>1151</x:v>
+      </x:c>
+      <x:c r="K15" s="52" t="n">
+        <x:f>'Riding comparison'!N15</x:f>
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="L15" s="52" t="n">
+        <x:f>'Riding comparison'!O15</x:f>
+        <x:v>13086</x:v>
+      </x:c>
+      <x:c r="M15" s="52" t="n">
+        <x:f>'Riding comparison'!P15</x:f>
+        <x:v>13144</x:v>
+      </x:c>
+      <x:c r="N15" s="53" t="n">
+        <x:f>H15-B15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="53" t="n">
+        <x:f>I15-C15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="53" t="n">
+        <x:f>J15-D15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q15" s="53" t="n">
+        <x:f>K15-E15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R15" s="53" t="n">
+        <x:f>L15-F15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" s="53" t="n">
+        <x:f>M15-G15</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T15" t="str">
+        <x:f>IF(COUNTIF(N15:S15,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U15" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V15" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="19" customHeight="1">
+      <x:c r="A16" t="str">
+        <x:v>Cariboo-Chilcotin</x:v>
+      </x:c>
+      <x:c r="B16" s="51" t="n">
+        <x:v>3123</x:v>
+      </x:c>
+      <x:c r="C16" s="51" t="n">
+        <x:v>14218</x:v>
+      </x:c>
+      <x:c r="D16" s="51" t="n">
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="E16" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="51" t="n">
+        <x:v>18444</x:v>
+      </x:c>
+      <x:c r="G16" s="51" t="n">
+        <x:v>18488</x:v>
+      </x:c>
+      <x:c r="H16" s="52" t="n">
+        <x:f>'Riding comparison'!K16</x:f>
+        <x:v>3123</x:v>
+      </x:c>
+      <x:c r="I16" s="52" t="n">
+        <x:f>'Riding comparison'!L16</x:f>
+        <x:v>14218</x:v>
+      </x:c>
+      <x:c r="J16" s="52" t="n">
+        <x:f>'Riding comparison'!M16</x:f>
+        <x:v>1103</x:v>
+      </x:c>
+      <x:c r="K16" s="52" t="n">
+        <x:f>'Riding comparison'!N16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="52" t="n">
+        <x:f>'Riding comparison'!O16</x:f>
+        <x:v>18444</x:v>
+      </x:c>
+      <x:c r="M16" s="52" t="n">
+        <x:f>'Riding comparison'!P16</x:f>
+        <x:v>18488</x:v>
+      </x:c>
+      <x:c r="N16" s="53" t="n">
+        <x:f>H16-B16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="53" t="n">
+        <x:f>I16-C16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="53" t="n">
+        <x:f>J16-D16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q16" s="53" t="n">
+        <x:f>K16-E16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R16" s="53" t="n">
+        <x:f>L16-F16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S16" s="53" t="n">
+        <x:f>M16-G16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T16" t="str">
+        <x:f>IF(COUNTIF(N16:S16,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U16" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V16" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="19" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>Chilliwack-Cultus Lake</x:v>
+      </x:c>
+      <x:c r="B17" s="51" t="n">
+        <x:v>8430</x:v>
+      </x:c>
+      <x:c r="C17" s="51" t="n">
+        <x:v>12712</x:v>
+      </x:c>
+      <x:c r="D17" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="51" t="n">
+        <x:v>21142</x:v>
+      </x:c>
+      <x:c r="G17" s="51" t="n">
+        <x:v>21224</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="n">
+        <x:f>'Riding comparison'!K17</x:f>
+        <x:v>8430</x:v>
+      </x:c>
+      <x:c r="I17" s="52" t="n">
+        <x:f>'Riding comparison'!L17</x:f>
+        <x:v>12712</x:v>
+      </x:c>
+      <x:c r="J17" s="52" t="n">
+        <x:f>'Riding comparison'!M17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="52" t="n">
+        <x:f>'Riding comparison'!N17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="52" t="n">
+        <x:f>'Riding comparison'!O17</x:f>
+        <x:v>21142</x:v>
+      </x:c>
+      <x:c r="M17" s="52" t="n">
+        <x:f>'Riding comparison'!P17</x:f>
+        <x:v>21224</x:v>
+      </x:c>
+      <x:c r="N17" s="53" t="n">
+        <x:f>H17-B17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="53" t="n">
+        <x:f>I17-C17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" s="53" t="n">
+        <x:f>J17-D17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q17" s="53" t="n">
+        <x:f>K17-E17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R17" s="53" t="n">
+        <x:f>L17-F17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S17" s="53" t="n">
+        <x:f>M17-G17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T17" t="str">
+        <x:f>IF(COUNTIF(N17:S17,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U17" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V17" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="19" customHeight="1">
+      <x:c r="A18" t="str">
+        <x:v>Chilliwack North</x:v>
+      </x:c>
+      <x:c r="B18" s="51" t="n">
+        <x:v>5817</x:v>
+      </x:c>
+      <x:c r="C18" s="51" t="n">
+        <x:v>10504</x:v>
+      </x:c>
+      <x:c r="D18" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="51" t="n">
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="F18" s="51" t="n">
+        <x:v>17647</x:v>
+      </x:c>
+      <x:c r="G18" s="51" t="n">
+        <x:v>17683</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="n">
+        <x:f>'Riding comparison'!K18</x:f>
+        <x:v>5817</x:v>
+      </x:c>
+      <x:c r="I18" s="52" t="n">
+        <x:f>'Riding comparison'!L18</x:f>
+        <x:v>10504</x:v>
+      </x:c>
+      <x:c r="J18" s="52" t="n">
+        <x:f>'Riding comparison'!M18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="52" t="n">
+        <x:f>'Riding comparison'!N18</x:f>
+        <x:v>1326</x:v>
+      </x:c>
+      <x:c r="L18" s="52" t="n">
+        <x:f>'Riding comparison'!O18</x:f>
+        <x:v>17647</x:v>
+      </x:c>
+      <x:c r="M18" s="52" t="n">
+        <x:f>'Riding comparison'!P18</x:f>
+        <x:v>17683</x:v>
+      </x:c>
+      <x:c r="N18" s="53" t="n">
+        <x:f>H18-B18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="53" t="n">
+        <x:f>I18-C18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="53" t="n">
+        <x:f>J18-D18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q18" s="53" t="n">
+        <x:f>K18-E18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R18" s="53" t="n">
+        <x:f>L18-F18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" s="53" t="n">
+        <x:f>M18-G18</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T18" t="str">
+        <x:f>IF(COUNTIF(N18:S18,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U18" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V18" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="19" customHeight="1">
+      <x:c r="A19" t="str">
+        <x:v>Columbia River-Revelstoke</x:v>
+      </x:c>
+      <x:c r="B19" s="51" t="n">
+        <x:v>6101</x:v>
+      </x:c>
+      <x:c r="C19" s="51" t="n">
+        <x:v>8894</x:v>
+      </x:c>
+      <x:c r="D19" s="51" t="n">
+        <x:v>1942</x:v>
+      </x:c>
+      <x:c r="E19" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="51" t="n">
+        <x:v>16937</x:v>
+      </x:c>
+      <x:c r="G19" s="51" t="n">
+        <x:v>16962</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="n">
+        <x:f>'Riding comparison'!K19</x:f>
+        <x:v>6101</x:v>
+      </x:c>
+      <x:c r="I19" s="52" t="n">
+        <x:f>'Riding comparison'!L19</x:f>
+        <x:v>8894</x:v>
+      </x:c>
+      <x:c r="J19" s="52" t="n">
+        <x:f>'Riding comparison'!M19</x:f>
+        <x:v>1942</x:v>
+      </x:c>
+      <x:c r="K19" s="52" t="n">
+        <x:f>'Riding comparison'!N19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="52" t="n">
+        <x:f>'Riding comparison'!O19</x:f>
+        <x:v>16937</x:v>
+      </x:c>
+      <x:c r="M19" s="52" t="n">
+        <x:f>'Riding comparison'!P19</x:f>
+        <x:v>16962</x:v>
+      </x:c>
+      <x:c r="N19" s="53" t="n">
+        <x:f>H19-B19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="53" t="n">
+        <x:f>I19-C19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="53" t="n">
+        <x:f>J19-D19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q19" s="53" t="n">
+        <x:f>K19-E19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R19" s="53" t="n">
+        <x:f>L19-F19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" s="53" t="n">
+        <x:f>M19-G19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T19" t="str">
+        <x:f>IF(COUNTIF(N19:S19,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U19" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V19" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="19" customHeight="1">
+      <x:c r="A20" t="str">
+        <x:v>Coquitlam-Burke Mountain</x:v>
+      </x:c>
+      <x:c r="B20" s="51" t="n">
+        <x:v>7323</x:v>
+      </x:c>
+      <x:c r="C20" s="51" t="n">
+        <x:v>9814</x:v>
+      </x:c>
+      <x:c r="D20" s="51" t="n">
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="E20" s="51" t="n">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="F20" s="51" t="n">
+        <x:v>18657</x:v>
+      </x:c>
+      <x:c r="G20" s="51" t="n">
+        <x:v>18687</x:v>
+      </x:c>
+      <x:c r="H20" s="52" t="n">
+        <x:f>'Riding comparison'!K20</x:f>
+        <x:v>7323</x:v>
+      </x:c>
+      <x:c r="I20" s="52" t="n">
+        <x:f>'Riding comparison'!L20</x:f>
+        <x:v>9814</x:v>
+      </x:c>
+      <x:c r="J20" s="52" t="n">
+        <x:f>'Riding comparison'!M20</x:f>
+        <x:v>1111</x:v>
+      </x:c>
+      <x:c r="K20" s="52" t="n">
+        <x:f>'Riding comparison'!N20</x:f>
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="L20" s="52" t="n">
+        <x:f>'Riding comparison'!O20</x:f>
+        <x:v>18657</x:v>
+      </x:c>
+      <x:c r="M20" s="52" t="n">
+        <x:f>'Riding comparison'!P20</x:f>
+        <x:v>18687</x:v>
+      </x:c>
+      <x:c r="N20" s="53" t="n">
+        <x:f>H20-B20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="53" t="n">
+        <x:f>I20-C20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="53" t="n">
+        <x:f>J20-D20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q20" s="53" t="n">
+        <x:f>K20-E20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R20" s="53" t="n">
+        <x:f>L20-F20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S20" s="53" t="n">
+        <x:f>M20-G20</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T20" t="str">
+        <x:f>IF(COUNTIF(N20:S20,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U20" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V20" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="19" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>Coquitlam-Maillardville</x:v>
+      </x:c>
+      <x:c r="B21" s="51" t="n">
+        <x:v>8057</x:v>
+      </x:c>
+      <x:c r="C21" s="51" t="n">
+        <x:v>9626</x:v>
+      </x:c>
+      <x:c r="D21" s="51" t="n">
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="E21" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="51" t="n">
+        <x:v>19415</x:v>
+      </x:c>
+      <x:c r="G21" s="51" t="n">
+        <x:v>19451</x:v>
+      </x:c>
+      <x:c r="H21" s="52" t="n">
+        <x:f>'Riding comparison'!K21</x:f>
+        <x:v>8057</x:v>
+      </x:c>
+      <x:c r="I21" s="52" t="n">
+        <x:f>'Riding comparison'!L21</x:f>
+        <x:v>9626</x:v>
+      </x:c>
+      <x:c r="J21" s="52" t="n">
+        <x:f>'Riding comparison'!M21</x:f>
+        <x:v>1732</x:v>
+      </x:c>
+      <x:c r="K21" s="52" t="n">
+        <x:f>'Riding comparison'!N21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21" s="52" t="n">
+        <x:f>'Riding comparison'!O21</x:f>
+        <x:v>19415</x:v>
+      </x:c>
+      <x:c r="M21" s="52" t="n">
+        <x:f>'Riding comparison'!P21</x:f>
+        <x:v>19451</x:v>
+      </x:c>
+      <x:c r="N21" s="53" t="n">
+        <x:f>H21-B21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" s="53" t="n">
+        <x:f>I21-C21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="53" t="n">
+        <x:f>J21-D21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q21" s="53" t="n">
+        <x:f>K21-E21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R21" s="53" t="n">
+        <x:f>L21-F21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S21" s="53" t="n">
+        <x:f>M21-G21</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T21" t="str">
+        <x:f>IF(COUNTIF(N21:S21,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U21" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V21" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="19" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Courtenay-Comox</x:v>
+      </x:c>
+      <x:c r="B22" s="51" t="n">
+        <x:v>13390</x:v>
+      </x:c>
+      <x:c r="C22" s="51" t="n">
+        <x:v>12694</x:v>
+      </x:c>
+      <x:c r="D22" s="51" t="n">
+        <x:v>2882</x:v>
+      </x:c>
+      <x:c r="E22" s="51" t="n">
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="F22" s="51" t="n">
+        <x:v>29706</x:v>
+      </x:c>
+      <x:c r="G22" s="51" t="n">
+        <x:v>29722</x:v>
+      </x:c>
+      <x:c r="H22" s="52" t="n">
+        <x:f>'Riding comparison'!K22</x:f>
+        <x:v>13390</x:v>
+      </x:c>
+      <x:c r="I22" s="52" t="n">
+        <x:f>'Riding comparison'!L22</x:f>
+        <x:v>12694</x:v>
+      </x:c>
+      <x:c r="J22" s="52" t="n">
+        <x:f>'Riding comparison'!M22</x:f>
+        <x:v>2882</x:v>
+      </x:c>
+      <x:c r="K22" s="52" t="n">
+        <x:f>'Riding comparison'!N22</x:f>
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="L22" s="52" t="n">
+        <x:f>'Riding comparison'!O22</x:f>
+        <x:v>29706</x:v>
+      </x:c>
+      <x:c r="M22" s="52" t="n">
+        <x:f>'Riding comparison'!P22</x:f>
+        <x:v>29722</x:v>
+      </x:c>
+      <x:c r="N22" s="53" t="n">
+        <x:f>H22-B22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O22" s="53" t="n">
+        <x:f>I22-C22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" s="53" t="n">
+        <x:f>J22-D22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q22" s="53" t="n">
+        <x:f>K22-E22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R22" s="53" t="n">
+        <x:f>L22-F22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S22" s="53" t="n">
+        <x:f>M22-G22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T22" t="str">
+        <x:f>IF(COUNTIF(N22:S22,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U22" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V22" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="19" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>Cowichan Valley</x:v>
+      </x:c>
+      <x:c r="B23" s="51" t="n">
+        <x:v>10949</x:v>
+      </x:c>
+      <x:c r="C23" s="51" t="n">
+        <x:v>11100</x:v>
+      </x:c>
+      <x:c r="D23" s="51" t="n">
+        <x:v>3750</x:v>
+      </x:c>
+      <x:c r="E23" s="51" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F23" s="51" t="n">
+        <x:v>25899</x:v>
+      </x:c>
+      <x:c r="G23" s="51" t="n">
+        <x:v>25940</x:v>
+      </x:c>
+      <x:c r="H23" s="52" t="n">
+        <x:f>'Riding comparison'!K23</x:f>
+        <x:v>10949</x:v>
+      </x:c>
+      <x:c r="I23" s="52" t="n">
+        <x:f>'Riding comparison'!L23</x:f>
+        <x:v>11100</x:v>
+      </x:c>
+      <x:c r="J23" s="52" t="n">
+        <x:f>'Riding comparison'!M23</x:f>
+        <x:v>3750</x:v>
+      </x:c>
+      <x:c r="K23" s="52" t="n">
+        <x:f>'Riding comparison'!N23</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="L23" s="52" t="n">
+        <x:f>'Riding comparison'!O23</x:f>
+        <x:v>25899</x:v>
+      </x:c>
+      <x:c r="M23" s="52" t="n">
+        <x:f>'Riding comparison'!P23</x:f>
+        <x:v>25940</x:v>
+      </x:c>
+      <x:c r="N23" s="53" t="n">
+        <x:f>H23-B23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O23" s="53" t="n">
+        <x:f>I23-C23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P23" s="53" t="n">
+        <x:f>J23-D23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q23" s="53" t="n">
+        <x:f>K23-E23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R23" s="53" t="n">
+        <x:f>L23-F23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S23" s="53" t="n">
+        <x:f>M23-G23</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T23" t="str">
+        <x:f>IF(COUNTIF(N23:S23,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U23" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V23" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="19" customHeight="1">
+      <x:c r="A24" t="str">
+        <x:v>Delta North</x:v>
+      </x:c>
+      <x:c r="B24" s="51" t="n">
+        <x:v>7425</x:v>
+      </x:c>
+      <x:c r="C24" s="51" t="n">
+        <x:v>9796</x:v>
+      </x:c>
+      <x:c r="D24" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="51" t="n">
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="F24" s="51" t="n">
+        <x:v>18283</x:v>
+      </x:c>
+      <x:c r="G24" s="51" t="n">
+        <x:v>18338</x:v>
+      </x:c>
+      <x:c r="H24" s="52" t="n">
+        <x:f>'Riding comparison'!K24</x:f>
+        <x:v>7425</x:v>
+      </x:c>
+      <x:c r="I24" s="52" t="n">
+        <x:f>'Riding comparison'!L24</x:f>
+        <x:v>9796</x:v>
+      </x:c>
+      <x:c r="J24" s="52" t="n">
+        <x:f>'Riding comparison'!M24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" s="52" t="n">
+        <x:f>'Riding comparison'!N24</x:f>
+        <x:v>1062</x:v>
+      </x:c>
+      <x:c r="L24" s="52" t="n">
+        <x:f>'Riding comparison'!O24</x:f>
+        <x:v>18283</x:v>
+      </x:c>
+      <x:c r="M24" s="52" t="n">
+        <x:f>'Riding comparison'!P24</x:f>
+        <x:v>18338</x:v>
+      </x:c>
+      <x:c r="N24" s="53" t="n">
+        <x:f>H24-B24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O24" s="53" t="n">
+        <x:f>I24-C24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P24" s="53" t="n">
+        <x:f>J24-D24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q24" s="53" t="n">
+        <x:f>K24-E24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R24" s="53" t="n">
+        <x:f>L24-F24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S24" s="53" t="n">
+        <x:f>M24-G24</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T24" t="str">
+        <x:f>IF(COUNTIF(N24:S24,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U24" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V24" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="19" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>Delta South</x:v>
+      </x:c>
+      <x:c r="B25" s="51" t="n">
+        <x:v>6918</x:v>
+      </x:c>
+      <x:c r="C25" s="51" t="n">
+        <x:v>14473</x:v>
+      </x:c>
+      <x:c r="D25" s="51" t="n">
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="E25" s="51" t="n">
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="F25" s="51" t="n">
+        <x:v>24178</x:v>
+      </x:c>
+      <x:c r="G25" s="51" t="n">
+        <x:v>24209</x:v>
+      </x:c>
+      <x:c r="H25" s="52" t="n">
+        <x:f>'Riding comparison'!K25</x:f>
+        <x:v>6918</x:v>
+      </x:c>
+      <x:c r="I25" s="52" t="n">
+        <x:f>'Riding comparison'!L25</x:f>
+        <x:v>14473</x:v>
+      </x:c>
+      <x:c r="J25" s="52" t="n">
+        <x:f>'Riding comparison'!M25</x:f>
+        <x:v>1988</x:v>
+      </x:c>
+      <x:c r="K25" s="52" t="n">
+        <x:f>'Riding comparison'!N25</x:f>
+        <x:v>799</x:v>
+      </x:c>
+      <x:c r="L25" s="52" t="n">
+        <x:f>'Riding comparison'!O25</x:f>
+        <x:v>24178</x:v>
+      </x:c>
+      <x:c r="M25" s="52" t="n">
+        <x:f>'Riding comparison'!P25</x:f>
+        <x:v>24209</x:v>
+      </x:c>
+      <x:c r="N25" s="53" t="n">
+        <x:f>H25-B25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O25" s="53" t="n">
+        <x:f>I25-C25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P25" s="53" t="n">
+        <x:f>J25-D25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q25" s="53" t="n">
+        <x:f>K25-E25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R25" s="53" t="n">
+        <x:f>L25-F25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S25" s="53" t="n">
+        <x:f>M25-G25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T25" t="str">
+        <x:f>IF(COUNTIF(N25:S25,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U25" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V25" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="19" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>Esquimalt-Colwood</x:v>
+      </x:c>
+      <x:c r="B26" s="51" t="n">
+        <x:v>10955</x:v>
+      </x:c>
+      <x:c r="C26" s="51" t="n">
+        <x:v>7391</x:v>
+      </x:c>
+      <x:c r="D26" s="51" t="n">
+        <x:v>5766</x:v>
+      </x:c>
+      <x:c r="E26" s="51" t="n">
+        <x:v>1216</x:v>
+      </x:c>
+      <x:c r="F26" s="51" t="n">
+        <x:v>25328</x:v>
+      </x:c>
+      <x:c r="G26" s="51" t="n">
+        <x:v>25359</x:v>
+      </x:c>
+      <x:c r="H26" s="52" t="n">
+        <x:f>'Riding comparison'!K26</x:f>
+        <x:v>10955</x:v>
+      </x:c>
+      <x:c r="I26" s="52" t="n">
+        <x:f>'Riding comparison'!L26</x:f>
+        <x:v>7391</x:v>
+      </x:c>
+      <x:c r="J26" s="52" t="n">
+        <x:f>'Riding comparison'!M26</x:f>
+        <x:v>5766</x:v>
+      </x:c>
+      <x:c r="K26" s="52" t="n">
+        <x:f>'Riding comparison'!N26</x:f>
+        <x:v>1216</x:v>
+      </x:c>
+      <x:c r="L26" s="52" t="n">
+        <x:f>'Riding comparison'!O26</x:f>
+        <x:v>25328</x:v>
+      </x:c>
+      <x:c r="M26" s="52" t="n">
+        <x:f>'Riding comparison'!P26</x:f>
+        <x:v>25359</x:v>
+      </x:c>
+      <x:c r="N26" s="53" t="n">
+        <x:f>H26-B26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" s="53" t="n">
+        <x:f>I26-C26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P26" s="53" t="n">
+        <x:f>J26-D26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q26" s="53" t="n">
+        <x:f>K26-E26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R26" s="53" t="n">
+        <x:f>L26-F26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S26" s="53" t="n">
+        <x:f>M26-G26</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T26" t="str">
+        <x:f>IF(COUNTIF(N26:S26,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U26" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V26" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="19" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>Fraser-Nicola</x:v>
+      </x:c>
+      <x:c r="B27" s="51" t="n">
+        <x:v>4744</x:v>
+      </x:c>
+      <x:c r="C27" s="51" t="n">
+        <x:v>9762</x:v>
+      </x:c>
+      <x:c r="D27" s="51" t="n">
+        <x:v>2190</x:v>
+      </x:c>
+      <x:c r="E27" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" s="51" t="n">
+        <x:v>16696</x:v>
+      </x:c>
+      <x:c r="G27" s="51" t="n">
+        <x:v>16730</x:v>
+      </x:c>
+      <x:c r="H27" s="52" t="n">
+        <x:f>'Riding comparison'!K27</x:f>
+        <x:v>4744</x:v>
+      </x:c>
+      <x:c r="I27" s="52" t="n">
+        <x:f>'Riding comparison'!L27</x:f>
+        <x:v>9762</x:v>
+      </x:c>
+      <x:c r="J27" s="52" t="n">
+        <x:f>'Riding comparison'!M27</x:f>
+        <x:v>2190</x:v>
+      </x:c>
+      <x:c r="K27" s="52" t="n">
+        <x:f>'Riding comparison'!N27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" s="52" t="n">
+        <x:f>'Riding comparison'!O27</x:f>
+        <x:v>16696</x:v>
+      </x:c>
+      <x:c r="M27" s="52" t="n">
+        <x:f>'Riding comparison'!P27</x:f>
+        <x:v>16730</x:v>
+      </x:c>
+      <x:c r="N27" s="53" t="n">
+        <x:f>H27-B27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O27" s="53" t="n">
+        <x:f>I27-C27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P27" s="53" t="n">
+        <x:f>J27-D27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q27" s="53" t="n">
+        <x:f>K27-E27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R27" s="53" t="n">
+        <x:f>L27-F27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S27" s="53" t="n">
+        <x:f>M27-G27</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T27" t="str">
+        <x:f>IF(COUNTIF(N27:S27,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U27" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V27" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="19" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>Juan de Fuca-Malahat</x:v>
+      </x:c>
+      <x:c r="B28" s="51" t="n">
+        <x:v>8478</x:v>
+      </x:c>
+      <x:c r="C28" s="51" t="n">
+        <x:v>9246</x:v>
+      </x:c>
+      <x:c r="D28" s="51" t="n">
+        <x:v>3880</x:v>
+      </x:c>
+      <x:c r="E28" s="51" t="n">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="F28" s="51" t="n">
+        <x:v>22217</x:v>
+      </x:c>
+      <x:c r="G28" s="51" t="n">
+        <x:v>22236</x:v>
+      </x:c>
+      <x:c r="H28" s="52" t="n">
+        <x:f>'Riding comparison'!K28</x:f>
+        <x:v>8478</x:v>
+      </x:c>
+      <x:c r="I28" s="52" t="n">
+        <x:f>'Riding comparison'!L28</x:f>
+        <x:v>9246</x:v>
+      </x:c>
+      <x:c r="J28" s="52" t="n">
+        <x:f>'Riding comparison'!M28</x:f>
+        <x:v>3880</x:v>
+      </x:c>
+      <x:c r="K28" s="52" t="n">
+        <x:f>'Riding comparison'!N28</x:f>
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="L28" s="52" t="n">
+        <x:f>'Riding comparison'!O28</x:f>
+        <x:v>22217</x:v>
+      </x:c>
+      <x:c r="M28" s="52" t="n">
+        <x:f>'Riding comparison'!P28</x:f>
+        <x:v>22236</x:v>
+      </x:c>
+      <x:c r="N28" s="53" t="n">
+        <x:f>H28-B28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O28" s="53" t="n">
+        <x:f>I28-C28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P28" s="53" t="n">
+        <x:f>J28-D28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q28" s="53" t="n">
+        <x:f>K28-E28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R28" s="53" t="n">
+        <x:f>L28-F28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S28" s="53" t="n">
+        <x:f>M28-G28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T28" t="str">
+        <x:f>IF(COUNTIF(N28:S28,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U28" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V28" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="19" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>Kamloops Centre</x:v>
+      </x:c>
+      <x:c r="B29" s="51" t="n">
+        <x:v>6751</x:v>
+      </x:c>
+      <x:c r="C29" s="51" t="n">
+        <x:v>11770</x:v>
+      </x:c>
+      <x:c r="D29" s="51" t="n">
+        <x:v>2482</x:v>
+      </x:c>
+      <x:c r="E29" s="51" t="n">
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="F29" s="51" t="n">
+        <x:v>22063</x:v>
+      </x:c>
+      <x:c r="G29" s="51" t="n">
+        <x:v>22085</x:v>
+      </x:c>
+      <x:c r="H29" s="52" t="n">
+        <x:f>'Riding comparison'!K29</x:f>
+        <x:v>6751</x:v>
+      </x:c>
+      <x:c r="I29" s="52" t="n">
+        <x:f>'Riding comparison'!L29</x:f>
+        <x:v>11770</x:v>
+      </x:c>
+      <x:c r="J29" s="52" t="n">
+        <x:f>'Riding comparison'!M29</x:f>
+        <x:v>2482</x:v>
+      </x:c>
+      <x:c r="K29" s="52" t="n">
+        <x:f>'Riding comparison'!N29</x:f>
+        <x:v>1060</x:v>
+      </x:c>
+      <x:c r="L29" s="52" t="n">
+        <x:f>'Riding comparison'!O29</x:f>
+        <x:v>22063</x:v>
+      </x:c>
+      <x:c r="M29" s="52" t="n">
+        <x:f>'Riding comparison'!P29</x:f>
+        <x:v>22085</x:v>
+      </x:c>
+      <x:c r="N29" s="53" t="n">
+        <x:f>H29-B29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O29" s="53" t="n">
+        <x:f>I29-C29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P29" s="53" t="n">
+        <x:f>J29-D29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q29" s="53" t="n">
+        <x:f>K29-E29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R29" s="53" t="n">
+        <x:f>L29-F29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S29" s="53" t="n">
+        <x:f>M29-G29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T29" t="str">
+        <x:f>IF(COUNTIF(N29:S29,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U29" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V29" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="19" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>Kamloops-North Thompson</x:v>
+      </x:c>
+      <x:c r="B30" s="51" t="n">
+        <x:v>7617</x:v>
+      </x:c>
+      <x:c r="C30" s="51" t="n">
+        <x:v>17232</x:v>
+      </x:c>
+      <x:c r="D30" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E30" s="51" t="n">
+        <x:v>1670</x:v>
+      </x:c>
+      <x:c r="F30" s="51" t="n">
+        <x:v>26519</x:v>
+      </x:c>
+      <x:c r="G30" s="51" t="n">
+        <x:v>26602</x:v>
+      </x:c>
+      <x:c r="H30" s="52" t="n">
+        <x:f>'Riding comparison'!K30</x:f>
+        <x:v>7617</x:v>
+      </x:c>
+      <x:c r="I30" s="52" t="n">
+        <x:f>'Riding comparison'!L30</x:f>
+        <x:v>17232</x:v>
+      </x:c>
+      <x:c r="J30" s="52" t="n">
+        <x:f>'Riding comparison'!M30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" s="52" t="n">
+        <x:f>'Riding comparison'!N30</x:f>
+        <x:v>1670</x:v>
+      </x:c>
+      <x:c r="L30" s="52" t="n">
+        <x:f>'Riding comparison'!O30</x:f>
+        <x:v>26519</x:v>
+      </x:c>
+      <x:c r="M30" s="52" t="n">
+        <x:f>'Riding comparison'!P30</x:f>
+        <x:v>26602</x:v>
+      </x:c>
+      <x:c r="N30" s="53" t="n">
+        <x:f>H30-B30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O30" s="53" t="n">
+        <x:f>I30-C30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P30" s="53" t="n">
+        <x:f>J30-D30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q30" s="53" t="n">
+        <x:f>K30-E30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R30" s="53" t="n">
+        <x:f>L30-F30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S30" s="53" t="n">
+        <x:f>M30-G30</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T30" t="str">
+        <x:f>IF(COUNTIF(N30:S30,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U30" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V30" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="19" customHeight="1">
+      <x:c r="A31" t="str">
+        <x:v>Kelowna Centre</x:v>
+      </x:c>
+      <x:c r="B31" s="51" t="n">
+        <x:v>10659</x:v>
+      </x:c>
+      <x:c r="C31" s="51" t="n">
+        <x:v>10791</x:v>
+      </x:c>
+      <x:c r="D31" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="51" t="n">
+        <x:v>873</x:v>
+      </x:c>
+      <x:c r="F31" s="51" t="n">
+        <x:v>22323</x:v>
+      </x:c>
+      <x:c r="G31" s="51" t="n">
+        <x:v>22379</x:v>
+      </x:c>
+      <x:c r="H31" s="52" t="n">
+        <x:f>'Riding comparison'!K31</x:f>
+        <x:v>10659</x:v>
+      </x:c>
+      <x:c r="I31" s="52" t="n">
+        <x:f>'Riding comparison'!L31</x:f>
+        <x:v>10791</x:v>
+      </x:c>
+      <x:c r="J31" s="52" t="n">
+        <x:f>'Riding comparison'!M31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="52" t="n">
+        <x:f>'Riding comparison'!N31</x:f>
+        <x:v>873</x:v>
+      </x:c>
+      <x:c r="L31" s="52" t="n">
+        <x:f>'Riding comparison'!O31</x:f>
+        <x:v>22323</x:v>
+      </x:c>
+      <x:c r="M31" s="52" t="n">
+        <x:f>'Riding comparison'!P31</x:f>
+        <x:v>22379</x:v>
+      </x:c>
+      <x:c r="N31" s="53" t="n">
+        <x:f>H31-B31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O31" s="53" t="n">
+        <x:f>I31-C31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P31" s="53" t="n">
+        <x:f>J31-D31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q31" s="53" t="n">
+        <x:f>K31-E31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R31" s="53" t="n">
+        <x:f>L31-F31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S31" s="53" t="n">
+        <x:f>M31-G31</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T31" t="str">
+        <x:f>IF(COUNTIF(N31:S31,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U31" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V31" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="19" customHeight="1">
+      <x:c r="A32" t="str">
+        <x:v>Kelowna-Lake Country-Coldstream</x:v>
+      </x:c>
+      <x:c r="B32" s="51" t="n">
+        <x:v>7255</x:v>
+      </x:c>
+      <x:c r="C32" s="51" t="n">
+        <x:v>10637</x:v>
+      </x:c>
+      <x:c r="D32" s="51" t="n">
+        <x:v>1823</x:v>
+      </x:c>
+      <x:c r="E32" s="51" t="n">
+        <x:v>2532</x:v>
+      </x:c>
+      <x:c r="F32" s="51" t="n">
+        <x:v>22247</x:v>
+      </x:c>
+      <x:c r="G32" s="51" t="n">
+        <x:v>22289</x:v>
+      </x:c>
+      <x:c r="H32" s="52" t="n">
+        <x:f>'Riding comparison'!K32</x:f>
+        <x:v>7255</x:v>
+      </x:c>
+      <x:c r="I32" s="52" t="n">
+        <x:f>'Riding comparison'!L32</x:f>
+        <x:v>10637</x:v>
+      </x:c>
+      <x:c r="J32" s="52" t="n">
+        <x:f>'Riding comparison'!M32</x:f>
+        <x:v>1823</x:v>
+      </x:c>
+      <x:c r="K32" s="52" t="n">
+        <x:f>'Riding comparison'!N32</x:f>
+        <x:v>2532</x:v>
+      </x:c>
+      <x:c r="L32" s="52" t="n">
+        <x:f>'Riding comparison'!O32</x:f>
+        <x:v>22247</x:v>
+      </x:c>
+      <x:c r="M32" s="52" t="n">
+        <x:f>'Riding comparison'!P32</x:f>
+        <x:v>22289</x:v>
+      </x:c>
+      <x:c r="N32" s="53" t="n">
+        <x:f>H32-B32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" s="53" t="n">
+        <x:f>I32-C32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P32" s="53" t="n">
+        <x:f>J32-D32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q32" s="53" t="n">
+        <x:f>K32-E32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R32" s="53" t="n">
+        <x:f>L32-F32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S32" s="53" t="n">
+        <x:f>M32-G32</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T32" t="str">
+        <x:f>IF(COUNTIF(N32:S32,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U32" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V32" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="19" customHeight="1">
+      <x:c r="A33" t="str">
+        <x:v>Kelowna-Mission</x:v>
+      </x:c>
+      <x:c r="B33" s="51" t="n">
+        <x:v>6427</x:v>
+      </x:c>
+      <x:c r="C33" s="51" t="n">
+        <x:v>13590</x:v>
+      </x:c>
+      <x:c r="D33" s="51" t="n">
+        <x:v>2354</x:v>
+      </x:c>
+      <x:c r="E33" s="51" t="n">
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="F33" s="51" t="n">
+        <x:v>23128</x:v>
+      </x:c>
+      <x:c r="G33" s="51" t="n">
+        <x:v>23159</x:v>
+      </x:c>
+      <x:c r="H33" s="52" t="n">
+        <x:f>'Riding comparison'!K33</x:f>
+        <x:v>6427</x:v>
+      </x:c>
+      <x:c r="I33" s="52" t="n">
+        <x:f>'Riding comparison'!L33</x:f>
+        <x:v>13590</x:v>
+      </x:c>
+      <x:c r="J33" s="52" t="n">
+        <x:f>'Riding comparison'!M33</x:f>
+        <x:v>2354</x:v>
+      </x:c>
+      <x:c r="K33" s="52" t="n">
+        <x:f>'Riding comparison'!N33</x:f>
+        <x:v>757</x:v>
+      </x:c>
+      <x:c r="L33" s="52" t="n">
+        <x:f>'Riding comparison'!O33</x:f>
+        <x:v>23128</x:v>
+      </x:c>
+      <x:c r="M33" s="52" t="n">
+        <x:f>'Riding comparison'!P33</x:f>
+        <x:v>23159</x:v>
+      </x:c>
+      <x:c r="N33" s="53" t="n">
+        <x:f>H33-B33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O33" s="53" t="n">
+        <x:f>I33-C33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P33" s="53" t="n">
+        <x:f>J33-D33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q33" s="53" t="n">
+        <x:f>K33-E33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R33" s="53" t="n">
+        <x:f>L33-F33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S33" s="53" t="n">
+        <x:f>M33-G33</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T33" t="str">
+        <x:f>IF(COUNTIF(N33:S33,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U33" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V33" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="19" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>Kootenay Central</x:v>
+      </x:c>
+      <x:c r="B34" s="51" t="n">
+        <x:v>7618</x:v>
+      </x:c>
+      <x:c r="C34" s="51" t="n">
+        <x:v>7151</x:v>
+      </x:c>
+      <x:c r="D34" s="51" t="n">
+        <x:v>3779</x:v>
+      </x:c>
+      <x:c r="E34" s="51" t="n">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="F34" s="51" t="n">
+        <x:v>19278</x:v>
+      </x:c>
+      <x:c r="G34" s="51" t="n">
+        <x:v>19327</x:v>
+      </x:c>
+      <x:c r="H34" s="52" t="n">
+        <x:f>'Riding comparison'!K34</x:f>
+        <x:v>7618</x:v>
+      </x:c>
+      <x:c r="I34" s="52" t="n">
+        <x:f>'Riding comparison'!L34</x:f>
+        <x:v>7151</x:v>
+      </x:c>
+      <x:c r="J34" s="52" t="n">
+        <x:f>'Riding comparison'!M34</x:f>
+        <x:v>3779</x:v>
+      </x:c>
+      <x:c r="K34" s="52" t="n">
+        <x:f>'Riding comparison'!N34</x:f>
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="L34" s="52" t="n">
+        <x:f>'Riding comparison'!O34</x:f>
+        <x:v>19278</x:v>
+      </x:c>
+      <x:c r="M34" s="52" t="n">
+        <x:f>'Riding comparison'!P34</x:f>
+        <x:v>19327</x:v>
+      </x:c>
+      <x:c r="N34" s="53" t="n">
+        <x:f>H34-B34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" s="53" t="n">
+        <x:f>I34-C34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P34" s="53" t="n">
+        <x:f>J34-D34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q34" s="53" t="n">
+        <x:f>K34-E34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R34" s="53" t="n">
+        <x:f>L34-F34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S34" s="53" t="n">
+        <x:f>M34-G34</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T34" t="str">
+        <x:f>IF(COUNTIF(N34:S34,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U34" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V34" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="19" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>Kootenay-Monashee</x:v>
+      </x:c>
+      <x:c r="B35" s="51" t="n">
+        <x:v>8526</x:v>
+      </x:c>
+      <x:c r="C35" s="51" t="n">
+        <x:v>6632</x:v>
+      </x:c>
+      <x:c r="D35" s="51" t="n">
+        <x:v>1822</x:v>
+      </x:c>
+      <x:c r="E35" s="51" t="n">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="F35" s="51" t="n">
+        <x:v>17751</x:v>
+      </x:c>
+      <x:c r="G35" s="51" t="n">
+        <x:v>17774</x:v>
+      </x:c>
+      <x:c r="H35" s="52" t="n">
+        <x:f>'Riding comparison'!K35</x:f>
+        <x:v>8526</x:v>
+      </x:c>
+      <x:c r="I35" s="52" t="n">
+        <x:f>'Riding comparison'!L35</x:f>
+        <x:v>6632</x:v>
+      </x:c>
+      <x:c r="J35" s="52" t="n">
+        <x:f>'Riding comparison'!M35</x:f>
+        <x:v>1822</x:v>
+      </x:c>
+      <x:c r="K35" s="52" t="n">
+        <x:f>'Riding comparison'!N35</x:f>
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="L35" s="52" t="n">
+        <x:f>'Riding comparison'!O35</x:f>
+        <x:v>17751</x:v>
+      </x:c>
+      <x:c r="M35" s="52" t="n">
+        <x:f>'Riding comparison'!P35</x:f>
+        <x:v>17774</x:v>
+      </x:c>
+      <x:c r="N35" s="53" t="n">
+        <x:f>H35-B35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" s="53" t="n">
+        <x:f>I35-C35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P35" s="53" t="n">
+        <x:f>J35-D35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q35" s="53" t="n">
+        <x:f>K35-E35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R35" s="53" t="n">
+        <x:f>L35-F35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S35" s="53" t="n">
+        <x:f>M35-G35</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T35" t="str">
+        <x:f>IF(COUNTIF(N35:S35,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U35" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V35" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="19" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>Kootenay-Rockies</x:v>
+      </x:c>
+      <x:c r="B36" s="51" t="n">
+        <x:v>4404</x:v>
+      </x:c>
+      <x:c r="C36" s="51" t="n">
+        <x:v>9130</x:v>
+      </x:c>
+      <x:c r="D36" s="51" t="n">
+        <x:v>1165</x:v>
+      </x:c>
+      <x:c r="E36" s="51" t="n">
+        <x:v>1513</x:v>
+      </x:c>
+      <x:c r="F36" s="51" t="n">
+        <x:v>16212</x:v>
+      </x:c>
+      <x:c r="G36" s="51" t="n">
+        <x:v>16239</x:v>
+      </x:c>
+      <x:c r="H36" s="52" t="n">
+        <x:f>'Riding comparison'!K36</x:f>
+        <x:v>4404</x:v>
+      </x:c>
+      <x:c r="I36" s="52" t="n">
+        <x:f>'Riding comparison'!L36</x:f>
+        <x:v>9130</x:v>
+      </x:c>
+      <x:c r="J36" s="52" t="n">
+        <x:f>'Riding comparison'!M36</x:f>
+        <x:v>1165</x:v>
+      </x:c>
+      <x:c r="K36" s="52" t="n">
+        <x:f>'Riding comparison'!N36</x:f>
+        <x:v>1513</x:v>
+      </x:c>
+      <x:c r="L36" s="52" t="n">
+        <x:f>'Riding comparison'!O36</x:f>
+        <x:v>16212</x:v>
+      </x:c>
+      <x:c r="M36" s="52" t="n">
+        <x:f>'Riding comparison'!P36</x:f>
+        <x:v>16239</x:v>
+      </x:c>
+      <x:c r="N36" s="53" t="n">
+        <x:f>H36-B36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" s="53" t="n">
+        <x:f>I36-C36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P36" s="53" t="n">
+        <x:f>J36-D36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q36" s="53" t="n">
+        <x:f>K36-E36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R36" s="53" t="n">
+        <x:f>L36-F36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S36" s="53" t="n">
+        <x:f>M36-G36</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T36" t="str">
+        <x:f>IF(COUNTIF(N36:S36,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U36" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V36" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="19" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>Ladysmith-Oceanside</x:v>
+      </x:c>
+      <x:c r="B37" s="51" t="n">
+        <x:v>13380</x:v>
+      </x:c>
+      <x:c r="C37" s="51" t="n">
+        <x:v>13367</x:v>
+      </x:c>
+      <x:c r="D37" s="51" t="n">
+        <x:v>3365</x:v>
+      </x:c>
+      <x:c r="E37" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F37" s="51" t="n">
+        <x:v>30112</x:v>
+      </x:c>
+      <x:c r="G37" s="51" t="n">
+        <x:v>30155</x:v>
+      </x:c>
+      <x:c r="H37" s="52" t="n">
+        <x:f>'Riding comparison'!K37</x:f>
+        <x:v>13380</x:v>
+      </x:c>
+      <x:c r="I37" s="52" t="n">
+        <x:f>'Riding comparison'!L37</x:f>
+        <x:v>13367</x:v>
+      </x:c>
+      <x:c r="J37" s="52" t="n">
+        <x:f>'Riding comparison'!M37</x:f>
+        <x:v>3365</x:v>
+      </x:c>
+      <x:c r="K37" s="52" t="n">
+        <x:f>'Riding comparison'!N37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37" s="52" t="n">
+        <x:f>'Riding comparison'!O37</x:f>
+        <x:v>30112</x:v>
+      </x:c>
+      <x:c r="M37" s="52" t="n">
+        <x:f>'Riding comparison'!P37</x:f>
+        <x:v>30155</x:v>
+      </x:c>
+      <x:c r="N37" s="53" t="n">
+        <x:f>H37-B37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O37" s="53" t="n">
+        <x:f>I37-C37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P37" s="53" t="n">
+        <x:f>J37-D37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q37" s="53" t="n">
+        <x:f>K37-E37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R37" s="53" t="n">
+        <x:f>L37-F37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S37" s="53" t="n">
+        <x:f>M37-G37</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T37" t="str">
+        <x:f>IF(COUNTIF(N37:S37,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U37" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V37" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="19" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>Langford-Highlands</x:v>
+      </x:c>
+      <x:c r="B38" s="51" t="n">
+        <x:v>8737</x:v>
+      </x:c>
+      <x:c r="C38" s="51" t="n">
+        <x:v>7588</x:v>
+      </x:c>
+      <x:c r="D38" s="51" t="n">
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="E38" s="51" t="n">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="F38" s="51" t="n">
+        <x:v>19519</x:v>
+      </x:c>
+      <x:c r="G38" s="51" t="n">
+        <x:v>19536</x:v>
+      </x:c>
+      <x:c r="H38" s="52" t="n">
+        <x:f>'Riding comparison'!K38</x:f>
+        <x:v>8737</x:v>
+      </x:c>
+      <x:c r="I38" s="52" t="n">
+        <x:f>'Riding comparison'!L38</x:f>
+        <x:v>7588</x:v>
+      </x:c>
+      <x:c r="J38" s="52" t="n">
+        <x:f>'Riding comparison'!M38</x:f>
+        <x:v>2550</x:v>
+      </x:c>
+      <x:c r="K38" s="52" t="n">
+        <x:f>'Riding comparison'!N38</x:f>
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="L38" s="52" t="n">
+        <x:f>'Riding comparison'!O38</x:f>
+        <x:v>19519</x:v>
+      </x:c>
+      <x:c r="M38" s="52" t="n">
+        <x:f>'Riding comparison'!P38</x:f>
+        <x:v>19536</x:v>
+      </x:c>
+      <x:c r="N38" s="53" t="n">
+        <x:f>H38-B38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O38" s="53" t="n">
+        <x:f>I38-C38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P38" s="53" t="n">
+        <x:f>J38-D38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q38" s="53" t="n">
+        <x:f>K38-E38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R38" s="53" t="n">
+        <x:f>L38-F38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S38" s="53" t="n">
+        <x:f>M38-G38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T38" t="str">
+        <x:f>IF(COUNTIF(N38:S38,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U38" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V38" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="19" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>Langley-Abbotsford</x:v>
+      </x:c>
+      <x:c r="B39" s="51" t="n">
+        <x:v>5199</x:v>
+      </x:c>
+      <x:c r="C39" s="51" t="n">
+        <x:v>13474</x:v>
+      </x:c>
+      <x:c r="D39" s="51" t="n">
+        <x:v>1874</x:v>
+      </x:c>
+      <x:c r="E39" s="51" t="n">
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c r="F39" s="51" t="n">
+        <x:v>21950</x:v>
+      </x:c>
+      <x:c r="G39" s="51" t="n">
+        <x:v>22007</x:v>
+      </x:c>
+      <x:c r="H39" s="52" t="n">
+        <x:f>'Riding comparison'!K39</x:f>
+        <x:v>5199</x:v>
+      </x:c>
+      <x:c r="I39" s="52" t="n">
+        <x:f>'Riding comparison'!L39</x:f>
+        <x:v>13474</x:v>
+      </x:c>
+      <x:c r="J39" s="52" t="n">
+        <x:f>'Riding comparison'!M39</x:f>
+        <x:v>1874</x:v>
+      </x:c>
+      <x:c r="K39" s="52" t="n">
+        <x:f>'Riding comparison'!N39</x:f>
+        <x:v>1403</x:v>
+      </x:c>
+      <x:c r="L39" s="52" t="n">
+        <x:f>'Riding comparison'!O39</x:f>
+        <x:v>21950</x:v>
+      </x:c>
+      <x:c r="M39" s="52" t="n">
+        <x:f>'Riding comparison'!P39</x:f>
+        <x:v>22007</x:v>
+      </x:c>
+      <x:c r="N39" s="53" t="n">
+        <x:f>H39-B39</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" s="53" t="n">
+        <x:f>I39-C39</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P39" s="53" t="n">
+        <x:f>J39-D39</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q39" s="53" t="n">
+        <x:f>K39-E39</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R39" s="53" t="n">
+        <x:f>L39-F39</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S39" s="53" t="n">
+        <x:f>M39-G39</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T39" t="str">
+        <x:f>IF(COUNTIF(N39:S39,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U39" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V39" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="19" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>Langley-Walnut Grove</x:v>
+      </x:c>
+      <x:c r="B40" s="51" t="n">
+        <x:v>6846</x:v>
+      </x:c>
+      <x:c r="C40" s="51" t="n">
+        <x:v>12310</x:v>
+      </x:c>
+      <x:c r="D40" s="51" t="n">
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="E40" s="51" t="n">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="F40" s="51" t="n">
+        <x:v>21660</x:v>
+      </x:c>
+      <x:c r="G40" s="51" t="n">
+        <x:v>21678</x:v>
+      </x:c>
+      <x:c r="H40" s="52" t="n">
+        <x:f>'Riding comparison'!K40</x:f>
+        <x:v>6846</x:v>
+      </x:c>
+      <x:c r="I40" s="52" t="n">
+        <x:f>'Riding comparison'!L40</x:f>
+        <x:v>12310</x:v>
+      </x:c>
+      <x:c r="J40" s="52" t="n">
+        <x:f>'Riding comparison'!M40</x:f>
+        <x:v>1560</x:v>
+      </x:c>
+      <x:c r="K40" s="52" t="n">
+        <x:f>'Riding comparison'!N40</x:f>
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="L40" s="52" t="n">
+        <x:f>'Riding comparison'!O40</x:f>
+        <x:v>21660</x:v>
+      </x:c>
+      <x:c r="M40" s="52" t="n">
+        <x:f>'Riding comparison'!P40</x:f>
+        <x:v>21678</x:v>
+      </x:c>
+      <x:c r="N40" s="53" t="n">
+        <x:f>H40-B40</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" s="53" t="n">
+        <x:f>I40-C40</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P40" s="53" t="n">
+        <x:f>J40-D40</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q40" s="53" t="n">
+        <x:f>K40-E40</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R40" s="53" t="n">
+        <x:f>L40-F40</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S40" s="53" t="n">
+        <x:f>M40-G40</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T40" t="str">
+        <x:f>IF(COUNTIF(N40:S40,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U40" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V40" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="19" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>Langley-Willowbrook</x:v>
+      </x:c>
+      <x:c r="B41" s="51" t="n">
+        <x:v>6834</x:v>
+      </x:c>
+      <x:c r="C41" s="51" t="n">
+        <x:v>9978</x:v>
+      </x:c>
+      <x:c r="D41" s="51" t="n">
+        <x:v>1486</x:v>
+      </x:c>
+      <x:c r="E41" s="51" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="F41" s="51" t="n">
+        <x:v>18998</x:v>
+      </x:c>
+      <x:c r="G41" s="51" t="n">
+        <x:v>19039</x:v>
+      </x:c>
+      <x:c r="H41" s="52" t="n">
+        <x:f>'Riding comparison'!K41</x:f>
+        <x:v>6834</x:v>
+      </x:c>
+      <x:c r="I41" s="52" t="n">
+        <x:f>'Riding comparison'!L41</x:f>
+        <x:v>9978</x:v>
+      </x:c>
+      <x:c r="J41" s="52" t="n">
+        <x:f>'Riding comparison'!M41</x:f>
+        <x:v>1486</x:v>
+      </x:c>
+      <x:c r="K41" s="52" t="n">
+        <x:f>'Riding comparison'!N41</x:f>
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="L41" s="52" t="n">
+        <x:f>'Riding comparison'!O41</x:f>
+        <x:v>18998</x:v>
+      </x:c>
+      <x:c r="M41" s="52" t="n">
+        <x:f>'Riding comparison'!P41</x:f>
+        <x:v>19039</x:v>
+      </x:c>
+      <x:c r="N41" s="53" t="n">
+        <x:f>H41-B41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O41" s="53" t="n">
+        <x:f>I41-C41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P41" s="53" t="n">
+        <x:f>J41-D41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q41" s="53" t="n">
+        <x:f>K41-E41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R41" s="53" t="n">
+        <x:f>L41-F41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S41" s="53" t="n">
+        <x:f>M41-G41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T41" t="str">
+        <x:f>IF(COUNTIF(N41:S41,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U41" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V41" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="19" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>Maple Ridge East</x:v>
+      </x:c>
+      <x:c r="B42" s="51" t="n">
+        <x:v>8398</x:v>
+      </x:c>
+      <x:c r="C42" s="51" t="n">
+        <x:v>12061</x:v>
+      </x:c>
+      <x:c r="D42" s="51" t="n">
+        <x:v>1711</x:v>
+      </x:c>
+      <x:c r="E42" s="51" t="n">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="F42" s="51" t="n">
+        <x:v>22501</x:v>
+      </x:c>
+      <x:c r="G42" s="51" t="n">
+        <x:v>22541</x:v>
+      </x:c>
+      <x:c r="H42" s="52" t="n">
+        <x:f>'Riding comparison'!K42</x:f>
+        <x:v>8398</x:v>
+      </x:c>
+      <x:c r="I42" s="52" t="n">
+        <x:f>'Riding comparison'!L42</x:f>
+        <x:v>12061</x:v>
+      </x:c>
+      <x:c r="J42" s="52" t="n">
+        <x:f>'Riding comparison'!M42</x:f>
+        <x:v>1711</x:v>
+      </x:c>
+      <x:c r="K42" s="52" t="n">
+        <x:f>'Riding comparison'!N42</x:f>
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="L42" s="52" t="n">
+        <x:f>'Riding comparison'!O42</x:f>
+        <x:v>22501</x:v>
+      </x:c>
+      <x:c r="M42" s="52" t="n">
+        <x:f>'Riding comparison'!P42</x:f>
+        <x:v>22541</x:v>
+      </x:c>
+      <x:c r="N42" s="53" t="n">
+        <x:f>H42-B42</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O42" s="53" t="n">
+        <x:f>I42-C42</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P42" s="53" t="n">
+        <x:f>J42-D42</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q42" s="53" t="n">
+        <x:f>K42-E42</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R42" s="53" t="n">
+        <x:f>L42-F42</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S42" s="53" t="n">
+        <x:f>M42-G42</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T42" t="str">
+        <x:f>IF(COUNTIF(N42:S42,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U42" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V42" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="19" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>Maple Ridge-Pitt Meadows</x:v>
+      </x:c>
+      <x:c r="B43" s="51" t="n">
+        <x:v>9987</x:v>
+      </x:c>
+      <x:c r="C43" s="51" t="n">
+        <x:v>10837</x:v>
+      </x:c>
+      <x:c r="D43" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E43" s="51" t="n">
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="F43" s="51" t="n">
+        <x:v>22419</x:v>
+      </x:c>
+      <x:c r="G43" s="51" t="n">
+        <x:v>22464</x:v>
+      </x:c>
+      <x:c r="H43" s="52" t="n">
+        <x:f>'Riding comparison'!K43</x:f>
+        <x:v>9987</x:v>
+      </x:c>
+      <x:c r="I43" s="52" t="n">
+        <x:f>'Riding comparison'!L43</x:f>
+        <x:v>10837</x:v>
+      </x:c>
+      <x:c r="J43" s="52" t="n">
+        <x:f>'Riding comparison'!M43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43" s="52" t="n">
+        <x:f>'Riding comparison'!N43</x:f>
+        <x:v>1595</x:v>
+      </x:c>
+      <x:c r="L43" s="52" t="n">
+        <x:f>'Riding comparison'!O43</x:f>
+        <x:v>22419</x:v>
+      </x:c>
+      <x:c r="M43" s="52" t="n">
+        <x:f>'Riding comparison'!P43</x:f>
+        <x:v>22464</x:v>
+      </x:c>
+      <x:c r="N43" s="53" t="n">
+        <x:f>H43-B43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" s="53" t="n">
+        <x:f>I43-C43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P43" s="53" t="n">
+        <x:f>J43-D43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q43" s="53" t="n">
+        <x:f>K43-E43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R43" s="53" t="n">
+        <x:f>L43-F43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S43" s="53" t="n">
+        <x:f>M43-G43</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T43" t="str">
+        <x:f>IF(COUNTIF(N43:S43,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U43" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V43" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="19" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>Mid Island-Pacific Rim</x:v>
+      </x:c>
+      <x:c r="B44" s="51" t="n">
+        <x:v>11916</x:v>
+      </x:c>
+      <x:c r="C44" s="51" t="n">
+        <x:v>10301</x:v>
+      </x:c>
+      <x:c r="D44" s="51" t="n">
+        <x:v>3203</x:v>
+      </x:c>
+      <x:c r="E44" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F44" s="51" t="n">
+        <x:v>25420</x:v>
+      </x:c>
+      <x:c r="G44" s="51" t="n">
+        <x:v>25462</x:v>
+      </x:c>
+      <x:c r="H44" s="52" t="n">
+        <x:f>'Riding comparison'!K44</x:f>
+        <x:v>11916</x:v>
+      </x:c>
+      <x:c r="I44" s="52" t="n">
+        <x:f>'Riding comparison'!L44</x:f>
+        <x:v>10301</x:v>
+      </x:c>
+      <x:c r="J44" s="52" t="n">
+        <x:f>'Riding comparison'!M44</x:f>
+        <x:v>3203</x:v>
+      </x:c>
+      <x:c r="K44" s="52" t="n">
+        <x:f>'Riding comparison'!N44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44" s="52" t="n">
+        <x:f>'Riding comparison'!O44</x:f>
+        <x:v>25420</x:v>
+      </x:c>
+      <x:c r="M44" s="52" t="n">
+        <x:f>'Riding comparison'!P44</x:f>
+        <x:v>25462</x:v>
+      </x:c>
+      <x:c r="N44" s="53" t="n">
+        <x:f>H44-B44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O44" s="53" t="n">
+        <x:f>I44-C44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P44" s="53" t="n">
+        <x:f>J44-D44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q44" s="53" t="n">
+        <x:f>K44-E44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R44" s="53" t="n">
+        <x:f>L44-F44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S44" s="53" t="n">
+        <x:f>M44-G44</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T44" t="str">
+        <x:f>IF(COUNTIF(N44:S44,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U44" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V44" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="19" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>Nanaimo-Gabriola Island</x:v>
+      </x:c>
+      <x:c r="B45" s="51" t="n">
+        <x:v>11079</x:v>
+      </x:c>
+      <x:c r="C45" s="51" t="n">
+        <x:v>8262</x:v>
+      </x:c>
+      <x:c r="D45" s="51" t="n">
+        <x:v>3692</x:v>
+      </x:c>
+      <x:c r="E45" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F45" s="51" t="n">
+        <x:v>23033</x:v>
+      </x:c>
+      <x:c r="G45" s="51" t="n">
+        <x:v>23077</x:v>
+      </x:c>
+      <x:c r="H45" s="52" t="n">
+        <x:f>'Riding comparison'!K45</x:f>
+        <x:v>11079</x:v>
+      </x:c>
+      <x:c r="I45" s="52" t="n">
+        <x:f>'Riding comparison'!L45</x:f>
+        <x:v>8262</x:v>
+      </x:c>
+      <x:c r="J45" s="52" t="n">
+        <x:f>'Riding comparison'!M45</x:f>
+        <x:v>3692</x:v>
+      </x:c>
+      <x:c r="K45" s="52" t="n">
+        <x:f>'Riding comparison'!N45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L45" s="52" t="n">
+        <x:f>'Riding comparison'!O45</x:f>
+        <x:v>23033</x:v>
+      </x:c>
+      <x:c r="M45" s="52" t="n">
+        <x:f>'Riding comparison'!P45</x:f>
+        <x:v>23077</x:v>
+      </x:c>
+      <x:c r="N45" s="53" t="n">
+        <x:f>H45-B45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O45" s="53" t="n">
+        <x:f>I45-C45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P45" s="53" t="n">
+        <x:f>J45-D45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q45" s="53" t="n">
+        <x:f>K45-E45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R45" s="53" t="n">
+        <x:f>L45-F45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S45" s="53" t="n">
+        <x:f>M45-G45</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T45" t="str">
+        <x:f>IF(COUNTIF(N45:S45,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U45" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V45" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="19" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>Nanaimo-Lantzville</x:v>
+      </x:c>
+      <x:c r="B46" s="51" t="n">
+        <x:v>11567</x:v>
+      </x:c>
+      <x:c r="C46" s="51" t="n">
+        <x:v>10701</x:v>
+      </x:c>
+      <x:c r="D46" s="51" t="n">
+        <x:v>2448</x:v>
+      </x:c>
+      <x:c r="E46" s="51" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F46" s="51" t="n">
+        <x:v>24792</x:v>
+      </x:c>
+      <x:c r="G46" s="51" t="n">
+        <x:v>24830</x:v>
+      </x:c>
+      <x:c r="H46" s="52" t="n">
+        <x:f>'Riding comparison'!K46</x:f>
+        <x:v>11567</x:v>
+      </x:c>
+      <x:c r="I46" s="52" t="n">
+        <x:f>'Riding comparison'!L46</x:f>
+        <x:v>10701</x:v>
+      </x:c>
+      <x:c r="J46" s="52" t="n">
+        <x:f>'Riding comparison'!M46</x:f>
+        <x:v>2448</x:v>
+      </x:c>
+      <x:c r="K46" s="52" t="n">
+        <x:f>'Riding comparison'!N46</x:f>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="L46" s="52" t="n">
+        <x:f>'Riding comparison'!O46</x:f>
+        <x:v>24792</x:v>
+      </x:c>
+      <x:c r="M46" s="52" t="n">
+        <x:f>'Riding comparison'!P46</x:f>
+        <x:v>24830</x:v>
+      </x:c>
+      <x:c r="N46" s="53" t="n">
+        <x:f>H46-B46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O46" s="53" t="n">
+        <x:f>I46-C46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P46" s="53" t="n">
+        <x:f>J46-D46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q46" s="53" t="n">
+        <x:f>K46-E46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R46" s="53" t="n">
+        <x:f>L46-F46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S46" s="53" t="n">
+        <x:f>M46-G46</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T46" t="str">
+        <x:f>IF(COUNTIF(N46:S46,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U46" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V46" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="19" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>Nechako Lakes</x:v>
+      </x:c>
+      <x:c r="B47" s="51" t="n">
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="C47" s="51" t="n">
+        <x:v>5954</x:v>
+      </x:c>
+      <x:c r="D47" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E47" s="51" t="n">
+        <x:v>1219</x:v>
+      </x:c>
+      <x:c r="F47" s="51" t="n">
+        <x:v>9323</x:v>
+      </x:c>
+      <x:c r="G47" s="51" t="n">
+        <x:v>9337</x:v>
+      </x:c>
+      <x:c r="H47" s="52" t="n">
+        <x:f>'Riding comparison'!K47</x:f>
+        <x:v>2150</x:v>
+      </x:c>
+      <x:c r="I47" s="52" t="n">
+        <x:f>'Riding comparison'!L47</x:f>
+        <x:v>5954</x:v>
+      </x:c>
+      <x:c r="J47" s="52" t="n">
+        <x:f>'Riding comparison'!M47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K47" s="52" t="n">
+        <x:f>'Riding comparison'!N47</x:f>
+        <x:v>1219</x:v>
+      </x:c>
+      <x:c r="L47" s="52" t="n">
+        <x:f>'Riding comparison'!O47</x:f>
+        <x:v>9323</x:v>
+      </x:c>
+      <x:c r="M47" s="52" t="n">
+        <x:f>'Riding comparison'!P47</x:f>
+        <x:v>9337</x:v>
+      </x:c>
+      <x:c r="N47" s="53" t="n">
+        <x:f>H47-B47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O47" s="53" t="n">
+        <x:f>I47-C47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P47" s="53" t="n">
+        <x:f>J47-D47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q47" s="53" t="n">
+        <x:f>K47-E47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R47" s="53" t="n">
+        <x:f>L47-F47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S47" s="53" t="n">
+        <x:f>M47-G47</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T47" t="str">
+        <x:f>IF(COUNTIF(N47:S47,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U47" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V47" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="19" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>New Westminster-Coquitlam</x:v>
+      </x:c>
+      <x:c r="B48" s="51" t="n">
+        <x:v>9289</x:v>
+      </x:c>
+      <x:c r="C48" s="51" t="n">
+        <x:v>6315</x:v>
+      </x:c>
+      <x:c r="D48" s="51" t="n">
+        <x:v>2838</x:v>
+      </x:c>
+      <x:c r="E48" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F48" s="51" t="n">
+        <x:v>18442</x:v>
+      </x:c>
+      <x:c r="G48" s="51" t="n">
+        <x:v>18536</x:v>
+      </x:c>
+      <x:c r="H48" s="52" t="n">
+        <x:f>'Riding comparison'!K48</x:f>
+        <x:v>9289</x:v>
+      </x:c>
+      <x:c r="I48" s="52" t="n">
+        <x:f>'Riding comparison'!L48</x:f>
+        <x:v>6315</x:v>
+      </x:c>
+      <x:c r="J48" s="52" t="n">
+        <x:f>'Riding comparison'!M48</x:f>
+        <x:v>2838</x:v>
+      </x:c>
+      <x:c r="K48" s="52" t="n">
+        <x:f>'Riding comparison'!N48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L48" s="52" t="n">
+        <x:f>'Riding comparison'!O48</x:f>
+        <x:v>18442</x:v>
+      </x:c>
+      <x:c r="M48" s="52" t="n">
+        <x:f>'Riding comparison'!P48</x:f>
+        <x:v>18536</x:v>
+      </x:c>
+      <x:c r="N48" s="53" t="n">
+        <x:f>H48-B48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O48" s="53" t="n">
+        <x:f>I48-C48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P48" s="53" t="n">
+        <x:f>J48-D48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q48" s="53" t="n">
+        <x:f>K48-E48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R48" s="53" t="n">
+        <x:f>L48-F48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S48" s="53" t="n">
+        <x:f>M48-G48</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T48" t="str">
+        <x:f>IF(COUNTIF(N48:S48,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U48" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V48" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="19" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>North Coast-Haida Gwaii</x:v>
+      </x:c>
+      <x:c r="B49" s="51" t="n">
+        <x:v>4051</x:v>
+      </x:c>
+      <x:c r="C49" s="51" t="n">
+        <x:v>1901</x:v>
+      </x:c>
+      <x:c r="D49" s="51" t="n">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="E49" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F49" s="51" t="n">
+        <x:v>6593</x:v>
+      </x:c>
+      <x:c r="G49" s="51" t="n">
+        <x:v>6621</x:v>
+      </x:c>
+      <x:c r="H49" s="52" t="n">
+        <x:f>'Riding comparison'!K49</x:f>
+        <x:v>4051</x:v>
+      </x:c>
+      <x:c r="I49" s="52" t="n">
+        <x:f>'Riding comparison'!L49</x:f>
+        <x:v>1901</x:v>
+      </x:c>
+      <x:c r="J49" s="52" t="n">
+        <x:f>'Riding comparison'!M49</x:f>
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="K49" s="52" t="n">
+        <x:f>'Riding comparison'!N49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" s="52" t="n">
+        <x:f>'Riding comparison'!O49</x:f>
+        <x:v>6593</x:v>
+      </x:c>
+      <x:c r="M49" s="52" t="n">
+        <x:f>'Riding comparison'!P49</x:f>
+        <x:v>6621</x:v>
+      </x:c>
+      <x:c r="N49" s="53" t="n">
+        <x:f>H49-B49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O49" s="53" t="n">
+        <x:f>I49-C49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P49" s="53" t="n">
+        <x:f>J49-D49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q49" s="53" t="n">
+        <x:f>K49-E49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R49" s="53" t="n">
+        <x:f>L49-F49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S49" s="53" t="n">
+        <x:f>M49-G49</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T49" t="str">
+        <x:f>IF(COUNTIF(N49:S49,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U49" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V49" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="19" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>North Island</x:v>
+      </x:c>
+      <x:c r="B50" s="51" t="n">
+        <x:v>10695</x:v>
+      </x:c>
+      <x:c r="C50" s="51" t="n">
+        <x:v>12071</x:v>
+      </x:c>
+      <x:c r="D50" s="51" t="n">
+        <x:v>2076</x:v>
+      </x:c>
+      <x:c r="E50" s="51" t="n">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="F50" s="51" t="n">
+        <x:v>25255</x:v>
+      </x:c>
+      <x:c r="G50" s="51" t="n">
+        <x:v>25279</x:v>
+      </x:c>
+      <x:c r="H50" s="52" t="n">
+        <x:f>'Riding comparison'!K50</x:f>
+        <x:v>10695</x:v>
+      </x:c>
+      <x:c r="I50" s="52" t="n">
+        <x:f>'Riding comparison'!L50</x:f>
+        <x:v>12071</x:v>
+      </x:c>
+      <x:c r="J50" s="52" t="n">
+        <x:f>'Riding comparison'!M50</x:f>
+        <x:v>2076</x:v>
+      </x:c>
+      <x:c r="K50" s="52" t="n">
+        <x:f>'Riding comparison'!N50</x:f>
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="L50" s="52" t="n">
+        <x:f>'Riding comparison'!O50</x:f>
+        <x:v>25255</x:v>
+      </x:c>
+      <x:c r="M50" s="52" t="n">
+        <x:f>'Riding comparison'!P50</x:f>
+        <x:v>25279</x:v>
+      </x:c>
+      <x:c r="N50" s="53" t="n">
+        <x:f>H50-B50</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O50" s="53" t="n">
+        <x:f>I50-C50</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P50" s="53" t="n">
+        <x:f>J50-D50</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q50" s="53" t="n">
+        <x:f>K50-E50</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R50" s="53" t="n">
+        <x:f>L50-F50</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S50" s="53" t="n">
+        <x:f>M50-G50</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T50" t="str">
+        <x:f>IF(COUNTIF(N50:S50,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U50" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V50" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="19" customHeight="1">
+      <x:c r="A51" t="str">
+        <x:v>North Vancouver-Lonsdale</x:v>
+      </x:c>
+      <x:c r="B51" s="51" t="n">
+        <x:v>10314</x:v>
+      </x:c>
+      <x:c r="C51" s="51" t="n">
+        <x:v>9121</x:v>
+      </x:c>
+      <x:c r="D51" s="51" t="n">
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="E51" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F51" s="51" t="n">
+        <x:v>21937</x:v>
+      </x:c>
+      <x:c r="G51" s="51" t="n">
+        <x:v>21979</x:v>
+      </x:c>
+      <x:c r="H51" s="52" t="n">
+        <x:f>'Riding comparison'!K51</x:f>
+        <x:v>10314</x:v>
+      </x:c>
+      <x:c r="I51" s="52" t="n">
+        <x:f>'Riding comparison'!L51</x:f>
+        <x:v>9121</x:v>
+      </x:c>
+      <x:c r="J51" s="52" t="n">
+        <x:f>'Riding comparison'!M51</x:f>
+        <x:v>2502</x:v>
+      </x:c>
+      <x:c r="K51" s="52" t="n">
+        <x:f>'Riding comparison'!N51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" s="52" t="n">
+        <x:f>'Riding comparison'!O51</x:f>
+        <x:v>21937</x:v>
+      </x:c>
+      <x:c r="M51" s="52" t="n">
+        <x:f>'Riding comparison'!P51</x:f>
+        <x:v>21979</x:v>
+      </x:c>
+      <x:c r="N51" s="53" t="n">
+        <x:f>H51-B51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O51" s="53" t="n">
+        <x:f>I51-C51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P51" s="53" t="n">
+        <x:f>J51-D51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q51" s="53" t="n">
+        <x:f>K51-E51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R51" s="53" t="n">
+        <x:f>L51-F51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S51" s="53" t="n">
+        <x:f>M51-G51</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T51" t="str">
+        <x:f>IF(COUNTIF(N51:S51,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U51" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V51" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="19" customHeight="1">
+      <x:c r="A52" t="str">
+        <x:v>North Vancouver-Seymour</x:v>
+      </x:c>
+      <x:c r="B52" s="51" t="n">
+        <x:v>9825</x:v>
+      </x:c>
+      <x:c r="C52" s="51" t="n">
+        <x:v>12291</x:v>
+      </x:c>
+      <x:c r="D52" s="51" t="n">
+        <x:v>2825</x:v>
+      </x:c>
+      <x:c r="E52" s="51" t="n">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="F52" s="51" t="n">
+        <x:v>26255</x:v>
+      </x:c>
+      <x:c r="G52" s="51" t="n">
+        <x:v>26334</x:v>
+      </x:c>
+      <x:c r="H52" s="52" t="n">
+        <x:f>'Riding comparison'!K52</x:f>
+        <x:v>9825</x:v>
+      </x:c>
+      <x:c r="I52" s="52" t="n">
+        <x:f>'Riding comparison'!L52</x:f>
+        <x:v>12291</x:v>
+      </x:c>
+      <x:c r="J52" s="52" t="n">
+        <x:f>'Riding comparison'!M52</x:f>
+        <x:v>2825</x:v>
+      </x:c>
+      <x:c r="K52" s="52" t="n">
+        <x:f>'Riding comparison'!N52</x:f>
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="L52" s="52" t="n">
+        <x:f>'Riding comparison'!O52</x:f>
+        <x:v>26255</x:v>
+      </x:c>
+      <x:c r="M52" s="52" t="n">
+        <x:f>'Riding comparison'!P52</x:f>
+        <x:v>26334</x:v>
+      </x:c>
+      <x:c r="N52" s="53" t="n">
+        <x:f>H52-B52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O52" s="53" t="n">
+        <x:f>I52-C52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P52" s="53" t="n">
+        <x:f>J52-D52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q52" s="53" t="n">
+        <x:f>K52-E52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R52" s="53" t="n">
+        <x:f>L52-F52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S52" s="53" t="n">
+        <x:f>M52-G52</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T52" t="str">
+        <x:f>IF(COUNTIF(N52:S52,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U52" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V52" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="19" customHeight="1">
+      <x:c r="A53" t="str">
+        <x:v>Oak Bay-Gordon Head</x:v>
+      </x:c>
+      <x:c r="B53" s="51" t="n">
+        <x:v>9200</x:v>
+      </x:c>
+      <x:c r="C53" s="51" t="n">
+        <x:v>7599</x:v>
+      </x:c>
+      <x:c r="D53" s="51" t="n">
+        <x:v>5452</x:v>
+      </x:c>
+      <x:c r="E53" s="51" t="n">
+        <x:v>2590</x:v>
+      </x:c>
+      <x:c r="F53" s="51" t="n">
+        <x:v>24841</x:v>
+      </x:c>
+      <x:c r="G53" s="51" t="n">
+        <x:v>24871</x:v>
+      </x:c>
+      <x:c r="H53" s="52" t="n">
+        <x:f>'Riding comparison'!K53</x:f>
+        <x:v>9200</x:v>
+      </x:c>
+      <x:c r="I53" s="52" t="n">
+        <x:f>'Riding comparison'!L53</x:f>
+        <x:v>7599</x:v>
+      </x:c>
+      <x:c r="J53" s="52" t="n">
+        <x:f>'Riding comparison'!M53</x:f>
+        <x:v>5452</x:v>
+      </x:c>
+      <x:c r="K53" s="52" t="n">
+        <x:f>'Riding comparison'!N53</x:f>
+        <x:v>2590</x:v>
+      </x:c>
+      <x:c r="L53" s="52" t="n">
+        <x:f>'Riding comparison'!O53</x:f>
+        <x:v>24841</x:v>
+      </x:c>
+      <x:c r="M53" s="52" t="n">
+        <x:f>'Riding comparison'!P53</x:f>
+        <x:v>24871</x:v>
+      </x:c>
+      <x:c r="N53" s="53" t="n">
+        <x:f>H53-B53</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O53" s="53" t="n">
+        <x:f>I53-C53</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P53" s="53" t="n">
+        <x:f>J53-D53</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q53" s="53" t="n">
+        <x:f>K53-E53</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R53" s="53" t="n">
+        <x:f>L53-F53</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S53" s="53" t="n">
+        <x:f>M53-G53</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T53" t="str">
+        <x:f>IF(COUNTIF(N53:S53,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U53" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V53" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="19" customHeight="1">
+      <x:c r="A54" t="str">
+        <x:v>Peace River North</x:v>
+      </x:c>
+      <x:c r="B54" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C54" s="51" t="n">
+        <x:v>8957</x:v>
+      </x:c>
+      <x:c r="D54" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E54" s="51" t="n">
+        <x:v>1489</x:v>
+      </x:c>
+      <x:c r="F54" s="51" t="n">
+        <x:v>10446</x:v>
+      </x:c>
+      <x:c r="G54" s="51" t="n">
+        <x:v>10749</x:v>
+      </x:c>
+      <x:c r="H54" s="52" t="n">
+        <x:f>'Riding comparison'!K54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I54" s="52" t="n">
+        <x:f>'Riding comparison'!L54</x:f>
+        <x:v>8957</x:v>
+      </x:c>
+      <x:c r="J54" s="52" t="n">
+        <x:f>'Riding comparison'!M54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54" s="52" t="n">
+        <x:f>'Riding comparison'!N54</x:f>
+        <x:v>1489</x:v>
+      </x:c>
+      <x:c r="L54" s="52" t="n">
+        <x:f>'Riding comparison'!O54</x:f>
+        <x:v>10446</x:v>
+      </x:c>
+      <x:c r="M54" s="52" t="n">
+        <x:f>'Riding comparison'!P54</x:f>
+        <x:v>10749</x:v>
+      </x:c>
+      <x:c r="N54" s="53" t="n">
+        <x:f>H54-B54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O54" s="53" t="n">
+        <x:f>I54-C54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P54" s="53" t="n">
+        <x:f>J54-D54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q54" s="53" t="n">
+        <x:f>K54-E54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R54" s="53" t="n">
+        <x:f>L54-F54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S54" s="53" t="n">
+        <x:f>M54-G54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T54" t="str">
+        <x:f>IF(COUNTIF(N54:S54,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U54" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V54" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="19" customHeight="1">
+      <x:c r="A55" t="str">
+        <x:v>Peace River South</x:v>
+      </x:c>
+      <x:c r="B55" s="51" t="n">
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="C55" s="51" t="n">
+        <x:v>6070</x:v>
+      </x:c>
+      <x:c r="D55" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E55" s="51" t="n">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="F55" s="51" t="n">
+        <x:v>7813</x:v>
+      </x:c>
+      <x:c r="G55" s="51" t="n">
+        <x:v>7841</x:v>
+      </x:c>
+      <x:c r="H55" s="52" t="n">
+        <x:f>'Riding comparison'!K55</x:f>
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="I55" s="52" t="n">
+        <x:f>'Riding comparison'!L55</x:f>
+        <x:v>6070</x:v>
+      </x:c>
+      <x:c r="J55" s="52" t="n">
+        <x:f>'Riding comparison'!M55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="52" t="n">
+        <x:f>'Riding comparison'!N55</x:f>
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="L55" s="52" t="n">
+        <x:f>'Riding comparison'!O55</x:f>
+        <x:v>7813</x:v>
+      </x:c>
+      <x:c r="M55" s="52" t="n">
+        <x:f>'Riding comparison'!P55</x:f>
+        <x:v>7841</x:v>
+      </x:c>
+      <x:c r="N55" s="53" t="n">
+        <x:f>H55-B55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O55" s="53" t="n">
+        <x:f>I55-C55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P55" s="53" t="n">
+        <x:f>J55-D55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q55" s="53" t="n">
+        <x:f>K55-E55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R55" s="53" t="n">
+        <x:f>L55-F55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S55" s="53" t="n">
+        <x:f>M55-G55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T55" t="str">
+        <x:f>IF(COUNTIF(N55:S55,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U55" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V55" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="19" customHeight="1">
+      <x:c r="A56" t="str">
+        <x:v>Penticton-Summerland</x:v>
+      </x:c>
+      <x:c r="B56" s="51" t="n">
+        <x:v>10470</x:v>
+      </x:c>
+      <x:c r="C56" s="51" t="n">
+        <x:v>11589</x:v>
+      </x:c>
+      <x:c r="D56" s="51" t="n">
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="E56" s="51" t="n">
+        <x:v>1341</x:v>
+      </x:c>
+      <x:c r="F56" s="51" t="n">
+        <x:v>25431</x:v>
+      </x:c>
+      <x:c r="G56" s="51" t="n">
+        <x:v>25461</x:v>
+      </x:c>
+      <x:c r="H56" s="52" t="n">
+        <x:f>'Riding comparison'!K56</x:f>
+        <x:v>10470</x:v>
+      </x:c>
+      <x:c r="I56" s="52" t="n">
+        <x:f>'Riding comparison'!L56</x:f>
+        <x:v>11589</x:v>
+      </x:c>
+      <x:c r="J56" s="52" t="n">
+        <x:f>'Riding comparison'!M56</x:f>
+        <x:v>2031</x:v>
+      </x:c>
+      <x:c r="K56" s="52" t="n">
+        <x:f>'Riding comparison'!N56</x:f>
+        <x:v>1341</x:v>
+      </x:c>
+      <x:c r="L56" s="52" t="n">
+        <x:f>'Riding comparison'!O56</x:f>
+        <x:v>25431</x:v>
+      </x:c>
+      <x:c r="M56" s="52" t="n">
+        <x:f>'Riding comparison'!P56</x:f>
+        <x:v>25461</x:v>
+      </x:c>
+      <x:c r="N56" s="53" t="n">
+        <x:f>H56-B56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O56" s="53" t="n">
+        <x:f>I56-C56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P56" s="53" t="n">
+        <x:f>J56-D56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q56" s="53" t="n">
+        <x:f>K56-E56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R56" s="53" t="n">
+        <x:f>L56-F56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S56" s="53" t="n">
+        <x:f>M56-G56</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T56" t="str">
+        <x:f>IF(COUNTIF(N56:S56,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U56" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V56" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="19" customHeight="1">
+      <x:c r="A57" t="str">
+        <x:v>Port Coquitlam</x:v>
+      </x:c>
+      <x:c r="B57" s="51" t="n">
+        <x:v>9760</x:v>
+      </x:c>
+      <x:c r="C57" s="51" t="n">
+        <x:v>9374</x:v>
+      </x:c>
+      <x:c r="D57" s="51" t="n">
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="E57" s="51" t="n">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="F57" s="51" t="n">
+        <x:v>21526</x:v>
+      </x:c>
+      <x:c r="G57" s="51" t="n">
+        <x:v>21570</x:v>
+      </x:c>
+      <x:c r="H57" s="52" t="n">
+        <x:f>'Riding comparison'!K57</x:f>
+        <x:v>9760</x:v>
+      </x:c>
+      <x:c r="I57" s="52" t="n">
+        <x:f>'Riding comparison'!L57</x:f>
+        <x:v>9374</x:v>
+      </x:c>
+      <x:c r="J57" s="52" t="n">
+        <x:f>'Riding comparison'!M57</x:f>
+        <x:v>1833</x:v>
+      </x:c>
+      <x:c r="K57" s="52" t="n">
+        <x:f>'Riding comparison'!N57</x:f>
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="L57" s="52" t="n">
+        <x:f>'Riding comparison'!O57</x:f>
+        <x:v>21526</x:v>
+      </x:c>
+      <x:c r="M57" s="52" t="n">
+        <x:f>'Riding comparison'!P57</x:f>
+        <x:v>21570</x:v>
+      </x:c>
+      <x:c r="N57" s="53" t="n">
+        <x:f>H57-B57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O57" s="53" t="n">
+        <x:f>I57-C57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P57" s="53" t="n">
+        <x:f>J57-D57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q57" s="53" t="n">
+        <x:f>K57-E57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R57" s="53" t="n">
+        <x:f>L57-F57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S57" s="53" t="n">
+        <x:f>M57-G57</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T57" t="str">
+        <x:f>IF(COUNTIF(N57:S57,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U57" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V57" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="19" customHeight="1">
+      <x:c r="A58" t="str">
+        <x:v>Port Moody-Burquitlam</x:v>
+      </x:c>
+      <x:c r="B58" s="51" t="n">
+        <x:v>9635</x:v>
+      </x:c>
+      <x:c r="C58" s="51" t="n">
+        <x:v>10713</x:v>
+      </x:c>
+      <x:c r="D58" s="51" t="n">
+        <x:v>1874</x:v>
+      </x:c>
+      <x:c r="E58" s="51" t="n">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="F58" s="51" t="n">
+        <x:v>22865</x:v>
+      </x:c>
+      <x:c r="G58" s="51" t="n">
+        <x:v>22896</x:v>
+      </x:c>
+      <x:c r="H58" s="52" t="n">
+        <x:f>'Riding comparison'!K58</x:f>
+        <x:v>9635</x:v>
+      </x:c>
+      <x:c r="I58" s="52" t="n">
+        <x:f>'Riding comparison'!L58</x:f>
+        <x:v>10713</x:v>
+      </x:c>
+      <x:c r="J58" s="52" t="n">
+        <x:f>'Riding comparison'!M58</x:f>
+        <x:v>1874</x:v>
+      </x:c>
+      <x:c r="K58" s="52" t="n">
+        <x:f>'Riding comparison'!N58</x:f>
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="L58" s="52" t="n">
+        <x:f>'Riding comparison'!O58</x:f>
+        <x:v>22865</x:v>
+      </x:c>
+      <x:c r="M58" s="52" t="n">
+        <x:f>'Riding comparison'!P58</x:f>
+        <x:v>22896</x:v>
+      </x:c>
+      <x:c r="N58" s="53" t="n">
+        <x:f>H58-B58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O58" s="53" t="n">
+        <x:f>I58-C58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P58" s="53" t="n">
+        <x:f>J58-D58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q58" s="53" t="n">
+        <x:f>K58-E58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R58" s="53" t="n">
+        <x:f>L58-F58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S58" s="53" t="n">
+        <x:f>M58-G58</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T58" t="str">
+        <x:f>IF(COUNTIF(N58:S58,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U58" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V58" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="19" customHeight="1">
+      <x:c r="A59" t="str">
+        <x:v>Powell River-Sunshine Coast</x:v>
+      </x:c>
+      <x:c r="B59" s="51" t="n">
+        <x:v>12783</x:v>
+      </x:c>
+      <x:c r="C59" s="51" t="n">
+        <x:v>10156</x:v>
+      </x:c>
+      <x:c r="D59" s="51" t="n">
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="E59" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F59" s="51" t="n">
+        <x:v>26042</x:v>
+      </x:c>
+      <x:c r="G59" s="51" t="n">
+        <x:v>26082</x:v>
+      </x:c>
+      <x:c r="H59" s="52" t="n">
+        <x:f>'Riding comparison'!K59</x:f>
+        <x:v>12783</x:v>
+      </x:c>
+      <x:c r="I59" s="52" t="n">
+        <x:f>'Riding comparison'!L59</x:f>
+        <x:v>10156</x:v>
+      </x:c>
+      <x:c r="J59" s="52" t="n">
+        <x:f>'Riding comparison'!M59</x:f>
+        <x:v>3103</x:v>
+      </x:c>
+      <x:c r="K59" s="52" t="n">
+        <x:f>'Riding comparison'!N59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59" s="52" t="n">
+        <x:f>'Riding comparison'!O59</x:f>
+        <x:v>26042</x:v>
+      </x:c>
+      <x:c r="M59" s="52" t="n">
+        <x:f>'Riding comparison'!P59</x:f>
+        <x:v>26082</x:v>
+      </x:c>
+      <x:c r="N59" s="53" t="n">
+        <x:f>H59-B59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O59" s="53" t="n">
+        <x:f>I59-C59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P59" s="53" t="n">
+        <x:f>J59-D59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q59" s="53" t="n">
+        <x:f>K59-E59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R59" s="53" t="n">
+        <x:f>L59-F59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S59" s="53" t="n">
+        <x:f>M59-G59</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T59" t="str">
+        <x:f>IF(COUNTIF(N59:S59,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U59" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V59" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="19" customHeight="1">
+      <x:c r="A60" t="str">
+        <x:v>Prince George-Mackenzie</x:v>
+      </x:c>
+      <x:c r="B60" s="51" t="n">
+        <x:v>3532</x:v>
+      </x:c>
+      <x:c r="C60" s="51" t="n">
+        <x:v>9926</x:v>
+      </x:c>
+      <x:c r="D60" s="51" t="n">
+        <x:v>1517</x:v>
+      </x:c>
+      <x:c r="E60" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F60" s="51" t="n">
+        <x:v>14975</x:v>
+      </x:c>
+      <x:c r="G60" s="51" t="n">
+        <x:v>15014</x:v>
+      </x:c>
+      <x:c r="H60" s="52" t="n">
+        <x:f>'Riding comparison'!K60</x:f>
+        <x:v>3532</x:v>
+      </x:c>
+      <x:c r="I60" s="52" t="n">
+        <x:f>'Riding comparison'!L60</x:f>
+        <x:v>9926</x:v>
+      </x:c>
+      <x:c r="J60" s="52" t="n">
+        <x:f>'Riding comparison'!M60</x:f>
+        <x:v>1517</x:v>
+      </x:c>
+      <x:c r="K60" s="52" t="n">
+        <x:f>'Riding comparison'!N60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L60" s="52" t="n">
+        <x:f>'Riding comparison'!O60</x:f>
+        <x:v>14975</x:v>
+      </x:c>
+      <x:c r="M60" s="52" t="n">
+        <x:f>'Riding comparison'!P60</x:f>
+        <x:v>15014</x:v>
+      </x:c>
+      <x:c r="N60" s="53" t="n">
+        <x:f>H60-B60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O60" s="53" t="n">
+        <x:f>I60-C60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P60" s="53" t="n">
+        <x:f>J60-D60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q60" s="53" t="n">
+        <x:f>K60-E60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R60" s="53" t="n">
+        <x:f>L60-F60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S60" s="53" t="n">
+        <x:f>M60-G60</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T60" t="str">
+        <x:f>IF(COUNTIF(N60:S60,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U60" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V60" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="19" customHeight="1">
+      <x:c r="A61" t="str">
+        <x:v>Prince George-North Cariboo</x:v>
+      </x:c>
+      <x:c r="B61" s="51" t="n">
+        <x:v>3380</x:v>
+      </x:c>
+      <x:c r="C61" s="51" t="n">
+        <x:v>11799</x:v>
+      </x:c>
+      <x:c r="D61" s="51" t="n">
+        <x:v>1577</x:v>
+      </x:c>
+      <x:c r="E61" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F61" s="51" t="n">
+        <x:v>16756</x:v>
+      </x:c>
+      <x:c r="G61" s="51" t="n">
+        <x:v>16792</x:v>
+      </x:c>
+      <x:c r="H61" s="52" t="n">
+        <x:f>'Riding comparison'!K61</x:f>
+        <x:v>3380</x:v>
+      </x:c>
+      <x:c r="I61" s="52" t="n">
+        <x:f>'Riding comparison'!L61</x:f>
+        <x:v>11799</x:v>
+      </x:c>
+      <x:c r="J61" s="52" t="n">
+        <x:f>'Riding comparison'!M61</x:f>
+        <x:v>1577</x:v>
+      </x:c>
+      <x:c r="K61" s="52" t="n">
+        <x:f>'Riding comparison'!N61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L61" s="52" t="n">
+        <x:f>'Riding comparison'!O61</x:f>
+        <x:v>16756</x:v>
+      </x:c>
+      <x:c r="M61" s="52" t="n">
+        <x:f>'Riding comparison'!P61</x:f>
+        <x:v>16792</x:v>
+      </x:c>
+      <x:c r="N61" s="53" t="n">
+        <x:f>H61-B61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O61" s="53" t="n">
+        <x:f>I61-C61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P61" s="53" t="n">
+        <x:f>J61-D61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q61" s="53" t="n">
+        <x:f>K61-E61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R61" s="53" t="n">
+        <x:f>L61-F61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S61" s="53" t="n">
+        <x:f>M61-G61</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T61" t="str">
+        <x:f>IF(COUNTIF(N61:S61,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U61" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V61" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="19" customHeight="1">
+      <x:c r="A62" t="str">
+        <x:v>Prince George-Valemount</x:v>
+      </x:c>
+      <x:c r="B62" s="51" t="n">
+        <x:v>3774</x:v>
+      </x:c>
+      <x:c r="C62" s="51" t="n">
+        <x:v>6597</x:v>
+      </x:c>
+      <x:c r="D62" s="51" t="n">
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="E62" s="51" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="F62" s="51" t="n">
+        <x:v>12900</x:v>
+      </x:c>
+      <x:c r="G62" s="51" t="n">
+        <x:v>12923</x:v>
+      </x:c>
+      <x:c r="H62" s="52" t="n">
+        <x:f>'Riding comparison'!K62</x:f>
+        <x:v>3774</x:v>
+      </x:c>
+      <x:c r="I62" s="52" t="n">
+        <x:f>'Riding comparison'!L62</x:f>
+        <x:v>6597</x:v>
+      </x:c>
+      <x:c r="J62" s="52" t="n">
+        <x:f>'Riding comparison'!M62</x:f>
+        <x:v>1502</x:v>
+      </x:c>
+      <x:c r="K62" s="52" t="n">
+        <x:f>'Riding comparison'!N62</x:f>
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="L62" s="52" t="n">
+        <x:f>'Riding comparison'!O62</x:f>
+        <x:v>12900</x:v>
+      </x:c>
+      <x:c r="M62" s="52" t="n">
+        <x:f>'Riding comparison'!P62</x:f>
+        <x:v>12923</x:v>
+      </x:c>
+      <x:c r="N62" s="53" t="n">
+        <x:f>H62-B62</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O62" s="53" t="n">
+        <x:f>I62-C62</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P62" s="53" t="n">
+        <x:f>J62-D62</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q62" s="53" t="n">
+        <x:f>K62-E62</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R62" s="53" t="n">
+        <x:f>L62-F62</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S62" s="53" t="n">
+        <x:f>M62-G62</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T62" t="str">
+        <x:f>IF(COUNTIF(N62:S62,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U62" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V62" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="19" customHeight="1">
+      <x:c r="A63" t="str">
+        <x:v>Richmond-Bridgeport</x:v>
+      </x:c>
+      <x:c r="B63" s="51" t="n">
+        <x:v>4360</x:v>
+      </x:c>
+      <x:c r="C63" s="51" t="n">
+        <x:v>9390</x:v>
+      </x:c>
+      <x:c r="D63" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E63" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F63" s="51" t="n">
+        <x:v>13750</x:v>
+      </x:c>
+      <x:c r="G63" s="51" t="n">
+        <x:v>13842</x:v>
+      </x:c>
+      <x:c r="H63" s="52" t="n">
+        <x:f>'Riding comparison'!K63</x:f>
+        <x:v>4360</x:v>
+      </x:c>
+      <x:c r="I63" s="52" t="n">
+        <x:f>'Riding comparison'!L63</x:f>
+        <x:v>9390</x:v>
+      </x:c>
+      <x:c r="J63" s="52" t="n">
+        <x:f>'Riding comparison'!M63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63" s="52" t="n">
+        <x:f>'Riding comparison'!N63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" s="52" t="n">
+        <x:f>'Riding comparison'!O63</x:f>
+        <x:v>13750</x:v>
+      </x:c>
+      <x:c r="M63" s="52" t="n">
+        <x:f>'Riding comparison'!P63</x:f>
+        <x:v>13842</x:v>
+      </x:c>
+      <x:c r="N63" s="53" t="n">
+        <x:f>H63-B63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O63" s="53" t="n">
+        <x:f>I63-C63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P63" s="53" t="n">
+        <x:f>J63-D63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q63" s="53" t="n">
+        <x:f>K63-E63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R63" s="53" t="n">
+        <x:f>L63-F63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S63" s="53" t="n">
+        <x:f>M63-G63</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T63" t="str">
+        <x:f>IF(COUNTIF(N63:S63,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U63" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V63" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="19" customHeight="1">
+      <x:c r="A64" t="str">
+        <x:v>Richmond Centre</x:v>
+      </x:c>
+      <x:c r="B64" s="51" t="n">
+        <x:v>4356</x:v>
+      </x:c>
+      <x:c r="C64" s="51" t="n">
+        <x:v>7414</x:v>
+      </x:c>
+      <x:c r="D64" s="51" t="n">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="E64" s="51" t="n">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="F64" s="51" t="n">
+        <x:v>12863</x:v>
+      </x:c>
+      <x:c r="G64" s="51" t="n">
+        <x:v>12901</x:v>
+      </x:c>
+      <x:c r="H64" s="52" t="n">
+        <x:f>'Riding comparison'!K64</x:f>
+        <x:v>4356</x:v>
+      </x:c>
+      <x:c r="I64" s="52" t="n">
+        <x:f>'Riding comparison'!L64</x:f>
+        <x:v>7414</x:v>
+      </x:c>
+      <x:c r="J64" s="52" t="n">
+        <x:f>'Riding comparison'!M64</x:f>
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="K64" s="52" t="n">
+        <x:f>'Riding comparison'!N64</x:f>
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="L64" s="52" t="n">
+        <x:f>'Riding comparison'!O64</x:f>
+        <x:v>12863</x:v>
+      </x:c>
+      <x:c r="M64" s="52" t="n">
+        <x:f>'Riding comparison'!P64</x:f>
+        <x:v>12901</x:v>
+      </x:c>
+      <x:c r="N64" s="53" t="n">
+        <x:f>H64-B64</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O64" s="53" t="n">
+        <x:f>I64-C64</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P64" s="53" t="n">
+        <x:f>J64-D64</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q64" s="53" t="n">
+        <x:f>K64-E64</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R64" s="53" t="n">
+        <x:f>L64-F64</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S64" s="53" t="n">
+        <x:f>M64-G64</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T64" t="str">
+        <x:f>IF(COUNTIF(N64:S64,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U64" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V64" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="19" customHeight="1">
+      <x:c r="A65" t="str">
+        <x:v>Richmond-Queensborough</x:v>
+      </x:c>
+      <x:c r="B65" s="51" t="n">
+        <x:v>5453</x:v>
+      </x:c>
+      <x:c r="C65" s="51" t="n">
+        <x:v>9642</x:v>
+      </x:c>
+      <x:c r="D65" s="51" t="n">
+        <x:v>1239</x:v>
+      </x:c>
+      <x:c r="E65" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F65" s="51" t="n">
+        <x:v>16334</x:v>
+      </x:c>
+      <x:c r="G65" s="51" t="n">
+        <x:v>16387</x:v>
+      </x:c>
+      <x:c r="H65" s="52" t="n">
+        <x:f>'Riding comparison'!K65</x:f>
+        <x:v>5453</x:v>
+      </x:c>
+      <x:c r="I65" s="52" t="n">
+        <x:f>'Riding comparison'!L65</x:f>
+        <x:v>9642</x:v>
+      </x:c>
+      <x:c r="J65" s="52" t="n">
+        <x:f>'Riding comparison'!M65</x:f>
+        <x:v>1239</x:v>
+      </x:c>
+      <x:c r="K65" s="52" t="n">
+        <x:f>'Riding comparison'!N65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L65" s="52" t="n">
+        <x:f>'Riding comparison'!O65</x:f>
+        <x:v>16334</x:v>
+      </x:c>
+      <x:c r="M65" s="52" t="n">
+        <x:f>'Riding comparison'!P65</x:f>
+        <x:v>16387</x:v>
+      </x:c>
+      <x:c r="N65" s="53" t="n">
+        <x:f>H65-B65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O65" s="53" t="n">
+        <x:f>I65-C65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P65" s="53" t="n">
+        <x:f>J65-D65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q65" s="53" t="n">
+        <x:f>K65-E65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R65" s="53" t="n">
+        <x:f>L65-F65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S65" s="53" t="n">
+        <x:f>M65-G65</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T65" t="str">
+        <x:f>IF(COUNTIF(N65:S65,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U65" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V65" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="19" customHeight="1">
+      <x:c r="A66" t="str">
+        <x:v>Richmond-Steveston</x:v>
+      </x:c>
+      <x:c r="B66" s="51" t="n">
+        <x:v>7002</x:v>
+      </x:c>
+      <x:c r="C66" s="51" t="n">
+        <x:v>10843</x:v>
+      </x:c>
+      <x:c r="D66" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E66" s="51" t="n">
+        <x:v>2168</x:v>
+      </x:c>
+      <x:c r="F66" s="51" t="n">
+        <x:v>20013</x:v>
+      </x:c>
+      <x:c r="G66" s="51" t="n">
+        <x:v>20066</x:v>
+      </x:c>
+      <x:c r="H66" s="52" t="n">
+        <x:f>'Riding comparison'!K66</x:f>
+        <x:v>7002</x:v>
+      </x:c>
+      <x:c r="I66" s="52" t="n">
+        <x:f>'Riding comparison'!L66</x:f>
+        <x:v>10843</x:v>
+      </x:c>
+      <x:c r="J66" s="52" t="n">
+        <x:f>'Riding comparison'!M66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="52" t="n">
+        <x:f>'Riding comparison'!N66</x:f>
+        <x:v>2168</x:v>
+      </x:c>
+      <x:c r="L66" s="52" t="n">
+        <x:f>'Riding comparison'!O66</x:f>
+        <x:v>20013</x:v>
+      </x:c>
+      <x:c r="M66" s="52" t="n">
+        <x:f>'Riding comparison'!P66</x:f>
+        <x:v>20066</x:v>
+      </x:c>
+      <x:c r="N66" s="53" t="n">
+        <x:f>H66-B66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O66" s="53" t="n">
+        <x:f>I66-C66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P66" s="53" t="n">
+        <x:f>J66-D66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q66" s="53" t="n">
+        <x:f>K66-E66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R66" s="53" t="n">
+        <x:f>L66-F66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S66" s="53" t="n">
+        <x:f>M66-G66</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T66" t="str">
+        <x:f>IF(COUNTIF(N66:S66,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U66" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V66" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="19" customHeight="1">
+      <x:c r="A67" t="str">
+        <x:v>Saanich North and the Islands</x:v>
+      </x:c>
+      <x:c r="B67" s="51" t="n">
+        <x:v>5225</x:v>
+      </x:c>
+      <x:c r="C67" s="51" t="n">
+        <x:v>9464</x:v>
+      </x:c>
+      <x:c r="D67" s="51" t="n">
+        <x:v>14481</x:v>
+      </x:c>
+      <x:c r="E67" s="51" t="n">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="F67" s="51" t="n">
+        <x:v>29868</x:v>
+      </x:c>
+      <x:c r="G67" s="51" t="n">
+        <x:v>29894</x:v>
+      </x:c>
+      <x:c r="H67" s="52" t="n">
+        <x:f>'Riding comparison'!K67</x:f>
+        <x:v>5225</x:v>
+      </x:c>
+      <x:c r="I67" s="52" t="n">
+        <x:f>'Riding comparison'!L67</x:f>
+        <x:v>9464</x:v>
+      </x:c>
+      <x:c r="J67" s="52" t="n">
+        <x:f>'Riding comparison'!M67</x:f>
+        <x:v>14481</x:v>
+      </x:c>
+      <x:c r="K67" s="52" t="n">
+        <x:f>'Riding comparison'!N67</x:f>
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="L67" s="52" t="n">
+        <x:f>'Riding comparison'!O67</x:f>
+        <x:v>29868</x:v>
+      </x:c>
+      <x:c r="M67" s="52" t="n">
+        <x:f>'Riding comparison'!P67</x:f>
+        <x:v>29894</x:v>
+      </x:c>
+      <x:c r="N67" s="53" t="n">
+        <x:f>H67-B67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O67" s="53" t="n">
+        <x:f>I67-C67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P67" s="53" t="n">
+        <x:f>J67-D67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q67" s="53" t="n">
+        <x:f>K67-E67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R67" s="53" t="n">
+        <x:f>L67-F67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S67" s="53" t="n">
+        <x:f>M67-G67</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T67" t="str">
+        <x:f>IF(COUNTIF(N67:S67,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U67" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V67" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="19" customHeight="1">
+      <x:c r="A68" t="str">
+        <x:v>Saanich South</x:v>
+      </x:c>
+      <x:c r="B68" s="51" t="n">
+        <x:v>9322</x:v>
+      </x:c>
+      <x:c r="C68" s="51" t="n">
+        <x:v>10549</x:v>
+      </x:c>
+      <x:c r="D68" s="51" t="n">
+        <x:v>6985</x:v>
+      </x:c>
+      <x:c r="E68" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F68" s="51" t="n">
+        <x:v>26856</x:v>
+      </x:c>
+      <x:c r="G68" s="51" t="n">
+        <x:v>26881</x:v>
+      </x:c>
+      <x:c r="H68" s="52" t="n">
+        <x:f>'Riding comparison'!K68</x:f>
+        <x:v>9322</x:v>
+      </x:c>
+      <x:c r="I68" s="52" t="n">
+        <x:f>'Riding comparison'!L68</x:f>
+        <x:v>10549</x:v>
+      </x:c>
+      <x:c r="J68" s="52" t="n">
+        <x:f>'Riding comparison'!M68</x:f>
+        <x:v>6985</x:v>
+      </x:c>
+      <x:c r="K68" s="52" t="n">
+        <x:f>'Riding comparison'!N68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L68" s="52" t="n">
+        <x:f>'Riding comparison'!O68</x:f>
+        <x:v>26856</x:v>
+      </x:c>
+      <x:c r="M68" s="52" t="n">
+        <x:f>'Riding comparison'!P68</x:f>
+        <x:v>26881</x:v>
+      </x:c>
+      <x:c r="N68" s="53" t="n">
+        <x:f>H68-B68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O68" s="53" t="n">
+        <x:f>I68-C68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P68" s="53" t="n">
+        <x:f>J68-D68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q68" s="53" t="n">
+        <x:f>K68-E68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R68" s="53" t="n">
+        <x:f>L68-F68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S68" s="53" t="n">
+        <x:f>M68-G68</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T68" t="str">
+        <x:f>IF(COUNTIF(N68:S68,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U68" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V68" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="19" customHeight="1">
+      <x:c r="A69" t="str">
+        <x:v>Salmon Arm-Shuswap</x:v>
+      </x:c>
+      <x:c r="B69" s="51" t="n">
+        <x:v>7906</x:v>
+      </x:c>
+      <x:c r="C69" s="51" t="n">
+        <x:v>15421</x:v>
+      </x:c>
+      <x:c r="D69" s="51" t="n">
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="E69" s="51" t="n">
+        <x:v>2469</x:v>
+      </x:c>
+      <x:c r="F69" s="51" t="n">
+        <x:v>28108</x:v>
+      </x:c>
+      <x:c r="G69" s="51" t="n">
+        <x:v>28152</x:v>
+      </x:c>
+      <x:c r="H69" s="52" t="n">
+        <x:f>'Riding comparison'!K69</x:f>
+        <x:v>7906</x:v>
+      </x:c>
+      <x:c r="I69" s="52" t="n">
+        <x:f>'Riding comparison'!L69</x:f>
+        <x:v>15421</x:v>
+      </x:c>
+      <x:c r="J69" s="52" t="n">
+        <x:f>'Riding comparison'!M69</x:f>
+        <x:v>2312</x:v>
+      </x:c>
+      <x:c r="K69" s="52" t="n">
+        <x:f>'Riding comparison'!N69</x:f>
+        <x:v>2469</x:v>
+      </x:c>
+      <x:c r="L69" s="52" t="n">
+        <x:f>'Riding comparison'!O69</x:f>
+        <x:v>28108</x:v>
+      </x:c>
+      <x:c r="M69" s="52" t="n">
+        <x:f>'Riding comparison'!P69</x:f>
+        <x:v>28152</x:v>
+      </x:c>
+      <x:c r="N69" s="53" t="n">
+        <x:f>H69-B69</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O69" s="53" t="n">
+        <x:f>I69-C69</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P69" s="53" t="n">
+        <x:f>J69-D69</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q69" s="53" t="n">
+        <x:f>K69-E69</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R69" s="53" t="n">
+        <x:f>L69-F69</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S69" s="53" t="n">
+        <x:f>M69-G69</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T69" t="str">
+        <x:f>IF(COUNTIF(N69:S69,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U69" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V69" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="19" customHeight="1">
+      <x:c r="A70" t="str">
+        <x:v>Skeena</x:v>
+      </x:c>
+      <x:c r="B70" s="51" t="n">
+        <x:v>4106</x:v>
+      </x:c>
+      <x:c r="C70" s="51" t="n">
+        <x:v>5634</x:v>
+      </x:c>
+      <x:c r="D70" s="51" t="n">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="E70" s="51" t="n">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="F70" s="51" t="n">
+        <x:v>10940</x:v>
+      </x:c>
+      <x:c r="G70" s="51" t="n">
+        <x:v>10960</x:v>
+      </x:c>
+      <x:c r="H70" s="52" t="n">
+        <x:f>'Riding comparison'!K70</x:f>
+        <x:v>4106</x:v>
+      </x:c>
+      <x:c r="I70" s="52" t="n">
+        <x:f>'Riding comparison'!L70</x:f>
+        <x:v>5634</x:v>
+      </x:c>
+      <x:c r="J70" s="52" t="n">
+        <x:f>'Riding comparison'!M70</x:f>
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="K70" s="52" t="n">
+        <x:f>'Riding comparison'!N70</x:f>
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="L70" s="52" t="n">
+        <x:f>'Riding comparison'!O70</x:f>
+        <x:v>10940</x:v>
+      </x:c>
+      <x:c r="M70" s="52" t="n">
+        <x:f>'Riding comparison'!P70</x:f>
+        <x:v>10960</x:v>
+      </x:c>
+      <x:c r="N70" s="53" t="n">
+        <x:f>H70-B70</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O70" s="53" t="n">
+        <x:f>I70-C70</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P70" s="53" t="n">
+        <x:f>J70-D70</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q70" s="53" t="n">
+        <x:f>K70-E70</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R70" s="53" t="n">
+        <x:f>L70-F70</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S70" s="53" t="n">
+        <x:f>M70-G70</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T70" t="str">
+        <x:f>IF(COUNTIF(N70:S70,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U70" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V70" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="19" customHeight="1">
+      <x:c r="A71" t="str">
+        <x:v>Surrey City Centre</x:v>
+      </x:c>
+      <x:c r="B71" s="51" t="n">
+        <x:v>5318</x:v>
+      </x:c>
+      <x:c r="C71" s="51" t="n">
+        <x:v>5713</x:v>
+      </x:c>
+      <x:c r="D71" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E71" s="51" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="F71" s="51" t="n">
+        <x:v>12032</x:v>
+      </x:c>
+      <x:c r="G71" s="51" t="n">
+        <x:v>12067</x:v>
+      </x:c>
+      <x:c r="H71" s="52" t="n">
+        <x:f>'Riding comparison'!K71</x:f>
+        <x:v>5318</x:v>
+      </x:c>
+      <x:c r="I71" s="52" t="n">
+        <x:f>'Riding comparison'!L71</x:f>
+        <x:v>5713</x:v>
+      </x:c>
+      <x:c r="J71" s="52" t="n">
+        <x:f>'Riding comparison'!M71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="52" t="n">
+        <x:f>'Riding comparison'!N71</x:f>
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="L71" s="52" t="n">
+        <x:f>'Riding comparison'!O71</x:f>
+        <x:v>12032</x:v>
+      </x:c>
+      <x:c r="M71" s="52" t="n">
+        <x:f>'Riding comparison'!P71</x:f>
+        <x:v>12067</x:v>
+      </x:c>
+      <x:c r="N71" s="53" t="n">
+        <x:f>H71-B71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O71" s="53" t="n">
+        <x:f>I71-C71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P71" s="53" t="n">
+        <x:f>J71-D71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q71" s="53" t="n">
+        <x:f>K71-E71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R71" s="53" t="n">
+        <x:f>L71-F71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S71" s="53" t="n">
+        <x:f>M71-G71</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T71" t="str">
+        <x:f>IF(COUNTIF(N71:S71,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U71" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V71" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="19" customHeight="1">
+      <x:c r="A72" t="str">
+        <x:v>Surrey-Cloverdale</x:v>
+      </x:c>
+      <x:c r="B72" s="51" t="n">
+        <x:v>5846</x:v>
+      </x:c>
+      <x:c r="C72" s="51" t="n">
+        <x:v>9151</x:v>
+      </x:c>
+      <x:c r="D72" s="51" t="n">
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="E72" s="51" t="n">
+        <x:v>1129</x:v>
+      </x:c>
+      <x:c r="F72" s="51" t="n">
+        <x:v>17440</x:v>
+      </x:c>
+      <x:c r="G72" s="51" t="n">
+        <x:v>17455</x:v>
+      </x:c>
+      <x:c r="H72" s="52" t="n">
+        <x:f>'Riding comparison'!K72</x:f>
+        <x:v>5846</x:v>
+      </x:c>
+      <x:c r="I72" s="52" t="n">
+        <x:f>'Riding comparison'!L72</x:f>
+        <x:v>9151</x:v>
+      </x:c>
+      <x:c r="J72" s="52" t="n">
+        <x:f>'Riding comparison'!M72</x:f>
+        <x:v>1314</x:v>
+      </x:c>
+      <x:c r="K72" s="52" t="n">
+        <x:f>'Riding comparison'!N72</x:f>
+        <x:v>1129</x:v>
+      </x:c>
+      <x:c r="L72" s="52" t="n">
+        <x:f>'Riding comparison'!O72</x:f>
+        <x:v>17440</x:v>
+      </x:c>
+      <x:c r="M72" s="52" t="n">
+        <x:f>'Riding comparison'!P72</x:f>
+        <x:v>17455</x:v>
+      </x:c>
+      <x:c r="N72" s="53" t="n">
+        <x:f>H72-B72</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O72" s="53" t="n">
+        <x:f>I72-C72</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P72" s="53" t="n">
+        <x:f>J72-D72</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q72" s="53" t="n">
+        <x:f>K72-E72</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R72" s="53" t="n">
+        <x:f>L72-F72</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S72" s="53" t="n">
+        <x:f>M72-G72</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T72" t="str">
+        <x:f>IF(COUNTIF(N72:S72,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U72" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V72" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="19" customHeight="1">
+      <x:c r="A73" t="str">
+        <x:v>Surrey-Fleetwood</x:v>
+      </x:c>
+      <x:c r="B73" s="51" t="n">
+        <x:v>6522</x:v>
+      </x:c>
+      <x:c r="C73" s="51" t="n">
+        <x:v>8691</x:v>
+      </x:c>
+      <x:c r="D73" s="51" t="n">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="E73" s="51" t="n">
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="F73" s="51" t="n">
+        <x:v>17136</x:v>
+      </x:c>
+      <x:c r="G73" s="51" t="n">
+        <x:v>17162</x:v>
+      </x:c>
+      <x:c r="H73" s="52" t="n">
+        <x:f>'Riding comparison'!K73</x:f>
+        <x:v>6522</x:v>
+      </x:c>
+      <x:c r="I73" s="52" t="n">
+        <x:f>'Riding comparison'!L73</x:f>
+        <x:v>8691</x:v>
+      </x:c>
+      <x:c r="J73" s="52" t="n">
+        <x:f>'Riding comparison'!M73</x:f>
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="K73" s="52" t="n">
+        <x:f>'Riding comparison'!N73</x:f>
+        <x:v>893</x:v>
+      </x:c>
+      <x:c r="L73" s="52" t="n">
+        <x:f>'Riding comparison'!O73</x:f>
+        <x:v>17136</x:v>
+      </x:c>
+      <x:c r="M73" s="52" t="n">
+        <x:f>'Riding comparison'!P73</x:f>
+        <x:v>17162</x:v>
+      </x:c>
+      <x:c r="N73" s="53" t="n">
+        <x:f>H73-B73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O73" s="53" t="n">
+        <x:f>I73-C73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P73" s="53" t="n">
+        <x:f>J73-D73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q73" s="53" t="n">
+        <x:f>K73-E73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R73" s="53" t="n">
+        <x:f>L73-F73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S73" s="53" t="n">
+        <x:f>M73-G73</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T73" t="str">
+        <x:f>IF(COUNTIF(N73:S73,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U73" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V73" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="19" customHeight="1">
+      <x:c r="A74" t="str">
+        <x:v>Surrey-Guildford</x:v>
+      </x:c>
+      <x:c r="B74" s="51" t="n">
+        <x:v>6269</x:v>
+      </x:c>
+      <x:c r="C74" s="51" t="n">
+        <x:v>7741</x:v>
+      </x:c>
+      <x:c r="D74" s="51" t="n">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="E74" s="51" t="n">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="F74" s="51" t="n">
+        <x:v>15281</x:v>
+      </x:c>
+      <x:c r="G74" s="51" t="n">
+        <x:v>15315</x:v>
+      </x:c>
+      <x:c r="H74" s="52" t="n">
+        <x:f>'Riding comparison'!K74</x:f>
+        <x:v>6269</x:v>
+      </x:c>
+      <x:c r="I74" s="52" t="n">
+        <x:f>'Riding comparison'!L74</x:f>
+        <x:v>7741</x:v>
+      </x:c>
+      <x:c r="J74" s="52" t="n">
+        <x:f>'Riding comparison'!M74</x:f>
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="K74" s="52" t="n">
+        <x:f>'Riding comparison'!N74</x:f>
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="L74" s="52" t="n">
+        <x:f>'Riding comparison'!O74</x:f>
+        <x:v>15281</x:v>
+      </x:c>
+      <x:c r="M74" s="52" t="n">
+        <x:f>'Riding comparison'!P74</x:f>
+        <x:v>15315</x:v>
+      </x:c>
+      <x:c r="N74" s="53" t="n">
+        <x:f>H74-B74</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O74" s="53" t="n">
+        <x:f>I74-C74</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P74" s="53" t="n">
+        <x:f>J74-D74</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q74" s="53" t="n">
+        <x:f>K74-E74</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R74" s="53" t="n">
+        <x:f>L74-F74</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S74" s="53" t="n">
+        <x:f>M74-G74</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T74" t="str">
+        <x:f>IF(COUNTIF(N74:S74,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U74" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V74" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="19" customHeight="1">
+      <x:c r="A75" t="str">
+        <x:v>Surrey-Newton</x:v>
+      </x:c>
+      <x:c r="B75" s="51" t="n">
+        <x:v>5476</x:v>
+      </x:c>
+      <x:c r="C75" s="51" t="n">
+        <x:v>7334</x:v>
+      </x:c>
+      <x:c r="D75" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E75" s="51" t="n">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="F75" s="51" t="n">
+        <x:v>13455</x:v>
+      </x:c>
+      <x:c r="G75" s="51" t="n">
+        <x:v>13498</x:v>
+      </x:c>
+      <x:c r="H75" s="52" t="n">
+        <x:f>'Riding comparison'!K75</x:f>
+        <x:v>5476</x:v>
+      </x:c>
+      <x:c r="I75" s="52" t="n">
+        <x:f>'Riding comparison'!L75</x:f>
+        <x:v>7334</x:v>
+      </x:c>
+      <x:c r="J75" s="52" t="n">
+        <x:f>'Riding comparison'!M75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="52" t="n">
+        <x:f>'Riding comparison'!N75</x:f>
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="L75" s="52" t="n">
+        <x:f>'Riding comparison'!O75</x:f>
+        <x:v>13455</x:v>
+      </x:c>
+      <x:c r="M75" s="52" t="n">
+        <x:f>'Riding comparison'!P75</x:f>
+        <x:v>13498</x:v>
+      </x:c>
+      <x:c r="N75" s="53" t="n">
+        <x:f>H75-B75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O75" s="53" t="n">
+        <x:f>I75-C75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P75" s="53" t="n">
+        <x:f>J75-D75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q75" s="53" t="n">
+        <x:f>K75-E75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R75" s="53" t="n">
+        <x:f>L75-F75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S75" s="53" t="n">
+        <x:f>M75-G75</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T75" t="str">
+        <x:f>IF(COUNTIF(N75:S75,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U75" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V75" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="19" customHeight="1">
+      <x:c r="A76" t="str">
+        <x:v>Surrey North</x:v>
+      </x:c>
+      <x:c r="B76" s="51" t="n">
+        <x:v>4280</x:v>
+      </x:c>
+      <x:c r="C76" s="51" t="n">
+        <x:v>7535</x:v>
+      </x:c>
+      <x:c r="D76" s="51" t="n">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="E76" s="51" t="n">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="F76" s="51" t="n">
+        <x:v>13013</x:v>
+      </x:c>
+      <x:c r="G76" s="51" t="n">
+        <x:v>13064</x:v>
+      </x:c>
+      <x:c r="H76" s="52" t="n">
+        <x:f>'Riding comparison'!K76</x:f>
+        <x:v>4280</x:v>
+      </x:c>
+      <x:c r="I76" s="52" t="n">
+        <x:f>'Riding comparison'!L76</x:f>
+        <x:v>7535</x:v>
+      </x:c>
+      <x:c r="J76" s="52" t="n">
+        <x:f>'Riding comparison'!M76</x:f>
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="K76" s="52" t="n">
+        <x:f>'Riding comparison'!N76</x:f>
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="L76" s="52" t="n">
+        <x:f>'Riding comparison'!O76</x:f>
+        <x:v>13013</x:v>
+      </x:c>
+      <x:c r="M76" s="52" t="n">
+        <x:f>'Riding comparison'!P76</x:f>
+        <x:v>13064</x:v>
+      </x:c>
+      <x:c r="N76" s="53" t="n">
+        <x:f>H76-B76</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O76" s="53" t="n">
+        <x:f>I76-C76</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P76" s="53" t="n">
+        <x:f>J76-D76</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q76" s="53" t="n">
+        <x:f>K76-E76</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R76" s="53" t="n">
+        <x:f>L76-F76</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S76" s="53" t="n">
+        <x:f>M76-G76</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T76" t="str">
+        <x:f>IF(COUNTIF(N76:S76,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U76" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V76" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="19" customHeight="1">
+      <x:c r="A77" t="str">
+        <x:v>Surrey-Panorama</x:v>
+      </x:c>
+      <x:c r="B77" s="51" t="n">
+        <x:v>4899</x:v>
+      </x:c>
+      <x:c r="C77" s="51" t="n">
+        <x:v>8599</x:v>
+      </x:c>
+      <x:c r="D77" s="51" t="n">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="E77" s="51" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="F77" s="51" t="n">
+        <x:v>14630</x:v>
+      </x:c>
+      <x:c r="G77" s="51" t="n">
+        <x:v>14645</x:v>
+      </x:c>
+      <x:c r="H77" s="52" t="n">
+        <x:f>'Riding comparison'!K77</x:f>
+        <x:v>4899</x:v>
+      </x:c>
+      <x:c r="I77" s="52" t="n">
+        <x:f>'Riding comparison'!L77</x:f>
+        <x:v>8599</x:v>
+      </x:c>
+      <x:c r="J77" s="52" t="n">
+        <x:f>'Riding comparison'!M77</x:f>
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="K77" s="52" t="n">
+        <x:f>'Riding comparison'!N77</x:f>
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="L77" s="52" t="n">
+        <x:f>'Riding comparison'!O77</x:f>
+        <x:v>14630</x:v>
+      </x:c>
+      <x:c r="M77" s="52" t="n">
+        <x:f>'Riding comparison'!P77</x:f>
+        <x:v>14645</x:v>
+      </x:c>
+      <x:c r="N77" s="53" t="n">
+        <x:f>H77-B77</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O77" s="53" t="n">
+        <x:f>I77-C77</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P77" s="53" t="n">
+        <x:f>J77-D77</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q77" s="53" t="n">
+        <x:f>K77-E77</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R77" s="53" t="n">
+        <x:f>L77-F77</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S77" s="53" t="n">
+        <x:f>M77-G77</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T77" t="str">
+        <x:f>IF(COUNTIF(N77:S77,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U77" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V77" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="19" customHeight="1">
+      <x:c r="A78" t="str">
+        <x:v>Surrey-Serpentine River</x:v>
+      </x:c>
+      <x:c r="B78" s="51" t="n">
+        <x:v>5679</x:v>
+      </x:c>
+      <x:c r="C78" s="51" t="n">
+        <x:v>10114</x:v>
+      </x:c>
+      <x:c r="D78" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E78" s="51" t="n">
+        <x:v>1610</x:v>
+      </x:c>
+      <x:c r="F78" s="51" t="n">
+        <x:v>17403</x:v>
+      </x:c>
+      <x:c r="G78" s="51" t="n">
+        <x:v>17439</x:v>
+      </x:c>
+      <x:c r="H78" s="52" t="n">
+        <x:f>'Riding comparison'!K78</x:f>
+        <x:v>5679</x:v>
+      </x:c>
+      <x:c r="I78" s="52" t="n">
+        <x:f>'Riding comparison'!L78</x:f>
+        <x:v>10114</x:v>
+      </x:c>
+      <x:c r="J78" s="52" t="n">
+        <x:f>'Riding comparison'!M78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K78" s="52" t="n">
+        <x:f>'Riding comparison'!N78</x:f>
+        <x:v>1610</x:v>
+      </x:c>
+      <x:c r="L78" s="52" t="n">
+        <x:f>'Riding comparison'!O78</x:f>
+        <x:v>17403</x:v>
+      </x:c>
+      <x:c r="M78" s="52" t="n">
+        <x:f>'Riding comparison'!P78</x:f>
+        <x:v>17439</x:v>
+      </x:c>
+      <x:c r="N78" s="53" t="n">
+        <x:f>H78-B78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O78" s="53" t="n">
+        <x:f>I78-C78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P78" s="53" t="n">
+        <x:f>J78-D78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q78" s="53" t="n">
+        <x:f>K78-E78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R78" s="53" t="n">
+        <x:f>L78-F78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S78" s="53" t="n">
+        <x:f>M78-G78</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T78" t="str">
+        <x:f>IF(COUNTIF(N78:S78,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U78" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V78" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="19" customHeight="1">
+      <x:c r="A79" t="str">
+        <x:v>Surrey South</x:v>
+      </x:c>
+      <x:c r="B79" s="51" t="n">
+        <x:v>4535</x:v>
+      </x:c>
+      <x:c r="C79" s="51" t="n">
+        <x:v>12557</x:v>
+      </x:c>
+      <x:c r="D79" s="51" t="n">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="E79" s="51" t="n">
+        <x:v>2340</x:v>
+      </x:c>
+      <x:c r="F79" s="51" t="n">
+        <x:v>20453</x:v>
+      </x:c>
+      <x:c r="G79" s="51" t="n">
+        <x:v>20466</x:v>
+      </x:c>
+      <x:c r="H79" s="52" t="n">
+        <x:f>'Riding comparison'!K79</x:f>
+        <x:v>4535</x:v>
+      </x:c>
+      <x:c r="I79" s="52" t="n">
+        <x:f>'Riding comparison'!L79</x:f>
+        <x:v>12557</x:v>
+      </x:c>
+      <x:c r="J79" s="52" t="n">
+        <x:f>'Riding comparison'!M79</x:f>
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="K79" s="52" t="n">
+        <x:f>'Riding comparison'!N79</x:f>
+        <x:v>2340</x:v>
+      </x:c>
+      <x:c r="L79" s="52" t="n">
+        <x:f>'Riding comparison'!O79</x:f>
+        <x:v>20453</x:v>
+      </x:c>
+      <x:c r="M79" s="52" t="n">
+        <x:f>'Riding comparison'!P79</x:f>
+        <x:v>20466</x:v>
+      </x:c>
+      <x:c r="N79" s="53" t="n">
+        <x:f>H79-B79</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O79" s="53" t="n">
+        <x:f>I79-C79</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P79" s="53" t="n">
+        <x:f>J79-D79</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q79" s="53" t="n">
+        <x:f>K79-E79</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R79" s="53" t="n">
+        <x:f>L79-F79</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S79" s="53" t="n">
+        <x:f>M79-G79</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T79" t="str">
+        <x:f>IF(COUNTIF(N79:S79,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U79" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V79" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="19" customHeight="1">
+      <x:c r="A80" t="str">
+        <x:v>Surrey-White Rock</x:v>
+      </x:c>
+      <x:c r="B80" s="51" t="n">
+        <x:v>7153</x:v>
+      </x:c>
+      <x:c r="C80" s="51" t="n">
+        <x:v>14386</x:v>
+      </x:c>
+      <x:c r="D80" s="51" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E80" s="51" t="n">
+        <x:v>1294</x:v>
+      </x:c>
+      <x:c r="F80" s="51" t="n">
+        <x:v>24733</x:v>
+      </x:c>
+      <x:c r="G80" s="51" t="n">
+        <x:v>24766</x:v>
+      </x:c>
+      <x:c r="H80" s="52" t="n">
+        <x:f>'Riding comparison'!K80</x:f>
+        <x:v>7153</x:v>
+      </x:c>
+      <x:c r="I80" s="52" t="n">
+        <x:f>'Riding comparison'!L80</x:f>
+        <x:v>14386</x:v>
+      </x:c>
+      <x:c r="J80" s="52" t="n">
+        <x:f>'Riding comparison'!M80</x:f>
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="K80" s="52" t="n">
+        <x:f>'Riding comparison'!N80</x:f>
+        <x:v>1294</x:v>
+      </x:c>
+      <x:c r="L80" s="52" t="n">
+        <x:f>'Riding comparison'!O80</x:f>
+        <x:v>24733</x:v>
+      </x:c>
+      <x:c r="M80" s="52" t="n">
+        <x:f>'Riding comparison'!P80</x:f>
+        <x:v>24766</x:v>
+      </x:c>
+      <x:c r="N80" s="53" t="n">
+        <x:f>H80-B80</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O80" s="53" t="n">
+        <x:f>I80-C80</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P80" s="53" t="n">
+        <x:f>J80-D80</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q80" s="53" t="n">
+        <x:f>K80-E80</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R80" s="53" t="n">
+        <x:f>L80-F80</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S80" s="53" t="n">
+        <x:f>M80-G80</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T80" t="str">
+        <x:f>IF(COUNTIF(N80:S80,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U80" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V80" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="19" customHeight="1">
+      <x:c r="A81" t="str">
+        <x:v>Vancouver-Fraserview</x:v>
+      </x:c>
+      <x:c r="B81" s="51" t="n">
+        <x:v>6769</x:v>
+      </x:c>
+      <x:c r="C81" s="51" t="n">
+        <x:v>7156</x:v>
+      </x:c>
+      <x:c r="D81" s="51" t="n">
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="E81" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F81" s="51" t="n">
+        <x:v>16227</x:v>
+      </x:c>
+      <x:c r="G81" s="51" t="n">
+        <x:v>16253</x:v>
+      </x:c>
+      <x:c r="H81" s="52" t="n">
+        <x:f>'Riding comparison'!K81</x:f>
+        <x:v>6769</x:v>
+      </x:c>
+      <x:c r="I81" s="52" t="n">
+        <x:f>'Riding comparison'!L81</x:f>
+        <x:v>7156</x:v>
+      </x:c>
+      <x:c r="J81" s="52" t="n">
+        <x:f>'Riding comparison'!M81</x:f>
+        <x:v>2302</x:v>
+      </x:c>
+      <x:c r="K81" s="52" t="n">
+        <x:f>'Riding comparison'!N81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L81" s="52" t="n">
+        <x:f>'Riding comparison'!O81</x:f>
+        <x:v>16227</x:v>
+      </x:c>
+      <x:c r="M81" s="52" t="n">
+        <x:f>'Riding comparison'!P81</x:f>
+        <x:v>16253</x:v>
+      </x:c>
+      <x:c r="N81" s="53" t="n">
+        <x:f>H81-B81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O81" s="53" t="n">
+        <x:f>I81-C81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P81" s="53" t="n">
+        <x:f>J81-D81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q81" s="53" t="n">
+        <x:f>K81-E81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R81" s="53" t="n">
+        <x:f>L81-F81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S81" s="53" t="n">
+        <x:f>M81-G81</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T81" t="str">
+        <x:f>IF(COUNTIF(N81:S81,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U81" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V81" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="19" customHeight="1">
+      <x:c r="A82" t="str">
+        <x:v>Vancouver-Hastings</x:v>
+      </x:c>
+      <x:c r="B82" s="51" t="n">
+        <x:v>9707</x:v>
+      </x:c>
+      <x:c r="C82" s="51" t="n">
+        <x:v>4795</x:v>
+      </x:c>
+      <x:c r="D82" s="51" t="n">
+        <x:v>3576</x:v>
+      </x:c>
+      <x:c r="E82" s="51" t="n">
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="F82" s="51" t="n">
+        <x:v>18929</x:v>
+      </x:c>
+      <x:c r="G82" s="51" t="n">
+        <x:v>18973</x:v>
+      </x:c>
+      <x:c r="H82" s="52" t="n">
+        <x:f>'Riding comparison'!K82</x:f>
+        <x:v>9707</x:v>
+      </x:c>
+      <x:c r="I82" s="52" t="n">
+        <x:f>'Riding comparison'!L82</x:f>
+        <x:v>4795</x:v>
+      </x:c>
+      <x:c r="J82" s="52" t="n">
+        <x:f>'Riding comparison'!M82</x:f>
+        <x:v>3576</x:v>
+      </x:c>
+      <x:c r="K82" s="52" t="n">
+        <x:f>'Riding comparison'!N82</x:f>
+        <x:v>851</x:v>
+      </x:c>
+      <x:c r="L82" s="52" t="n">
+        <x:f>'Riding comparison'!O82</x:f>
+        <x:v>18929</x:v>
+      </x:c>
+      <x:c r="M82" s="52" t="n">
+        <x:f>'Riding comparison'!P82</x:f>
+        <x:v>18973</x:v>
+      </x:c>
+      <x:c r="N82" s="53" t="n">
+        <x:f>H82-B82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O82" s="53" t="n">
+        <x:f>I82-C82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P82" s="53" t="n">
+        <x:f>J82-D82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q82" s="53" t="n">
+        <x:f>K82-E82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R82" s="53" t="n">
+        <x:f>L82-F82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S82" s="53" t="n">
+        <x:f>M82-G82</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T82" t="str">
+        <x:f>IF(COUNTIF(N82:S82,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U82" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V82" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="19" customHeight="1">
+      <x:c r="A83" t="str">
+        <x:v>Vancouver-Kensington</x:v>
+      </x:c>
+      <x:c r="B83" s="51" t="n">
+        <x:v>7278</x:v>
+      </x:c>
+      <x:c r="C83" s="51" t="n">
+        <x:v>5599</x:v>
+      </x:c>
+      <x:c r="D83" s="51" t="n">
+        <x:v>2716</x:v>
+      </x:c>
+      <x:c r="E83" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F83" s="51" t="n">
+        <x:v>15593</x:v>
+      </x:c>
+      <x:c r="G83" s="51" t="n">
+        <x:v>15621</x:v>
+      </x:c>
+      <x:c r="H83" s="52" t="n">
+        <x:f>'Riding comparison'!K83</x:f>
+        <x:v>7278</x:v>
+      </x:c>
+      <x:c r="I83" s="52" t="n">
+        <x:f>'Riding comparison'!L83</x:f>
+        <x:v>5599</x:v>
+      </x:c>
+      <x:c r="J83" s="52" t="n">
+        <x:f>'Riding comparison'!M83</x:f>
+        <x:v>2716</x:v>
+      </x:c>
+      <x:c r="K83" s="52" t="n">
+        <x:f>'Riding comparison'!N83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83" s="52" t="n">
+        <x:f>'Riding comparison'!O83</x:f>
+        <x:v>15593</x:v>
+      </x:c>
+      <x:c r="M83" s="52" t="n">
+        <x:f>'Riding comparison'!P83</x:f>
+        <x:v>15621</x:v>
+      </x:c>
+      <x:c r="N83" s="53" t="n">
+        <x:f>H83-B83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O83" s="53" t="n">
+        <x:f>I83-C83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P83" s="53" t="n">
+        <x:f>J83-D83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q83" s="53" t="n">
+        <x:f>K83-E83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R83" s="53" t="n">
+        <x:f>L83-F83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S83" s="53" t="n">
+        <x:f>M83-G83</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T83" t="str">
+        <x:f>IF(COUNTIF(N83:S83,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U83" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V83" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="19" customHeight="1">
+      <x:c r="A84" t="str">
+        <x:v>Vancouver-Langara</x:v>
+      </x:c>
+      <x:c r="B84" s="51" t="n">
+        <x:v>5544</x:v>
+      </x:c>
+      <x:c r="C84" s="51" t="n">
+        <x:v>7194</x:v>
+      </x:c>
+      <x:c r="D84" s="51" t="n">
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="E84" s="51" t="n">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="F84" s="51" t="n">
+        <x:v>14223</x:v>
+      </x:c>
+      <x:c r="G84" s="51" t="n">
+        <x:v>14245</x:v>
+      </x:c>
+      <x:c r="H84" s="52" t="n">
+        <x:f>'Riding comparison'!K84</x:f>
+        <x:v>5544</x:v>
+      </x:c>
+      <x:c r="I84" s="52" t="n">
+        <x:f>'Riding comparison'!L84</x:f>
+        <x:v>7194</x:v>
+      </x:c>
+      <x:c r="J84" s="52" t="n">
+        <x:f>'Riding comparison'!M84</x:f>
+        <x:v>1123</x:v>
+      </x:c>
+      <x:c r="K84" s="52" t="n">
+        <x:f>'Riding comparison'!N84</x:f>
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="L84" s="52" t="n">
+        <x:f>'Riding comparison'!O84</x:f>
+        <x:v>14223</x:v>
+      </x:c>
+      <x:c r="M84" s="52" t="n">
+        <x:f>'Riding comparison'!P84</x:f>
+        <x:v>14245</x:v>
+      </x:c>
+      <x:c r="N84" s="53" t="n">
+        <x:f>H84-B84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O84" s="53" t="n">
+        <x:f>I84-C84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P84" s="53" t="n">
+        <x:f>J84-D84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q84" s="53" t="n">
+        <x:f>K84-E84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R84" s="53" t="n">
+        <x:f>L84-F84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S84" s="53" t="n">
+        <x:f>M84-G84</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T84" t="str">
+        <x:f>IF(COUNTIF(N84:S84,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U84" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V84" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="19" customHeight="1">
+      <x:c r="A85" t="str">
+        <x:v>Vancouver-Little Mountain</x:v>
+      </x:c>
+      <x:c r="B85" s="51" t="n">
+        <x:v>10145</x:v>
+      </x:c>
+      <x:c r="C85" s="51" t="n">
+        <x:v>7075</x:v>
+      </x:c>
+      <x:c r="D85" s="51" t="n">
+        <x:v>3424</x:v>
+      </x:c>
+      <x:c r="E85" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F85" s="51" t="n">
+        <x:v>20644</x:v>
+      </x:c>
+      <x:c r="G85" s="51" t="n">
+        <x:v>20688</x:v>
+      </x:c>
+      <x:c r="H85" s="52" t="n">
+        <x:f>'Riding comparison'!K85</x:f>
+        <x:v>10145</x:v>
+      </x:c>
+      <x:c r="I85" s="52" t="n">
+        <x:f>'Riding comparison'!L85</x:f>
+        <x:v>7075</x:v>
+      </x:c>
+      <x:c r="J85" s="52" t="n">
+        <x:f>'Riding comparison'!M85</x:f>
+        <x:v>3424</x:v>
+      </x:c>
+      <x:c r="K85" s="52" t="n">
+        <x:f>'Riding comparison'!N85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L85" s="52" t="n">
+        <x:f>'Riding comparison'!O85</x:f>
+        <x:v>20644</x:v>
+      </x:c>
+      <x:c r="M85" s="52" t="n">
+        <x:f>'Riding comparison'!P85</x:f>
+        <x:v>20688</x:v>
+      </x:c>
+      <x:c r="N85" s="53" t="n">
+        <x:f>H85-B85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O85" s="53" t="n">
+        <x:f>I85-C85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P85" s="53" t="n">
+        <x:f>J85-D85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q85" s="53" t="n">
+        <x:f>K85-E85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R85" s="53" t="n">
+        <x:f>L85-F85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S85" s="53" t="n">
+        <x:f>M85-G85</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T85" t="str">
+        <x:f>IF(COUNTIF(N85:S85,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U85" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V85" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="19" customHeight="1">
+      <x:c r="A86" t="str">
+        <x:v>Vancouver-Point Grey</x:v>
+      </x:c>
+      <x:c r="B86" s="51" t="n">
+        <x:v>7811</x:v>
+      </x:c>
+      <x:c r="C86" s="51" t="n">
+        <x:v>7273</x:v>
+      </x:c>
+      <x:c r="D86" s="51" t="n">
+        <x:v>2448</x:v>
+      </x:c>
+      <x:c r="E86" s="51" t="n">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="F86" s="51" t="n">
+        <x:v>18179</x:v>
+      </x:c>
+      <x:c r="G86" s="51" t="n">
+        <x:v>18199</x:v>
+      </x:c>
+      <x:c r="H86" s="52" t="n">
+        <x:f>'Riding comparison'!K86</x:f>
+        <x:v>7811</x:v>
+      </x:c>
+      <x:c r="I86" s="52" t="n">
+        <x:f>'Riding comparison'!L86</x:f>
+        <x:v>7273</x:v>
+      </x:c>
+      <x:c r="J86" s="52" t="n">
+        <x:f>'Riding comparison'!M86</x:f>
+        <x:v>2448</x:v>
+      </x:c>
+      <x:c r="K86" s="52" t="n">
+        <x:f>'Riding comparison'!N86</x:f>
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="L86" s="52" t="n">
+        <x:f>'Riding comparison'!O86</x:f>
+        <x:v>18179</x:v>
+      </x:c>
+      <x:c r="M86" s="52" t="n">
+        <x:f>'Riding comparison'!P86</x:f>
+        <x:v>18199</x:v>
+      </x:c>
+      <x:c r="N86" s="53" t="n">
+        <x:f>H86-B86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O86" s="53" t="n">
+        <x:f>I86-C86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P86" s="53" t="n">
+        <x:f>J86-D86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q86" s="53" t="n">
+        <x:f>K86-E86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R86" s="53" t="n">
+        <x:f>L86-F86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S86" s="53" t="n">
+        <x:f>M86-G86</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T86" t="str">
+        <x:f>IF(COUNTIF(N86:S86,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U86" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V86" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="19" customHeight="1">
+      <x:c r="A87" t="str">
+        <x:v>Vancouver-Quilchena</x:v>
+      </x:c>
+      <x:c r="B87" s="51" t="n">
+        <x:v>5269</x:v>
+      </x:c>
+      <x:c r="C87" s="51" t="n">
+        <x:v>10956</x:v>
+      </x:c>
+      <x:c r="D87" s="51" t="n">
+        <x:v>1844</x:v>
+      </x:c>
+      <x:c r="E87" s="51" t="n">
+        <x:v>1843</x:v>
+      </x:c>
+      <x:c r="F87" s="51" t="n">
+        <x:v>19912</x:v>
+      </x:c>
+      <x:c r="G87" s="51" t="n">
+        <x:v>19939</x:v>
+      </x:c>
+      <x:c r="H87" s="52" t="n">
+        <x:f>'Riding comparison'!K87</x:f>
+        <x:v>5269</x:v>
+      </x:c>
+      <x:c r="I87" s="52" t="n">
+        <x:f>'Riding comparison'!L87</x:f>
+        <x:v>10956</x:v>
+      </x:c>
+      <x:c r="J87" s="52" t="n">
+        <x:f>'Riding comparison'!M87</x:f>
+        <x:v>1844</x:v>
+      </x:c>
+      <x:c r="K87" s="52" t="n">
+        <x:f>'Riding comparison'!N87</x:f>
+        <x:v>1843</x:v>
+      </x:c>
+      <x:c r="L87" s="52" t="n">
+        <x:f>'Riding comparison'!O87</x:f>
+        <x:v>19912</x:v>
+      </x:c>
+      <x:c r="M87" s="52" t="n">
+        <x:f>'Riding comparison'!P87</x:f>
+        <x:v>19939</x:v>
+      </x:c>
+      <x:c r="N87" s="53" t="n">
+        <x:f>H87-B87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O87" s="53" t="n">
+        <x:f>I87-C87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P87" s="53" t="n">
+        <x:f>J87-D87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q87" s="53" t="n">
+        <x:f>K87-E87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R87" s="53" t="n">
+        <x:f>L87-F87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S87" s="53" t="n">
+        <x:f>M87-G87</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T87" t="str">
+        <x:f>IF(COUNTIF(N87:S87,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U87" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V87" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="19" customHeight="1">
+      <x:c r="A88" t="str">
+        <x:v>Vancouver-Renfrew</x:v>
+      </x:c>
+      <x:c r="B88" s="51" t="n">
+        <x:v>7708</x:v>
+      </x:c>
+      <x:c r="C88" s="51" t="n">
+        <x:v>4409</x:v>
+      </x:c>
+      <x:c r="D88" s="51" t="n">
+        <x:v>1675</x:v>
+      </x:c>
+      <x:c r="E88" s="51" t="n">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="F88" s="51" t="n">
+        <x:v>14106</x:v>
+      </x:c>
+      <x:c r="G88" s="51" t="n">
+        <x:v>14158</x:v>
+      </x:c>
+      <x:c r="H88" s="52" t="n">
+        <x:f>'Riding comparison'!K88</x:f>
+        <x:v>7708</x:v>
+      </x:c>
+      <x:c r="I88" s="52" t="n">
+        <x:f>'Riding comparison'!L88</x:f>
+        <x:v>4409</x:v>
+      </x:c>
+      <x:c r="J88" s="52" t="n">
+        <x:f>'Riding comparison'!M88</x:f>
+        <x:v>1675</x:v>
+      </x:c>
+      <x:c r="K88" s="52" t="n">
+        <x:f>'Riding comparison'!N88</x:f>
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="L88" s="52" t="n">
+        <x:f>'Riding comparison'!O88</x:f>
+        <x:v>14106</x:v>
+      </x:c>
+      <x:c r="M88" s="52" t="n">
+        <x:f>'Riding comparison'!P88</x:f>
+        <x:v>14158</x:v>
+      </x:c>
+      <x:c r="N88" s="53" t="n">
+        <x:f>H88-B88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O88" s="53" t="n">
+        <x:f>I88-C88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P88" s="53" t="n">
+        <x:f>J88-D88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q88" s="53" t="n">
+        <x:f>K88-E88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R88" s="53" t="n">
+        <x:f>L88-F88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S88" s="53" t="n">
+        <x:f>M88-G88</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T88" t="str">
+        <x:f>IF(COUNTIF(N88:S88,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U88" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V88" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="19" customHeight="1">
+      <x:c r="A89" t="str">
+        <x:v>Vancouver-South Granville</x:v>
+      </x:c>
+      <x:c r="B89" s="51" t="n">
+        <x:v>10427</x:v>
+      </x:c>
+      <x:c r="C89" s="51" t="n">
+        <x:v>6489</x:v>
+      </x:c>
+      <x:c r="D89" s="51" t="n">
+        <x:v>4151</x:v>
+      </x:c>
+      <x:c r="E89" s="51" t="n">
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="F89" s="51" t="n">
+        <x:v>21984</x:v>
+      </x:c>
+      <x:c r="G89" s="51" t="n">
+        <x:v>22002</x:v>
+      </x:c>
+      <x:c r="H89" s="52" t="n">
+        <x:f>'Riding comparison'!K89</x:f>
+        <x:v>10427</x:v>
+      </x:c>
+      <x:c r="I89" s="52" t="n">
+        <x:f>'Riding comparison'!L89</x:f>
+        <x:v>6489</x:v>
+      </x:c>
+      <x:c r="J89" s="52" t="n">
+        <x:f>'Riding comparison'!M89</x:f>
+        <x:v>4151</x:v>
+      </x:c>
+      <x:c r="K89" s="52" t="n">
+        <x:f>'Riding comparison'!N89</x:f>
+        <x:v>917</x:v>
+      </x:c>
+      <x:c r="L89" s="52" t="n">
+        <x:f>'Riding comparison'!O89</x:f>
+        <x:v>21984</x:v>
+      </x:c>
+      <x:c r="M89" s="52" t="n">
+        <x:f>'Riding comparison'!P89</x:f>
+        <x:v>22002</x:v>
+      </x:c>
+      <x:c r="N89" s="53" t="n">
+        <x:f>H89-B89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O89" s="53" t="n">
+        <x:f>I89-C89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P89" s="53" t="n">
+        <x:f>J89-D89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q89" s="53" t="n">
+        <x:f>K89-E89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R89" s="53" t="n">
+        <x:f>L89-F89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S89" s="53" t="n">
+        <x:f>M89-G89</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T89" t="str">
+        <x:f>IF(COUNTIF(N89:S89,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U89" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V89" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="19" customHeight="1">
+      <x:c r="A90" t="str">
+        <x:v>Vancouver-Strathcona</x:v>
+      </x:c>
+      <x:c r="B90" s="51" t="n">
+        <x:v>9484</x:v>
+      </x:c>
+      <x:c r="C90" s="51" t="n">
+        <x:v>2531</x:v>
+      </x:c>
+      <x:c r="D90" s="51" t="n">
+        <x:v>4985</x:v>
+      </x:c>
+      <x:c r="E90" s="51" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="F90" s="51" t="n">
+        <x:v>17216</x:v>
+      </x:c>
+      <x:c r="G90" s="51" t="n">
+        <x:v>17309</x:v>
+      </x:c>
+      <x:c r="H90" s="52" t="n">
+        <x:f>'Riding comparison'!K90</x:f>
+        <x:v>9484</x:v>
+      </x:c>
+      <x:c r="I90" s="52" t="n">
+        <x:f>'Riding comparison'!L90</x:f>
+        <x:v>2531</x:v>
+      </x:c>
+      <x:c r="J90" s="52" t="n">
+        <x:f>'Riding comparison'!M90</x:f>
+        <x:v>4985</x:v>
+      </x:c>
+      <x:c r="K90" s="52" t="n">
+        <x:f>'Riding comparison'!N90</x:f>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="L90" s="52" t="n">
+        <x:f>'Riding comparison'!O90</x:f>
+        <x:v>17216</x:v>
+      </x:c>
+      <x:c r="M90" s="52" t="n">
+        <x:f>'Riding comparison'!P90</x:f>
+        <x:v>17309</x:v>
+      </x:c>
+      <x:c r="N90" s="53" t="n">
+        <x:f>H90-B90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O90" s="53" t="n">
+        <x:f>I90-C90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P90" s="53" t="n">
+        <x:f>J90-D90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q90" s="53" t="n">
+        <x:f>K90-E90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R90" s="53" t="n">
+        <x:f>L90-F90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S90" s="53" t="n">
+        <x:f>M90-G90</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T90" t="str">
+        <x:f>IF(COUNTIF(N90:S90,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U90" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V90" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="19" customHeight="1">
+      <x:c r="A91" t="str">
+        <x:v>Vancouver-West End</x:v>
+      </x:c>
+      <x:c r="B91" s="51" t="n">
+        <x:v>8661</x:v>
+      </x:c>
+      <x:c r="C91" s="51" t="n">
+        <x:v>5115</x:v>
+      </x:c>
+      <x:c r="D91" s="51" t="n">
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="E91" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F91" s="51" t="n">
+        <x:v>16777</x:v>
+      </x:c>
+      <x:c r="G91" s="51" t="n">
+        <x:v>16804</x:v>
+      </x:c>
+      <x:c r="H91" s="52" t="n">
+        <x:f>'Riding comparison'!K91</x:f>
+        <x:v>8661</x:v>
+      </x:c>
+      <x:c r="I91" s="52" t="n">
+        <x:f>'Riding comparison'!L91</x:f>
+        <x:v>5115</x:v>
+      </x:c>
+      <x:c r="J91" s="52" t="n">
+        <x:f>'Riding comparison'!M91</x:f>
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="K91" s="52" t="n">
+        <x:f>'Riding comparison'!N91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L91" s="52" t="n">
+        <x:f>'Riding comparison'!O91</x:f>
+        <x:v>16777</x:v>
+      </x:c>
+      <x:c r="M91" s="52" t="n">
+        <x:f>'Riding comparison'!P91</x:f>
+        <x:v>16804</x:v>
+      </x:c>
+      <x:c r="N91" s="53" t="n">
+        <x:f>H91-B91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O91" s="53" t="n">
+        <x:f>I91-C91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P91" s="53" t="n">
+        <x:f>J91-D91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q91" s="53" t="n">
+        <x:f>K91-E91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R91" s="53" t="n">
+        <x:f>L91-F91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S91" s="53" t="n">
+        <x:f>M91-G91</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T91" t="str">
+        <x:f>IF(COUNTIF(N91:S91,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U91" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V91" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="19" customHeight="1">
+      <x:c r="A92" t="str">
+        <x:v>Vancouver-Yaletown</x:v>
+      </x:c>
+      <x:c r="B92" s="51" t="n">
+        <x:v>5870</x:v>
+      </x:c>
+      <x:c r="C92" s="51" t="n">
+        <x:v>6714</x:v>
+      </x:c>
+      <x:c r="D92" s="51" t="n">
+        <x:v>1253</x:v>
+      </x:c>
+      <x:c r="E92" s="51" t="n">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="F92" s="51" t="n">
+        <x:v>14319</x:v>
+      </x:c>
+      <x:c r="G92" s="51" t="n">
+        <x:v>14391</x:v>
+      </x:c>
+      <x:c r="H92" s="52" t="n">
+        <x:f>'Riding comparison'!K92</x:f>
+        <x:v>5870</x:v>
+      </x:c>
+      <x:c r="I92" s="52" t="n">
+        <x:f>'Riding comparison'!L92</x:f>
+        <x:v>6714</x:v>
+      </x:c>
+      <x:c r="J92" s="52" t="n">
+        <x:f>'Riding comparison'!M92</x:f>
+        <x:v>1253</x:v>
+      </x:c>
+      <x:c r="K92" s="52" t="n">
+        <x:f>'Riding comparison'!N92</x:f>
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="L92" s="52" t="n">
+        <x:f>'Riding comparison'!O92</x:f>
+        <x:v>14319</x:v>
+      </x:c>
+      <x:c r="M92" s="52" t="n">
+        <x:f>'Riding comparison'!P92</x:f>
+        <x:v>14391</x:v>
+      </x:c>
+      <x:c r="N92" s="53" t="n">
+        <x:f>H92-B92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O92" s="53" t="n">
+        <x:f>I92-C92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P92" s="53" t="n">
+        <x:f>J92-D92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q92" s="53" t="n">
+        <x:f>K92-E92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R92" s="53" t="n">
+        <x:f>L92-F92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S92" s="53" t="n">
+        <x:f>M92-G92</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T92" t="str">
+        <x:f>IF(COUNTIF(N92:S92,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U92" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V92" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="19" customHeight="1">
+      <x:c r="A93" t="str">
+        <x:v>Vernon-Lumby</x:v>
+      </x:c>
+      <x:c r="B93" s="51" t="n">
+        <x:v>9448</x:v>
+      </x:c>
+      <x:c r="C93" s="51" t="n">
+        <x:v>12702</x:v>
+      </x:c>
+      <x:c r="D93" s="51" t="n">
+        <x:v>1729</x:v>
+      </x:c>
+      <x:c r="E93" s="51" t="n">
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="F93" s="51" t="n">
+        <x:v>24999</x:v>
+      </x:c>
+      <x:c r="G93" s="51" t="n">
+        <x:v>25031</x:v>
+      </x:c>
+      <x:c r="H93" s="52" t="n">
+        <x:f>'Riding comparison'!K93</x:f>
+        <x:v>9448</x:v>
+      </x:c>
+      <x:c r="I93" s="52" t="n">
+        <x:f>'Riding comparison'!L93</x:f>
+        <x:v>12702</x:v>
+      </x:c>
+      <x:c r="J93" s="52" t="n">
+        <x:f>'Riding comparison'!M93</x:f>
+        <x:v>1729</x:v>
+      </x:c>
+      <x:c r="K93" s="52" t="n">
+        <x:f>'Riding comparison'!N93</x:f>
+        <x:v>1120</x:v>
+      </x:c>
+      <x:c r="L93" s="52" t="n">
+        <x:f>'Riding comparison'!O93</x:f>
+        <x:v>24999</x:v>
+      </x:c>
+      <x:c r="M93" s="52" t="n">
+        <x:f>'Riding comparison'!P93</x:f>
+        <x:v>25031</x:v>
+      </x:c>
+      <x:c r="N93" s="53" t="n">
+        <x:f>H93-B93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O93" s="53" t="n">
+        <x:f>I93-C93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P93" s="53" t="n">
+        <x:f>J93-D93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q93" s="53" t="n">
+        <x:f>K93-E93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R93" s="53" t="n">
+        <x:f>L93-F93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S93" s="53" t="n">
+        <x:f>M93-G93</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T93" t="str">
+        <x:f>IF(COUNTIF(N93:S93,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U93" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V93" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="19" customHeight="1">
+      <x:c r="A94" t="str">
+        <x:v>Victoria-Beacon Hill</x:v>
+      </x:c>
+      <x:c r="B94" s="51" t="n">
+        <x:v>10407</x:v>
+      </x:c>
+      <x:c r="C94" s="51" t="n">
+        <x:v>3193</x:v>
+      </x:c>
+      <x:c r="D94" s="51" t="n">
+        <x:v>9189</x:v>
+      </x:c>
+      <x:c r="E94" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F94" s="51" t="n">
+        <x:v>22789</x:v>
+      </x:c>
+      <x:c r="G94" s="51" t="n">
+        <x:v>22888</x:v>
+      </x:c>
+      <x:c r="H94" s="52" t="n">
+        <x:f>'Riding comparison'!K94</x:f>
+        <x:v>10407</x:v>
+      </x:c>
+      <x:c r="I94" s="52" t="n">
+        <x:f>'Riding comparison'!L94</x:f>
+        <x:v>3193</x:v>
+      </x:c>
+      <x:c r="J94" s="52" t="n">
+        <x:f>'Riding comparison'!M94</x:f>
+        <x:v>9189</x:v>
+      </x:c>
+      <x:c r="K94" s="52" t="n">
+        <x:f>'Riding comparison'!N94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L94" s="52" t="n">
+        <x:f>'Riding comparison'!O94</x:f>
+        <x:v>22789</x:v>
+      </x:c>
+      <x:c r="M94" s="52" t="n">
+        <x:f>'Riding comparison'!P94</x:f>
+        <x:v>22888</x:v>
+      </x:c>
+      <x:c r="N94" s="53" t="n">
+        <x:f>H94-B94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O94" s="53" t="n">
+        <x:f>I94-C94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P94" s="53" t="n">
+        <x:f>J94-D94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q94" s="53" t="n">
+        <x:f>K94-E94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R94" s="53" t="n">
+        <x:f>L94-F94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S94" s="53" t="n">
+        <x:f>M94-G94</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T94" t="str">
+        <x:f>IF(COUNTIF(N94:S94,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U94" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V94" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="19" customHeight="1">
+      <x:c r="A95" t="str">
+        <x:v>Victoria-Swan Lake</x:v>
+      </x:c>
+      <x:c r="B95" s="51" t="n">
+        <x:v>9250</x:v>
+      </x:c>
+      <x:c r="C95" s="51" t="n">
+        <x:v>4475</x:v>
+      </x:c>
+      <x:c r="D95" s="51" t="n">
+        <x:v>7470</x:v>
+      </x:c>
+      <x:c r="E95" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F95" s="51" t="n">
+        <x:v>21195</x:v>
+      </x:c>
+      <x:c r="G95" s="51" t="n">
+        <x:v>21234</x:v>
+      </x:c>
+      <x:c r="H95" s="52" t="n">
+        <x:f>'Riding comparison'!K95</x:f>
+        <x:v>9250</x:v>
+      </x:c>
+      <x:c r="I95" s="52" t="n">
+        <x:f>'Riding comparison'!L95</x:f>
+        <x:v>4475</x:v>
+      </x:c>
+      <x:c r="J95" s="52" t="n">
+        <x:f>'Riding comparison'!M95</x:f>
+        <x:v>7470</x:v>
+      </x:c>
+      <x:c r="K95" s="52" t="n">
+        <x:f>'Riding comparison'!N95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L95" s="52" t="n">
+        <x:f>'Riding comparison'!O95</x:f>
+        <x:v>21195</x:v>
+      </x:c>
+      <x:c r="M95" s="52" t="n">
+        <x:f>'Riding comparison'!P95</x:f>
+        <x:v>21234</x:v>
+      </x:c>
+      <x:c r="N95" s="53" t="n">
+        <x:f>H95-B95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O95" s="53" t="n">
+        <x:f>I95-C95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P95" s="53" t="n">
+        <x:f>J95-D95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q95" s="53" t="n">
+        <x:f>K95-E95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R95" s="53" t="n">
+        <x:f>L95-F95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S95" s="53" t="n">
+        <x:f>M95-G95</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T95" t="str">
+        <x:f>IF(COUNTIF(N95:S95,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U95" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V95" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="19" customHeight="1">
+      <x:c r="A96" t="str">
+        <x:v>West Kelowna-Peachland</x:v>
+      </x:c>
+      <x:c r="B96" s="51" t="n">
+        <x:v>6884</x:v>
+      </x:c>
+      <x:c r="C96" s="51" t="n">
+        <x:v>14467</x:v>
+      </x:c>
+      <x:c r="D96" s="51" t="n">
+        <x:v>1847</x:v>
+      </x:c>
+      <x:c r="E96" s="51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F96" s="51" t="n">
+        <x:v>23198</x:v>
+      </x:c>
+      <x:c r="G96" s="51" t="n">
+        <x:v>23248</x:v>
+      </x:c>
+      <x:c r="H96" s="52" t="n">
+        <x:f>'Riding comparison'!K96</x:f>
+        <x:v>6884</x:v>
+      </x:c>
+      <x:c r="I96" s="52" t="n">
+        <x:f>'Riding comparison'!L96</x:f>
+        <x:v>14467</x:v>
+      </x:c>
+      <x:c r="J96" s="52" t="n">
+        <x:f>'Riding comparison'!M96</x:f>
+        <x:v>1847</x:v>
+      </x:c>
+      <x:c r="K96" s="52" t="n">
+        <x:f>'Riding comparison'!N96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L96" s="52" t="n">
+        <x:f>'Riding comparison'!O96</x:f>
+        <x:v>23198</x:v>
+      </x:c>
+      <x:c r="M96" s="52" t="n">
+        <x:f>'Riding comparison'!P96</x:f>
+        <x:v>23248</x:v>
+      </x:c>
+      <x:c r="N96" s="53" t="n">
+        <x:f>H96-B96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O96" s="53" t="n">
+        <x:f>I96-C96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P96" s="53" t="n">
+        <x:f>J96-D96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q96" s="53" t="n">
+        <x:f>K96-E96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R96" s="53" t="n">
+        <x:f>L96-F96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S96" s="53" t="n">
+        <x:f>M96-G96</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T96" t="str">
+        <x:f>IF(COUNTIF(N96:S96,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U96" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V96" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="19" customHeight="1">
+      <x:c r="A97" t="str">
+        <x:v>West Vancouver-Capilano</x:v>
+      </x:c>
+      <x:c r="B97" s="51" t="n">
+        <x:v>4493</x:v>
+      </x:c>
+      <x:c r="C97" s="51" t="n">
+        <x:v>14628</x:v>
+      </x:c>
+      <x:c r="D97" s="51" t="n">
+        <x:v>2360</x:v>
+      </x:c>
+      <x:c r="E97" s="51" t="n">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="F97" s="51" t="n">
+        <x:v>21867</x:v>
+      </x:c>
+      <x:c r="G97" s="51" t="n">
+        <x:v>21903</x:v>
+      </x:c>
+      <x:c r="H97" s="52" t="n">
+        <x:f>'Riding comparison'!K97</x:f>
+        <x:v>4493</x:v>
+      </x:c>
+      <x:c r="I97" s="52" t="n">
+        <x:f>'Riding comparison'!L97</x:f>
+        <x:v>14628</x:v>
+      </x:c>
+      <x:c r="J97" s="52" t="n">
+        <x:f>'Riding comparison'!M97</x:f>
+        <x:v>2360</x:v>
+      </x:c>
+      <x:c r="K97" s="52" t="n">
+        <x:f>'Riding comparison'!N97</x:f>
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="L97" s="52" t="n">
+        <x:f>'Riding comparison'!O97</x:f>
+        <x:v>21867</x:v>
+      </x:c>
+      <x:c r="M97" s="52" t="n">
+        <x:f>'Riding comparison'!P97</x:f>
+        <x:v>21903</x:v>
+      </x:c>
+      <x:c r="N97" s="53" t="n">
+        <x:f>H97-B97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O97" s="53" t="n">
+        <x:f>I97-C97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P97" s="53" t="n">
+        <x:f>J97-D97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q97" s="53" t="n">
+        <x:f>K97-E97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R97" s="53" t="n">
+        <x:f>L97-F97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S97" s="53" t="n">
+        <x:f>M97-G97</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T97" t="str">
+        <x:f>IF(COUNTIF(N97:S97,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U97" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V97" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="19" customHeight="1">
+      <x:c r="A98" t="str">
+        <x:v>West Vancouver-Sea to Sky</x:v>
+      </x:c>
+      <x:c r="B98" s="51" t="n">
+        <x:v>2283</x:v>
+      </x:c>
+      <x:c r="C98" s="51" t="n">
+        <x:v>8478</x:v>
+      </x:c>
+      <x:c r="D98" s="51" t="n">
+        <x:v>10503</x:v>
+      </x:c>
+      <x:c r="E98" s="51" t="n">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="F98" s="51" t="n">
+        <x:v>22082</x:v>
+      </x:c>
+      <x:c r="G98" s="51" t="n">
+        <x:v>22104</x:v>
+      </x:c>
+      <x:c r="H98" s="52" t="n">
+        <x:f>'Riding comparison'!K98</x:f>
+        <x:v>2283</x:v>
+      </x:c>
+      <x:c r="I98" s="52" t="n">
+        <x:f>'Riding comparison'!L98</x:f>
+        <x:v>8478</x:v>
+      </x:c>
+      <x:c r="J98" s="52" t="n">
+        <x:f>'Riding comparison'!M98</x:f>
+        <x:v>10503</x:v>
+      </x:c>
+      <x:c r="K98" s="52" t="n">
+        <x:f>'Riding comparison'!N98</x:f>
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="L98" s="52" t="n">
+        <x:f>'Riding comparison'!O98</x:f>
+        <x:v>22082</x:v>
+      </x:c>
+      <x:c r="M98" s="52" t="n">
+        <x:f>'Riding comparison'!P98</x:f>
+        <x:v>22104</x:v>
+      </x:c>
+      <x:c r="N98" s="53" t="n">
+        <x:f>H98-B98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O98" s="53" t="n">
+        <x:f>I98-C98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P98" s="53" t="n">
+        <x:f>J98-D98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q98" s="53" t="n">
+        <x:f>K98-E98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R98" s="53" t="n">
+        <x:f>L98-F98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S98" s="53" t="n">
+        <x:f>M98-G98</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T98" t="str">
+        <x:f>IF(COUNTIF(N98:S98,"&lt;&gt;0")=0,"UNCHANGED","UPDATED")</x:f>
+        <x:v>UNCHANGED</x:v>
+      </x:c>
+      <x:c r="U98" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+      <x:c r="V98" t="str">
+        <x:v>https://results.elections.bc.ca/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="23" customHeight="1">
+      <x:c r="A100" s="54" t="str">
+        <x:v>Check date</x:v>
+      </x:c>
+      <x:c r="B100" s="54" t="str">
+        <x:v>Data timestamp</x:v>
+      </x:c>
+      <x:c r="C100" s="54" t="str">
+        <x:v>Changed ridings</x:v>
+      </x:c>
+      <x:c r="D100" s="54" t="str">
+        <x:v>Check result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="23" customHeight="1">
+      <x:c r="A101" t="str">
+        <x:v>2026-10-27</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>2026-10-26 10:34</x:v>
+      </x:c>
+      <x:c r="C101" t="n">
+        <x:f>COUNTIF(T6:T98,"UPDATED")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>No new release</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="23" customHeight="1">
+      <x:c r="A102" t="str">
+        <x:v>Final count</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>6-10 Nov 2026</x:v>
+      </x:c>
+      <x:c r="C102"/>
+      <x:c r="D102" t="str">
+        <x:v>Planned, not yet published</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="23" customHeight="1">
+      <x:c r="A103" t="str">
+        <x:v>Caveat</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>Any new ballot counts may alter close seats</x:v>
+      </x:c>
+      <x:c r="C103"/>
+      <x:c r="D103" t="str">
+        <x:v>Not certified</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:V1"/>
+    <x:mergeCell ref="A2:V2"/>
+    <x:mergeCell ref="A3:V3"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="N6:S98">
+    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/client/public/election-data/BC_Election_2026_Riding_Analysis_Preliminary.xlsx
+++ b/client/public/election-data/BC_Election_2026_Riding_Analysis_Preliminary.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive dashboard" sheetId="1" r:id="Rb1759a6322464445"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding comparison" sheetId="2" r:id="R2a5aa45eff8d42f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional patterns" sheetId="3" r:id="R1d35ce84f15b4559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDP seat changes" sheetId="4" r:id="R8b1d1223dbcf470f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closest races" sheetId="5" r:id="Rbf403fbcf4434545"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and sources" sheetId="6" r:id="R41228100a60f4278"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since last snapshot" sheetId="7" r:id="R39b2c0de49e540a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive dashboard" sheetId="1" r:id="R4ad283919c094e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding comparison" sheetId="2" r:id="R08ed5d13a8c6400c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional patterns" sheetId="3" r:id="R1a6a262c7037460b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDP seat changes" sheetId="4" r:id="Rf0ec53c396ef4770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closest races" sheetId="5" r:id="R1a400a9f0e9d4360"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and sources" sheetId="6" r:id="R912722820bc24ba9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since last snapshot" sheetId="7" r:id="R4cb16492e5784622"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -86,7 +86,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -123,6 +123,11 @@
         <x:fgColor rgb="FFF4F9F5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE4F2F4"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -131,7 +136,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -215,6 +220,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -236,7 +242,7 @@
         <x:color rgb="FFB91C1C"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -479,7 +485,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>PRELIMINARY INITIAL COUNT • Elections BC data: 26 Oct 2026, 10:34 (site timestamp) • rechecked 27 Oct: NO NEW DATA • final count planned 6-10 Nov</x:v>
+        <x:v>PRELIMINARY INITIAL COUNT • Elections BC data: 26 Oct 2026, 10:34 (site timestamp) • rechecked 28 Oct: NO NEW DATA • final count planned 6–10 Nov</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -987,7 +993,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>Latest official snapshot: 26 Oct 2026, 10:34 (site timestamp) • verified 27 Oct: same data • NDP/Con/Green shares use valid votes</x:v>
+        <x:v>Latest official snapshot: 26 Oct 2026, 10:34 (site timestamp) • verified 28 Oct: same data • NDP/Con/Green shares use valid votes</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -17827,7 +17833,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>Public edition | Initial-count data: 26 Oct 2026 | Latest source check: 27 Oct 2026 | Still preliminary</x:v>
+        <x:v>Public edition | Initial-count data: 26 Oct 2026 | Latest source check: 28 Oct 2026 | Still preliminary</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -18018,7 +18024,7 @@
         <x:v>Verification update</x:v>
       </x:c>
       <x:c r="B27" s="40" t="str">
-        <x:v>27 October 2026: official live results page still shows initial-count snapshot dated 26 Oct, 10:34. No new riding-level data or seat-lead changes.</x:v>
+        <x:v>28 October 2026: Elections BC still displays the 26 Oct, 10:34 initial-count snapshot. No new riding-level counts or seat-lead changes since 27 October.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -18034,7 +18040,7 @@
         <x:v>Source status</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>No new official count published as of 27 October check; avoid interpreting unchanged figures as a new vote count.</x:v>
+        <x:v>No new official count published as of the 28 October check; the October 26 source data remains unchanged. This verification is not a new vote count.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -18102,7 +18108,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="46" t="str">
-        <x:v>CHECKED 27 OCT 2026  |  LATEST ELECTIONS BC DATA 26 OCT, 10:34  |  NO NEW COUNT PUBLISHED</x:v>
+        <x:v>CHECKED 28 OCT 2026  |  LATEST ELECTIONS BC DATA 26 OCT, 10:34  |  NO NEW COUNT PUBLISHED</x:v>
       </x:c>
       <x:c r="B2" s="46"/>
       <x:c r="C2" s="46"/>
@@ -25782,27 +25788,41 @@
         <x:v>No new release</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="23" customHeight="1">
-      <x:c r="A102" t="str">
+    <x:row r="102" ht="21" customHeight="1">
+      <x:c r="A102" s="55" t="str">
+        <x:v>2026-10-28</x:v>
+      </x:c>
+      <x:c r="B102" s="55" t="str">
+        <x:v>2026-10-26 10:34</x:v>
+      </x:c>
+      <x:c r="C102" s="55" t="n">
+        <x:f>COUNTIF(T6:T98,"UPDATED")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D102" s="55" t="str">
+        <x:v>No new release; unchanged since Oct 27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" t="str">
         <x:v>Final count</x:v>
       </x:c>
-      <x:c r="B102" t="str">
-        <x:v>6-10 Nov 2026</x:v>
-      </x:c>
-      <x:c r="C102"/>
-      <x:c r="D102" t="str">
-        <x:v>Planned, not yet published</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="23" customHeight="1">
-      <x:c r="A103" t="str">
-        <x:v>Caveat</x:v>
-      </x:c>
       <x:c r="B103" t="str">
-        <x:v>Any new ballot counts may alter close seats</x:v>
+        <x:v>6–10 Nov 2026</x:v>
       </x:c>
       <x:c r="C103"/>
       <x:c r="D103" t="str">
+        <x:v>Planned, not yet published</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" t="str">
+        <x:v>Caveat</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>Any new ballot counts may alter close seats</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
         <x:v>Not certified</x:v>
       </x:c>
     </x:row>

--- a/client/public/election-data/BC_Election_2026_Riding_Analysis_Preliminary.xlsx
+++ b/client/public/election-data/BC_Election_2026_Riding_Analysis_Preliminary.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive dashboard" sheetId="1" r:id="R4ad283919c094e15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding comparison" sheetId="2" r:id="R08ed5d13a8c6400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional patterns" sheetId="3" r:id="R1a6a262c7037460b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDP seat changes" sheetId="4" r:id="Rf0ec53c396ef4770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closest races" sheetId="5" r:id="R1a400a9f0e9d4360"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and sources" sheetId="6" r:id="R912722820bc24ba9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since last snapshot" sheetId="7" r:id="R4cb16492e5784622"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive dashboard" sheetId="1" r:id="R3620b152acef496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riding comparison" sheetId="2" r:id="Rd0c5a59387f44a54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regional patterns" sheetId="3" r:id="R846a0c7297594625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDP seat changes" sheetId="4" r:id="Rbd7cd94a33d44282"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Closest races" sheetId="5" r:id="Ra3aa25967baa4169"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method and sources" sheetId="6" r:id="Rc73a9bc7bcda4e74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Since last snapshot" sheetId="7" r:id="Rf673ad7bc84d4621"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +25,7 @@
     <x:numFmt numFmtId="202" formatCode="#,##0;[Red](#,##0);-"/>
     <x:numFmt numFmtId="203" formatCode="#,##0;[Red](#,##0);–"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -85,8 +85,12 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -128,6 +132,11 @@
         <x:fgColor rgb="FFE4F2F4"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFECFDF5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -136,7 +145,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="56">
+  <x:cellXfs count="59">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -221,6 +230,9 @@
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -485,7 +497,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>PRELIMINARY INITIAL COUNT • Elections BC data: 26 Oct 2026, 10:34 (site timestamp) • rechecked 28 Oct: NO NEW DATA • final count planned 6–10 Nov</x:v>
+        <x:v>PRELIMINARY INITIAL COUNT • Elections BC data: 26 Oct 2026, 10:34 (site timestamp) • rechecked 29 Oct: NO NEW DATA • final count planned 6–10 Nov</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -17833,7 +17845,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="18" t="str">
-        <x:v>Public edition | Initial-count data: 26 Oct 2026 | Latest source check: 28 Oct 2026 | Still preliminary</x:v>
+        <x:v>Public edition | Initial-count data: 26 Oct 2026 | Latest source check: 29 Oct 2026 | Still preliminary</x:v>
       </x:c>
       <x:c r="B3" s="18"/>
       <x:c r="C3" s="18"/>
@@ -18024,7 +18036,7 @@
         <x:v>Verification update</x:v>
       </x:c>
       <x:c r="B27" s="40" t="str">
-        <x:v>28 October 2026: Elections BC still displays the 26 Oct, 10:34 initial-count snapshot. No new riding-level counts or seat-lead changes since 27 October.</x:v>
+        <x:v>29 October 2026: Elections BC still displays the 26 Oct, 10:34 initial-count snapshot. No new riding-level counts or seat-lead changes since 28 October.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -18040,7 +18052,7 @@
         <x:v>Source status</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>No new official count published as of the 28 October check; the October 26 source data remains unchanged. This verification is not a new vote count.</x:v>
+        <x:v>No new official count published as of the 29 October check; the October 26 source data remains unchanged. This verification is not a new vote count.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -18056,10 +18068,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="33" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
@@ -18108,7 +18120,7 @@
     </x:row>
     <x:row r="2" ht="27" customHeight="1">
       <x:c r="A2" s="46" t="str">
-        <x:v>CHECKED 28 OCT 2026  |  LATEST ELECTIONS BC DATA 26 OCT, 10:34  |  NO NEW COUNT PUBLISHED</x:v>
+        <x:v>CHECKED 29 OCT 2026  |  LATEST ELECTIONS BC DATA 26 OCT, 10:34  |  NO NEW COUNT PUBLISHED</x:v>
       </x:c>
       <x:c r="B2" s="46"/>
       <x:c r="C2" s="46"/>
@@ -25803,26 +25815,42 @@
         <x:v>No new release; unchanged since Oct 27</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="22" customHeight="1">
-      <x:c r="A103" t="str">
+    <x:row r="103" ht="23" customHeight="1">
+      <x:c r="A103" s="57" t="str">
+        <x:v>2026-10-29</x:v>
+      </x:c>
+      <x:c r="B103" s="57" t="str">
+        <x:v>2026-10-26 10:34</x:v>
+      </x:c>
+      <x:c r="C103" s="57" t="n">
+        <x:f>COUNTIF(T6:T98,"UPDATED")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D103" s="57" t="str">
+        <x:v>No new release; unchanged since Oct 28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" s="58" t="str">
         <x:v>Final count</x:v>
       </x:c>
-      <x:c r="B103" t="str">
+      <x:c r="B104" s="58" t="str">
         <x:v>6–10 Nov 2026</x:v>
       </x:c>
-      <x:c r="C103"/>
-      <x:c r="D103" t="str">
+      <x:c r="C104" s="58"/>
+      <x:c r="D104" s="58" t="str">
         <x:v>Planned, not yet published</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="22" customHeight="1">
-      <x:c r="A104" t="str">
+    <x:row r="105">
+      <x:c r="A105" s="58" t="str">
         <x:v>Caveat</x:v>
       </x:c>
-      <x:c r="B104" t="str">
+      <x:c r="B105" s="58" t="str">
         <x:v>Any new ballot counts may alter close seats</x:v>
       </x:c>
-      <x:c r="D104" t="str">
+      <x:c r="C105" s="58"/>
+      <x:c r="D105" s="58" t="str">
         <x:v>Not certified</x:v>
       </x:c>
     </x:row>
